--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -56,7 +56,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,6 +128,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -510,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  22-Apr-2026 20:30</t>
+          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  23-Apr-2026 15:17</t>
         </is>
       </c>
     </row>
@@ -557,24 +574,4344 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>465.9</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>465</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>AARTIIND_CM | AARTIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>7575.5</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>7600</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>ABB_CM | ABB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>25410</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>25400</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA_CM | ABBOTINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>349.75</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>ABCAPITAL_CM | ABCAPITAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>ABFRL_CM | ABFRL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1423.1</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>ACC_CM | ACC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>ADANIENT_CM | ADANIENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1602.9</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>ADANIPORTS_CM | ADANIPORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5520.5</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ALKEM_CM | ALKEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>450.4</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>AMBUJACEM_CM | AMBUJACEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>321.21</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE_CM | ANGELONE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>7781</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP_CM | APOLLOHOSP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>432.45</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE_CM | APOLLOTYRE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>170.63</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>ASHOKLEY_CM | ASHOKLEY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2521.4</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ASIANPAINT_CM | ASIANPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1574.9</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1575</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>ASTRAL_CM | ASTRAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>621.7</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>625</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ATGL_CM | ATGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1435.4</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>AUROPHARMA_CM | AUROPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1056.25</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>AUBANK_CM | AUBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>1369.6</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>625</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>1375</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>AXISBANK_CM | AXISBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>9550.5</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO_CM | BAJAJ-AUTO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1792.6</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV_CM | BAJAJFINSV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>918.35</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>BAJFINANCE_CM | BAJFINANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>BALKRISIND</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2265.4</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>BALKRISIND_CM | BALKRISIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>173.9</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>BANDHANBNK_CM | BANDHANBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>276.34</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>5850</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>275</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>BANKBARODA_CM | BANKBARODA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>449.95</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>BEL_CM | BEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>468.65</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>475</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>BERGEPAINT_CM | BERGEPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1841.2</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>BHARTIARTL_CM | BHARTIARTL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>340</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>BHEL_CM | BHEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>358</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>BIOCON_CM | BIOCON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>37380</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>37400</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>BOSCHLTD_CM | BOSCHLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>BPCL_CM | BPCL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>5671.5</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>5650</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>BRITANNIA_CM | BRITANNIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>140.87</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>4350</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>CANBK_CM | CANBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>1543.4</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>CHOLAFIN_CM | CHOLAFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1305.9</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>CIPLA_CM | CIPLA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>450.65</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>COALINDIA_CM | COALINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1220.6</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE_CM | COFORGE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>2150.2</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>COLPAL_CM | COLPAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>505.05</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>CONCOR_CM | CONCOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>253.39</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>255</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>CROMPTON_CM | CROMPTON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>5176.9</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>CUMMINSIND_CM | CUMMINSIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>460</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>460</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>DABUR_CM | DABUR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1731.9</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR_CM | DEEPAKNTR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>6378.5</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>DIVISLAB_CM | DIVISLAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>10866.5</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>10900</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>DIXON_CM | DIXON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>592.8</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>590</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>DLF_CM | DLF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1331</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>DRREDDY_CM | DRREDDY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>7092.5</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>EICHERMOT_CM | EICHERMOT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>3309</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>ESCORTS_CM | ESCORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>345</v>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>EXIDEIND_CM | EXIDEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>295</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK_CM | FEDERALBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>164.96</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>6400</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>GAIL_CM | GAIL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2335</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>2325</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK_CM | GLENMARK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>1142.95</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>GODREJCP_CM | GODREJCP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1791</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>GODREJPROP_CM | GODREJPROP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>686.95</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>685</v>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>GRANULES_CM | GRANULES_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>2735</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>475</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>2725</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM_CM | GRASIM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>GUJGASLTD</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>386</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>375</v>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>GUJGASLTD_CM | GUJGASLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4352.5</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>4400</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>HAL_CM | HAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>1260.3</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>HAVELLS_CM | HAVELLS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1277.6</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>HCLTECH_CM | HCLTECH_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>2708.2</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>HDFCAMC_CM | HDFCAMC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>784.35</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>775</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>HDFCBANK_CM | HDFCBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>598.65</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>600</v>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>HDFCLIFE_CM | HDFCLIFE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>5032</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO_CM | HEROMOTOCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>1041.35</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>HINDALCO_CM | HINDALCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>549.45</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>3650</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>HINDCOPPER_CM | HINDCOPPER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>375</v>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>HINDPETRO_CM | HINDPETRO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>2366.4</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>HINDUNILVR_CM | HINDUNILVR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>67.83</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB_CM | IDFCFIRSTB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>126.92</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>IEX_CM | IEX_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>165.55</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>1375</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>IGL_CM | IGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>639.45</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>640</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL_CM | INDHOTEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>INDIAMART</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>2159.4</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>INDIAMART_CM | INDIAMART_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>4556</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>4550</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>INDIGO_CM | INDIGO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>860.35</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>850</v>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>INDUSINDBK_CM | INDUSINDBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>405</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>INDUSTOWER_CM | INDUSTOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>1240.6</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>INFY_CM | INFY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>145.48</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>IOC_CM | IOC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>551.35</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>875</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>550</v>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>IRCTC_CM | IRCTC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>305.3</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>ITC_CM | ITC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>1254.5</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>JINDALSTEL_CM | JINDALSTEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>561.4</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>JSWENERGY_CM | JSWENERGY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n">
+        <v>1257</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>JSWSTEEL_CM | JSWSTEEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>492.85</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>625</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>JUBLFOOD_CM | JUBLFOOD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>375</v>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_CM | KOTAKBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>733.65</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>725</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>KPITTECH_CM | KPITTECH_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n">
+        <v>1430.9</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>LALPATHLAB_CM | LALPATHLAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>1129</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS_CM | LAURUSLABS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>545.55</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>550</v>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>LICHSGFIN_CM | LICHSGFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>4054.1</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>4050</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>LT_CM | LT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>292.12</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>290</v>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>LTF_CM | LTF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
           <t>LTIM</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>4757.9</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C97" s="5" t="n">
+        <v>4604.3</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E97" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F97" s="6" t="n">
+        <v>4600</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
         <is>
           <t>LTIM_CM | LTIM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>3449.6</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>LTTS_CM | LTTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>2341.4</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN_CM | LUPIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>3047.7</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>3050</v>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>M&amp;M_CM | M&amp;M_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>292.85</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>295</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>MANAPPURAM_CM | MANAPPURAM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>778.9</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>780</v>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>MARICO_CM | MARICO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>13160</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>13200</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>MARUTI_CM | MARUTI_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>2791.4</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>MCX_CM | MCX_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>METROPOLIS</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>472.2</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>METROPOLIS_CM | METROPOLIS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>1595.4</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>MFSL_CM | MFSL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>1137.4</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>MGL_CM | MGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>127.22</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>MOTHERSON_CM | MOTHERSON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>2277</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>MPHASIS_CM | MPHASIS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>134615</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>134500</v>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>MRF_CM | MRF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>3561.4</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>3550</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN_CM | MUTHOOTFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>439.25</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>440</v>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>NATIONALUM_CM | NATIONALUM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>1018.05</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>NAUKRI_CM | NAUKRI_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>6280.5</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR_CM | NAVINFLUOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>1410.5</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>NESTLEIND_CM | NESTLEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>87.31</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>NMDC_CM | NMDC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>402.25</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>NTPC_CM | NTPC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>1707.7</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY_CM | OBEROIRLTY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>8791.5</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>OFSS_CM | OFSS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>290</v>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>ONGC_CM | ONGC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>37965</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>PAGEIND_CM | PAGEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>5065.2</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>PERSISTENT_CM | PERSISTENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>275.81</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET_CM | PETRONET_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="n">
+        <v>469.8</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>470</v>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>PFC_CM | PFC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>1402.1</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND_CM | PIDILITIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="n">
+        <v>3069.6</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>3050</v>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>PIIND_CM | PIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>PNB_CM | PNB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>7963.5</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>POLYCAB_CM | POLYCAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>319.15</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>POWERGRID_CM | POWERGRID_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="n">
+        <v>312.45</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>310</v>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>RBLBANK_CM | RBLBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>RECLTD_CM | RECLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E132" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>RELIANCE_CM | RELIANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>176.45</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>SAIL_CM | SAIL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>680.55</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E134" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>675</v>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>SBICARD_CM | SBICARD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>1828.1</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>1825</v>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>SBILIFE_CM | SBILIFE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>1094.25</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E136" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F136" s="10" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>SBIN_CM | SBIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>25470</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>25500</v>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>SHREECEM_CM | SHREECEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>1009.3</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E138" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F138" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN_CM | SHRIRAMFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>3864.4</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>3850</v>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>SIEMENS_CM | SIEMENS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>2542.4</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="E140" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>2550</v>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>SRF_CM | SRF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>1680.1</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_CM | SUNPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="n">
+        <v>625.85</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E142" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>630</v>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>SUNTV_CM | SUNTV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>428.35</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>SYNGENE_CM | SYNGENE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E144" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>700</v>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>TATACHEM_CM | TATACHEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>1580.7</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>1575</v>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>TATACOMM_CM | TATACOMM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="n">
+        <v>1184.4</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>TATACONSUM_CM | TATACONSUM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>430.3</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>3375</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F147" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER_CM | TATAPOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>210.91</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E148" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F148" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>TATASTEEL_CM | TATASTEEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>2521.8</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>TCS_CM | TCS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>1421.5</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>TECHM_CM | TECHM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>4456.5</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>4450</v>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>TITAN_CM | TITAN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="n">
+        <v>4147.2</v>
+      </c>
+      <c r="D152" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E152" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>TORNTPHARM_CM | TORNTPHARM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>1737</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>1725</v>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>TORNTPOWER_CM | TORNTPOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="n">
+        <v>4251.4</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F154" s="10" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>TRENT_CM | TRENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>3513</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>3525</v>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>TVSMOTOR_CM | TVSMOTOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="n">
+        <v>1483.2</v>
+      </c>
+      <c r="D156" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>1475</v>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>UBL_CM | UBL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>12167</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v>12200</v>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO_CM | ULTRACEMCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="n">
+        <v>179.71</v>
+      </c>
+      <c r="D158" s="7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>UNIONBANK_CM | UNIONBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>642.05</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>UPL_CM | UPL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="n">
+        <v>735.6</v>
+      </c>
+      <c r="D160" s="7" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E160" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F160" s="10" t="n">
+        <v>740</v>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>VEDL_CM | VEDL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>1445.5</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>VOLTAS_CM | VOLTAS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="n">
+        <v>202.76</v>
+      </c>
+      <c r="D162" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F162" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>WIPRO_CM | WIPRO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>946.35</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F163" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE_CM | ZYDUSLIFE_NM</t>
         </is>
       </c>
     </row>
@@ -601,151 +4938,151 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Legend &amp; Column Guide</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Sheet Naming</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SYMBOL_CM = Current Month | SYMBOL_NM = Next Month</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Monthly Expiry</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Last Thursday of each month (NSE standard for stock F&amp;O)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>ATM Row</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Yellow = At-The-Money strike (nearest to spot price)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>CALL (CE)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Blue — buyer profits when stock RISES above strike</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>PUT (PE)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Red — buyer profits when stock FALLS below strike</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Last traded price of the option contract</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Open Interest — total outstanding contracts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Contracts traded in current session</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>IV (%)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Implied Volatility (%) from Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Open / Chg OI</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>0 = not available via Yahoo Finance option chain</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Data Source</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Yahoo Finance (yfinance) — NSE option chain</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>GitHub Actions — Every weekday Mon–Fri at 6:30 PM IST</t>
         </is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  23-Apr-2026 15:17</t>
+          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  24-Apr-2026 14:47</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>465.9</v>
+        <v>472.75</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7575.5</v>
+        <v>7328.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7600</v>
+        <v>7350</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25410</v>
+        <v>25180</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25400</v>
+        <v>25200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>349.75</v>
+        <v>340.6</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63.2</v>
+        <v>61.79</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1423.1</v>
+        <v>1412.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2300</v>
+        <v>2287.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1602.9</v>
+        <v>1585.1</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5520.5</v>
+        <v>5235</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>450.4</v>
+        <v>451.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>321.21</v>
+        <v>314.52</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7781</v>
+        <v>7732.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7800</v>
+        <v>7700</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>432.45</v>
+        <v>423.85</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>170.63</v>
+        <v>169.9</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2521.4</v>
+        <v>2485.1</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1574.9</v>
+        <v>1563.2</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>621.7</v>
+        <v>626.85</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1435.4</v>
+        <v>1413.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1056.25</v>
+        <v>1065.65</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1369.6</v>
+        <v>1365.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9550.5</v>
+        <v>9576</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1792.6</v>
+        <v>1770.7</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>918.35</v>
+        <v>921.55</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2265.4</v>
+        <v>2225.4</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>173.9</v>
+        <v>174.67</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>276.34</v>
+        <v>274.13</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>449.95</v>
+        <v>444.45</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>468.65</v>
+        <v>460.4</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1841.2</v>
+        <v>1814.5</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>337.6</v>
+        <v>337.39</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>358</v>
+        <v>349.85</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37380</v>
+        <v>36690</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37400</v>
+        <v>36600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>309.8</v>
+        <v>308.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5671.5</v>
+        <v>5730.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5650</v>
+        <v>5750</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>140.87</v>
+        <v>140.85</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1543.4</v>
+        <v>1568.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1305.9</v>
+        <v>1295</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>450.65</v>
+        <v>456</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1220.6</v>
+        <v>1150.9</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2150.2</v>
+        <v>2171.3</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2150</v>
+        <v>2175</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>505.05</v>
+        <v>502.8</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>253.39</v>
+        <v>250.23</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5176.9</v>
+        <v>5232</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>460</v>
+        <v>451.1</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1731.9</v>
+        <v>1690.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6378.5</v>
+        <v>6361.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10866.5</v>
+        <v>10815.5</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>10900</v>
+        <v>10800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>592.8</v>
+        <v>587.05</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1331</v>
+        <v>1317.1</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7092.5</v>
+        <v>7111.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3309</v>
+        <v>3231.3</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3300</v>
+        <v>3250</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>347.25</v>
+        <v>342.8</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>295.4</v>
+        <v>293</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>164.96</v>
+        <v>165.61</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2335</v>
+        <v>2299.5</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2325</v>
+        <v>2300</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1142.95</v>
+        <v>1089.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1791</v>
+        <v>1769.4</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>686.95</v>
+        <v>689.45</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2735</v>
+        <v>2739.3</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2725</v>
+        <v>2750</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>386</v>
+        <v>383.85</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4352.5</v>
+        <v>4265.8</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1260.3</v>
+        <v>1238.6</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1277.6</v>
+        <v>1203.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1275</v>
+        <v>1200</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2708.2</v>
+        <v>2735</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>784.35</v>
+        <v>784.85</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>598.65</v>
+        <v>588.2</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5032</v>
+        <v>4961.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5050</v>
+        <v>4950</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1041.35</v>
+        <v>1048.35</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>549.45</v>
+        <v>541.5</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>376.9</v>
+        <v>373.5</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2366.4</v>
+        <v>2327.3</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>67.83</v>
+        <v>67.23</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>126.92</v>
+        <v>123.23</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>165.55</v>
+        <v>164.61</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>639.45</v>
+        <v>635.35</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2159.4</v>
+        <v>2107.1</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4556</v>
+        <v>4523.1</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4550</v>
+        <v>4500</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>860.35</v>
+        <v>847.95</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>404.7</v>
+        <v>402.2</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1240.6</v>
+        <v>1154.6</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1250</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>145.48</v>
+        <v>143.47</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>551.35</v>
+        <v>541.2</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>305.3</v>
+        <v>301.6</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1254.5</v>
+        <v>1256</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>561.4</v>
+        <v>544.95</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1257</v>
+        <v>1255.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>492.85</v>
+        <v>491.95</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>370.4</v>
+        <v>370.85</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>733.65</v>
+        <v>709.6</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1430.9</v>
+        <v>1408.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1129</v>
+        <v>1113.45</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1130</v>
+        <v>1115</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>545.55</v>
+        <v>540.75</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4054.1</v>
+        <v>4014.3</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4000</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>292.12</v>
+        <v>290.05</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>4604.3</v>
+        <v>4531.5</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>150</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3449.6</v>
+        <v>3379.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>200</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2341.4</v>
+        <v>2296.1</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>500</v>
@@ -3179,7 +3179,7 @@
         <v>25</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>3047.7</v>
+        <v>3038.4</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>175</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>292.85</v>
+        <v>289.4</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>4000</v>
@@ -3233,7 +3233,7 @@
         <v>5</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>778.9</v>
+        <v>783.3</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>1200</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>13160</v>
+        <v>13048</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>100</v>
@@ -3287,7 +3287,7 @@
         <v>100</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>13200</v>
+        <v>13000</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>2791.4</v>
+        <v>2760.9</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>472.2</v>
+        <v>467.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>400</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1595.4</v>
+        <v>1587.3</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>1100</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1137.4</v>
+        <v>1130.15</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>550</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>127.22</v>
+        <v>125.7</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>14000</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2277</v>
+        <v>2175.8</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>300</v>
@@ -3449,7 +3449,7 @@
         <v>50</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>134615</v>
+        <v>132145</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>5</v>
@@ -3476,7 +3476,7 @@
         <v>500</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>134500</v>
+        <v>132000</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>3561.4</v>
+        <v>3493.5</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>600</v>
@@ -3503,7 +3503,7 @@
         <v>25</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>3550</v>
+        <v>3500</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>439.25</v>
+        <v>437.05</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>7500</v>
@@ -3530,7 +3530,7 @@
         <v>5</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1018.05</v>
+        <v>984.95</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>150</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>6280.5</v>
+        <v>6452</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>200</v>
@@ -3584,7 +3584,7 @@
         <v>100</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1410.5</v>
+        <v>1421.3</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>50</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>87.31</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>6750</v>
@@ -3638,7 +3638,7 @@
         <v>5</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>402.25</v>
+        <v>401.85</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>2250</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1707.7</v>
+        <v>1687</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>700</v>
@@ -3692,7 +3692,7 @@
         <v>25</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>8791.5</v>
+        <v>8949</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>75</v>
@@ -3719,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>286.25</v>
+        <v>284.8</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>1925</v>
@@ -3746,7 +3746,7 @@
         <v>10</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>37965</v>
+        <v>37665</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
         <v>500</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>38000</v>
+        <v>37500</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>5065.2</v>
+        <v>4747.3</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>175</v>
@@ -3800,7 +3800,7 @@
         <v>100</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>5100</v>
+        <v>4700</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>275.81</v>
+        <v>273.45</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>3000</v>
@@ -3827,7 +3827,7 @@
         <v>10</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>469.8</v>
+        <v>469.35</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>2700</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1402.1</v>
+        <v>1394.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>3069.6</v>
+        <v>3081.2</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>250</v>
@@ -3908,7 +3908,7 @@
         <v>50</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>112.71</v>
+        <v>113.09</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>8000</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>7963.5</v>
+        <v>8033</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>175</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>319.15</v>
+        <v>316.4</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>2700</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>312.45</v>
+        <v>321.4</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>5000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>376.45</v>
+        <v>374</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>3000</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1343.4</v>
+        <v>1327.8</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1250</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>176.45</v>
+        <v>178.46</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>8500</v>
@@ -4097,7 +4097,7 @@
         <v>5</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>680.55</v>
+        <v>670.3</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1000</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1828.1</v>
+        <v>1768.9</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>750</v>
@@ -4151,7 +4151,7 @@
         <v>25</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1825</v>
+        <v>1775</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1094.25</v>
+        <v>1101.1</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>1500</v>
@@ -4178,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>1090</v>
+        <v>1100</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>25470</v>
+        <v>24950</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>25</v>
@@ -4205,7 +4205,7 @@
         <v>500</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>25500</v>
+        <v>25000</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>1009.3</v>
+        <v>1011.3</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>300</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3864.4</v>
+        <v>3808.9</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>275</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>3850</v>
+        <v>3800</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2542.4</v>
+        <v>2493.6</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>375</v>
@@ -4286,7 +4286,7 @@
         <v>50</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1680.1</v>
+        <v>1620.4</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>350</v>
@@ -4313,7 +4313,7 @@
         <v>25</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1675</v>
+        <v>1625</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>625.85</v>
+        <v>600.15</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>428.35</v>
+        <v>421.2</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1500</v>
@@ -4367,7 +4367,7 @@
         <v>10</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>707.7</v>
+        <v>693.25</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1580.7</v>
+        <v>1520.6</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>700</v>
@@ -4421,7 +4421,7 @@
         <v>25</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1575</v>
+        <v>1525</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1184.4</v>
+        <v>1174</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>1100</v>
@@ -4448,7 +4448,7 @@
         <v>10</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>430.3</v>
+        <v>435</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>3375</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>210.91</v>
+        <v>210.07</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>5500</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>2521.8</v>
+        <v>2396.9</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>150</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1421.5</v>
+        <v>1358.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>400</v>
@@ -4556,7 +4556,7 @@
         <v>25</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1425</v>
+        <v>1350</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4456.5</v>
+        <v>4410</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>375</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4450</v>
+        <v>4400</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>4147.2</v>
+        <v>4117.2</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>500</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>4150</v>
+        <v>4100</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1737</v>
+        <v>1699.5</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>1500</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4251.4</v>
+        <v>4297.3</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>375</v>
@@ -4664,7 +4664,7 @@
         <v>50</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4250</v>
+        <v>4300</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>3513</v>
+        <v>3488.2</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>350</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>3525</v>
+        <v>3500</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1483.2</v>
+        <v>1477.1</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>700</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>12167</v>
+        <v>11998</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>200</v>
@@ -4745,7 +4745,7 @@
         <v>100</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>12200</v>
+        <v>12000</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>179.71</v>
+        <v>177</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>8400</v>
@@ -4772,7 +4772,7 @@
         <v>5</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>642.05</v>
+        <v>631.4</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1300</v>
@@ -4799,7 +4799,7 @@
         <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>735.6</v>
+        <v>720.95</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>2750</v>
@@ -4826,7 +4826,7 @@
         <v>10</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1445.5</v>
+        <v>1464</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1000</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>202.76</v>
+        <v>199.36</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>1500</v>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>946.35</v>
+        <v>927.4</v>
       </c>
       <c r="D163" s="3" t="n">
         <v>700</v>
@@ -4907,7 +4907,7 @@
         <v>25</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  24-Apr-2026 14:47</t>
+          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  27-Apr-2026 15:10</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>472.75</v>
+        <v>488.75</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7328.5</v>
+        <v>7430.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7350</v>
+        <v>7450</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25180</v>
+        <v>25425</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25200</v>
+        <v>25400</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>340.6</v>
+        <v>342.55</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61.79</v>
+        <v>63.92</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1412.7</v>
+        <v>1439.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2287.6</v>
+        <v>2321.8</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1585.1</v>
+        <v>1628.5</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1575</v>
+        <v>1625</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5235</v>
+        <v>5344</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>451.2</v>
+        <v>460.5</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>314.52</v>
+        <v>318.64</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7732.5</v>
+        <v>7825</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7700</v>
+        <v>7800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>423.85</v>
+        <v>428.55</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>169.9</v>
+        <v>169.3</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2485.1</v>
+        <v>2485.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1563.2</v>
+        <v>1535</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1575</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>626.85</v>
+        <v>635.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1413.8</v>
+        <v>1416.7</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1065.65</v>
+        <v>1043</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1365.9</v>
+        <v>1324.2</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1375</v>
+        <v>1325</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9576</v>
+        <v>9662</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1770.7</v>
+        <v>1772.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>921.55</v>
+        <v>921.8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2225.4</v>
+        <v>2223.4</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>174.67</v>
+        <v>181.87</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>274.13</v>
+        <v>273.99</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>444.45</v>
+        <v>435.6</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>460.4</v>
+        <v>463.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1814.5</v>
+        <v>1820.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>337.39</v>
+        <v>348.58</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>349.85</v>
+        <v>362</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36690</v>
+        <v>37225</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36600</v>
+        <v>37200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>308.1</v>
+        <v>312.65</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5730.5</v>
+        <v>5717.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5750</v>
+        <v>5700</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>140.85</v>
+        <v>140.52</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1568.2</v>
+        <v>1560.7</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1295</v>
+        <v>1317.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>456</v>
+        <v>452.5</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1150.9</v>
+        <v>1202.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2171.3</v>
+        <v>2141</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2175</v>
+        <v>2150</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>502.8</v>
+        <v>514.2</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>250.23</v>
+        <v>258.68</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5232</v>
+        <v>5233.2</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>451.1</v>
+        <v>452</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1690.3</v>
+        <v>1684.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6361.5</v>
+        <v>6477</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10815.5</v>
+        <v>11252</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>10800</v>
+        <v>11300</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>587.05</v>
+        <v>592.45</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1317.1</v>
+        <v>1334.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7111.5</v>
+        <v>7174</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3231.3</v>
+        <v>3262.5</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>342.8</v>
+        <v>352.35</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>293</v>
+        <v>294.05</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>165.61</v>
+        <v>165.74</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2299.5</v>
+        <v>2325.1</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2300</v>
+        <v>2325</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1089.9</v>
+        <v>1089.25</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1769.4</v>
+        <v>1828.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1750</v>
+        <v>1850</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>689.45</v>
+        <v>694.9</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2739.3</v>
+        <v>2778.2</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2750</v>
+        <v>2775</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>383.85</v>
+        <v>383</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4265.8</v>
+        <v>4310.3</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1238.6</v>
+        <v>1274.1</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1203.2</v>
+        <v>1228.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1200</v>
+        <v>1225</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2735</v>
+        <v>2756</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>784.85</v>
+        <v>789.8</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>588.2</v>
+        <v>597.3</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4961.5</v>
+        <v>5043</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4950</v>
+        <v>5050</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1048.35</v>
+        <v>1061.8</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>541.5</v>
+        <v>559.35</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>373.5</v>
+        <v>380.9</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2327.3</v>
+        <v>2328.3</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>67.23</v>
+        <v>70.27</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123.23</v>
+        <v>126.45</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>164.61</v>
+        <v>164.88</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>635.35</v>
+        <v>647.85</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>635</v>
+        <v>650</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2107.1</v>
+        <v>2119.5</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4523.1</v>
+        <v>4561.2</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4500</v>
+        <v>4550</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>847.95</v>
+        <v>900.15</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>402.2</v>
+        <v>402.3</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1154.6</v>
+        <v>1170.3</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>143.47</v>
+        <v>146.26</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>541.2</v>
+        <v>545.1</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>301.6</v>
+        <v>303.85</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1256</v>
+        <v>1278.2</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>544.95</v>
+        <v>573.8</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1255.7</v>
+        <v>1282.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>491.95</v>
+        <v>485.1</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>370.85</v>
+        <v>376.8</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>709.6</v>
+        <v>735.3</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1408.9</v>
+        <v>1416</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1113.45</v>
+        <v>1123.55</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>540.75</v>
+        <v>543.1</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4014.3</v>
+        <v>4053.6</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4000</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>290.05</v>
+        <v>287.79</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>4531.5</v>
+        <v>4282.3</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>150</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3379.8</v>
+        <v>3589.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>200</v>
@@ -3152,7 +3152,7 @@
         <v>100</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2296.1</v>
+        <v>2324.5</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>500</v>
@@ -3179,7 +3179,7 @@
         <v>25</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>2300</v>
+        <v>2325</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>3038.4</v>
+        <v>3102.4</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>175</v>
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>289.4</v>
+        <v>288.2</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>4000</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>783.3</v>
+        <v>787</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>1200</v>
@@ -3260,7 +3260,7 @@
         <v>10</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>13048</v>
+        <v>13222</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>100</v>
@@ -3287,7 +3287,7 @@
         <v>100</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>13000</v>
+        <v>13200</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>2760.9</v>
+        <v>2830</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>2750</v>
+        <v>2825</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>467.1</v>
+        <v>476.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>400</v>
@@ -3341,7 +3341,7 @@
         <v>50</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1587.3</v>
+        <v>1603</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>1100</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1130.15</v>
+        <v>1141.8</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>550</v>
@@ -3395,7 +3395,7 @@
         <v>25</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>125.7</v>
+        <v>127.93</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>14000</v>
@@ -3422,7 +3422,7 @@
         <v>5</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2175.8</v>
+        <v>2264.9</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>300</v>
@@ -3449,7 +3449,7 @@
         <v>50</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>132145</v>
+        <v>132205</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>5</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>3493.5</v>
+        <v>3493.8</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>600</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>437.05</v>
+        <v>441</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>7500</v>
@@ -3530,7 +3530,7 @@
         <v>5</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>984.95</v>
+        <v>1000.9</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>150</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>6452</v>
+        <v>6578.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>200</v>
@@ -3584,7 +3584,7 @@
         <v>100</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1421.3</v>
+        <v>1417.3</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>50</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>89.29000000000001</v>
+        <v>90.42</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>6750</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>401.85</v>
+        <v>410.2</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>2250</v>
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1687</v>
+        <v>1723.3</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>700</v>
@@ -3692,7 +3692,7 @@
         <v>25</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>1675</v>
+        <v>1725</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>8949</v>
+        <v>9360</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>75</v>
@@ -3719,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>8900</v>
+        <v>9400</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>284.8</v>
+        <v>285.9</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>1925</v>
@@ -3746,7 +3746,7 @@
         <v>10</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>37665</v>
+        <v>37705</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>15</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>4747.3</v>
+        <v>4817.5</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>175</v>
@@ -3800,7 +3800,7 @@
         <v>100</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>273.45</v>
+        <v>279.9</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>3000</v>
@@ -3827,7 +3827,7 @@
         <v>10</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>469.35</v>
+        <v>474.9</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>2700</v>
@@ -3854,7 +3854,7 @@
         <v>5</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1394.3</v>
+        <v>1399.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>3081.2</v>
+        <v>3083.6</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>250</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>113.09</v>
+        <v>113.88</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>8000</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>8033</v>
+        <v>8065.5</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>175</v>
@@ -3962,7 +3962,7 @@
         <v>100</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>316.4</v>
+        <v>320.9</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>2700</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>321.4</v>
+        <v>312.8</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>5000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>374</v>
+        <v>378.05</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>3000</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1327.8</v>
+        <v>1365.8</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1250</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>178.46</v>
+        <v>184.2</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>8500</v>
@@ -4097,7 +4097,7 @@
         <v>5</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>670.3</v>
+        <v>670.7</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1000</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1768.9</v>
+        <v>1815.4</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>750</v>
@@ -4151,7 +4151,7 @@
         <v>25</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1775</v>
+        <v>1825</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1101.1</v>
+        <v>1111.85</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>1500</v>
@@ -4178,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>24950</v>
+        <v>25125</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>25</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>1011.3</v>
+        <v>974.65</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>300</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3808.9</v>
+        <v>3856</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>275</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>3800</v>
+        <v>3850</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2493.6</v>
+        <v>2508.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>375</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1620.4</v>
+        <v>1733.5</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>350</v>
@@ -4313,7 +4313,7 @@
         <v>25</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1625</v>
+        <v>1725</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>600.15</v>
+        <v>611</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>421.2</v>
+        <v>437.95</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1500</v>
@@ -4367,7 +4367,7 @@
         <v>10</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>693.25</v>
+        <v>722.3</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1520.6</v>
+        <v>1574.7</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>700</v>
@@ -4421,7 +4421,7 @@
         <v>25</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1525</v>
+        <v>1575</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1174</v>
+        <v>1160.5</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>1100</v>
@@ -4448,7 +4448,7 @@
         <v>10</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1170</v>
+        <v>1160</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>435</v>
+        <v>453.2</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>3375</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>210.07</v>
+        <v>213.27</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>5500</v>
@@ -4502,7 +4502,7 @@
         <v>5</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>2396.9</v>
+        <v>2447.6</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>150</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1358.5</v>
+        <v>1396.1</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>400</v>
@@ -4556,7 +4556,7 @@
         <v>25</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4410</v>
+        <v>4441.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>375</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4400</v>
+        <v>4450</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>4117.2</v>
+        <v>4219.8</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>500</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1699.5</v>
+        <v>1772.5</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>1500</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>1700</v>
+        <v>1775</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4297.3</v>
+        <v>4260.8</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>375</v>
@@ -4664,7 +4664,7 @@
         <v>50</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4300</v>
+        <v>4250</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>3488.2</v>
+        <v>3552.6</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>350</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>3500</v>
+        <v>3550</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1477.1</v>
+        <v>1479.2</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>700</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>11998</v>
+        <v>12010</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>200</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>177</v>
+        <v>176.1</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>8400</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>631.4</v>
+        <v>639.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1300</v>
@@ -4799,7 +4799,7 @@
         <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>720.95</v>
+        <v>742.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>2750</v>
@@ -4826,7 +4826,7 @@
         <v>10</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1464</v>
+        <v>1515</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1000</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1475</v>
+        <v>1525</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>199.36</v>
+        <v>205.05</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>1500</v>
@@ -4880,7 +4880,7 @@
         <v>10</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>927.4</v>
+        <v>939.65</v>
       </c>
       <c r="D163" s="3" t="n">
         <v>700</v>
@@ -4907,7 +4907,7 @@
         <v>25</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  27-Apr-2026 15:10</t>
+          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  28-Apr-2026 15:30</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>488.75</v>
+        <v>501.7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7430.5</v>
+        <v>7288</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7450</v>
+        <v>7300</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25425</v>
+        <v>25345</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>342.55</v>
+        <v>338.3</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63.92</v>
+        <v>63.58</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1439.8</v>
+        <v>1439.3</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2321.8</v>
+        <v>2412.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1628.5</v>
+        <v>1637.6</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5344</v>
+        <v>5418.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>460.5</v>
+        <v>458.8</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>318.64</v>
+        <v>319.27</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7825</v>
+        <v>7753</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>428.55</v>
+        <v>423.65</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>169.3</v>
+        <v>167.52</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2485.2</v>
+        <v>2462.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1535</v>
+        <v>1548.9</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>635.6</v>
+        <v>653.85</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1416.7</v>
+        <v>1422.6</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1043</v>
+        <v>1022.8</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1324.2</v>
+        <v>1289</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9662</v>
+        <v>9495.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1772.2</v>
+        <v>1779</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>921.8</v>
+        <v>923.65</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2223.4</v>
+        <v>2189.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>181.87</v>
+        <v>178.65</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>273.99</v>
+        <v>267.83</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>435.6</v>
+        <v>435.75</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>463.6</v>
+        <v>459.85</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1820.1</v>
+        <v>1843.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>348.58</v>
+        <v>354.71</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>362</v>
+        <v>362.8</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37225</v>
+        <v>37320</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37200</v>
+        <v>37400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>312.65</v>
+        <v>307.75</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5717.5</v>
+        <v>5662</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5700</v>
+        <v>5650</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>140.52</v>
+        <v>137.1</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1560.7</v>
+        <v>1536.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1317.2</v>
+        <v>1306.5</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>452.5</v>
+        <v>467</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1202.4</v>
+        <v>1200.9</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2141</v>
+        <v>2125.2</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2150</v>
+        <v>2125</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>514.2</v>
+        <v>510.5</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>258.68</v>
+        <v>269.63</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5233.2</v>
+        <v>5258</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>452</v>
+        <v>450.15</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1684.9</v>
+        <v>1682.6</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6477</v>
+        <v>6432.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11252</v>
+        <v>11370</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>592.45</v>
+        <v>587.9</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1334.5</v>
+        <v>1354.6</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7174</v>
+        <v>7071.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3262.5</v>
+        <v>3308.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3250</v>
+        <v>3300</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>352.35</v>
+        <v>356.25</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>294.05</v>
+        <v>290.6</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>165.74</v>
+        <v>165.68</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2325.1</v>
+        <v>2403.7</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2325</v>
+        <v>2400</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1089.25</v>
+        <v>1092</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1828.2</v>
+        <v>1824.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>694.9</v>
+        <v>705.15</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2778.2</v>
+        <v>2783</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>383</v>
+        <v>389.45</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4310.3</v>
+        <v>4341.4</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1274.1</v>
+        <v>1272.2</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1228.2</v>
+        <v>1196</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2756</v>
+        <v>2760.2</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>789.8</v>
+        <v>782.55</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>597.3</v>
+        <v>590.15</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5043</v>
+        <v>5068</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1061.8</v>
+        <v>1074.3</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>559.35</v>
+        <v>556.4</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>380.9</v>
+        <v>380.05</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2328.3</v>
+        <v>2289.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>70.27</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>126.45</v>
+        <v>125.94</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>164.88</v>
+        <v>166.45</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>647.85</v>
+        <v>652.45</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2119.5</v>
+        <v>2129.3</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4561.2</v>
+        <v>4442.4</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4550</v>
+        <v>4450</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>900.15</v>
+        <v>885.55</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>402.3</v>
+        <v>413.95</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1170.3</v>
+        <v>1152.1</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>146.26</v>
+        <v>145.39</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>545.1</v>
+        <v>543.85</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>303.85</v>
+        <v>304.45</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1278.2</v>
+        <v>1265.5</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>573.8</v>
+        <v>580.9</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1282.7</v>
+        <v>1281.6</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>485.1</v>
+        <v>482.4</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>376.8</v>
+        <v>377.95</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>735.3</v>
+        <v>734.45</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1416</v>
+        <v>1411.7</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1123.55</v>
+        <v>1090.45</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1125</v>
+        <v>1090</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>543.1</v>
+        <v>550</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4053.6</v>
+        <v>4037.7</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>287.79</v>
+        <v>285.78</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>4282.3</v>
+        <v>4346</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>150</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3589.8</v>
+        <v>3566.4</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>200</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2324.5</v>
+        <v>2302.7</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>500</v>
@@ -3179,7 +3179,7 @@
         <v>25</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>2325</v>
+        <v>2300</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>3102.4</v>
+        <v>3088.1</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>175</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>288.2</v>
+        <v>292.75</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>4000</v>
@@ -3233,7 +3233,7 @@
         <v>5</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>787</v>
+        <v>780.85</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>1200</v>
@@ -3260,7 +3260,7 @@
         <v>10</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>13222</v>
+        <v>12892</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>100</v>
@@ -3287,7 +3287,7 @@
         <v>100</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>13200</v>
+        <v>12900</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>2830</v>
+        <v>2898</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>2825</v>
+        <v>2900</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>476.5</v>
+        <v>480.85</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>400</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1603</v>
+        <v>1610.8</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>1100</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1141.8</v>
+        <v>1133</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>550</v>
@@ -3395,7 +3395,7 @@
         <v>25</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>127.93</v>
+        <v>125.22</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>14000</v>
@@ -3422,7 +3422,7 @@
         <v>5</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2264.9</v>
+        <v>2270.3</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>300</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>132205</v>
+        <v>130120</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>5</v>
@@ -3476,7 +3476,7 @@
         <v>500</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>132000</v>
+        <v>130000</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>3493.8</v>
+        <v>3496</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>600</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>441</v>
+        <v>441.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>7500</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1000.9</v>
+        <v>1004.6</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>150</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>6578.5</v>
+        <v>6627</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>200</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1417.3</v>
+        <v>1440</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>50</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>90.42</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>6750</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>410.2</v>
+        <v>406.85</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>2250</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1723.3</v>
+        <v>1710.3</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>700</v>
@@ -3692,7 +3692,7 @@
         <v>25</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>9360</v>
+        <v>9570</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>75</v>
@@ -3719,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>285.9</v>
+        <v>301.3</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>1925</v>
@@ -3746,7 +3746,7 @@
         <v>10</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>37705</v>
+        <v>37505</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>15</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>4817.5</v>
+        <v>4803.5</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>175</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>279.9</v>
+        <v>277.72</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>3000</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>474.9</v>
+        <v>481.4</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>2700</v>
@@ -3854,7 +3854,7 @@
         <v>5</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1399.3</v>
+        <v>1392.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>3083.6</v>
+        <v>3097.6</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>250</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>113.88</v>
+        <v>111.39</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>8000</v>
@@ -3935,7 +3935,7 @@
         <v>5</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>8065.5</v>
+        <v>8254</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>175</v>
@@ -3962,7 +3962,7 @@
         <v>100</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>320.9</v>
+        <v>319</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>2700</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>312.8</v>
+        <v>320.75</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>5000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>378.05</v>
+        <v>375.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>3000</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1365.8</v>
+        <v>1388.9</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1250</v>
@@ -4070,7 +4070,7 @@
         <v>50</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>184.2</v>
+        <v>185.63</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>8500</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>670.7</v>
+        <v>647.45</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1000</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1815.4</v>
+        <v>1808.3</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>750</v>
@@ -4151,7 +4151,7 @@
         <v>25</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1111.85</v>
+        <v>1091.3</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>1500</v>
@@ -4178,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>1110</v>
+        <v>1090</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>25125</v>
+        <v>24890</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>25</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>974.65</v>
+        <v>953.25</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>300</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3856</v>
+        <v>3827.3</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>275</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2508.2</v>
+        <v>2532.8</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>375</v>
@@ -4286,7 +4286,7 @@
         <v>50</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>2500</v>
+        <v>2550</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1733.5</v>
+        <v>1747.3</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>350</v>
@@ -4313,7 +4313,7 @@
         <v>25</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>611</v>
+        <v>595.05</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>437.95</v>
+        <v>440.25</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1500</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>722.3</v>
+        <v>802.15</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>725</v>
+        <v>800</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1574.7</v>
+        <v>1598.6</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>700</v>
@@ -4421,7 +4421,7 @@
         <v>25</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1160.5</v>
+        <v>1147.7</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>1100</v>
@@ -4448,7 +4448,7 @@
         <v>10</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1160</v>
+        <v>1150</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>453.2</v>
+        <v>461.8</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>3375</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>213.27</v>
+        <v>215.05</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>5500</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>2447.6</v>
+        <v>2444.7</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>150</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1396.1</v>
+        <v>1408.1</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>400</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4441.8</v>
+        <v>4417</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>375</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4450</v>
+        <v>4400</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>4219.8</v>
+        <v>4182.9</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1772.5</v>
+        <v>1754.9</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>1500</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4260.8</v>
+        <v>4253.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>375</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>3552.6</v>
+        <v>3495.9</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>350</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>3550</v>
+        <v>3500</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1479.2</v>
+        <v>1477.2</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>700</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>12010</v>
+        <v>11817</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>200</v>
@@ -4745,7 +4745,7 @@
         <v>100</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>12000</v>
+        <v>11800</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>176.1</v>
+        <v>170.48</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>8400</v>
@@ -4772,7 +4772,7 @@
         <v>5</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>639.5</v>
+        <v>645.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1300</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>742.5</v>
+        <v>739.3</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>2750</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1515</v>
+        <v>1511.1</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1000</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>205.05</v>
+        <v>201.58</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>1500</v>
@@ -4880,7 +4880,7 @@
         <v>10</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>939.65</v>
+        <v>911.3</v>
       </c>
       <c r="D163" s="3" t="n">
         <v>700</v>
@@ -4907,7 +4907,7 @@
         <v>25</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  28-Apr-2026 15:30</t>
+          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  29-Apr-2026 15:18</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>501.7</v>
+        <v>502.35</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7288</v>
+        <v>7264.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7300</v>
+        <v>7250</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25345</v>
+        <v>25475</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>338.3</v>
+        <v>348.45</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63.58</v>
+        <v>65.05</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1439.3</v>
+        <v>1436.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2412.4</v>
+        <v>2425.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1637.6</v>
+        <v>1661.1</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5418.5</v>
+        <v>5344</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>458.8</v>
+        <v>454.6</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>319.27</v>
+        <v>313.1</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7753</v>
+        <v>7709</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7800</v>
+        <v>7700</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>423.65</v>
+        <v>424.15</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>167.52</v>
+        <v>165.73</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2462.6</v>
+        <v>2447.3</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1548.9</v>
+        <v>1552.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>653.85</v>
+        <v>656.95</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1422.6</v>
+        <v>1396.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1022.8</v>
+        <v>1017.65</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1289</v>
+        <v>1296.4</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9495.5</v>
+        <v>9543.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1779</v>
+        <v>1764.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>923.65</v>
+        <v>930</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2189.3</v>
+        <v>2199.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>178.65</v>
+        <v>198.3</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>267.83</v>
+        <v>268.25</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>435.75</v>
+        <v>437.55</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>459.85</v>
+        <v>463.8</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1843.8</v>
+        <v>1888.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>354.71</v>
+        <v>344.5</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>362.8</v>
+        <v>362.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37320</v>
+        <v>36345</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37400</v>
+        <v>36400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>307.75</v>
+        <v>303.9</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5662</v>
+        <v>5709</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5650</v>
+        <v>5700</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>137.1</v>
+        <v>137.06</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1536.4</v>
+        <v>1553.3</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1306.5</v>
+        <v>1317.6</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>467</v>
+        <v>479.9</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1200.9</v>
+        <v>1204</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2125.2</v>
+        <v>2132.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>510.5</v>
+        <v>514.6</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>269.63</v>
+        <v>276.01</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5258</v>
+        <v>5288</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5250</v>
+        <v>5300</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>450.15</v>
+        <v>456</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1682.6</v>
+        <v>1724.1</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6432.5</v>
+        <v>6534</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11370</v>
+        <v>11325</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>587.9</v>
+        <v>594.45</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1354.6</v>
+        <v>1329.8</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7071.5</v>
+        <v>7189.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3308.6</v>
+        <v>3302.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>356.25</v>
+        <v>363.45</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>290.6</v>
+        <v>284.75</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>165.68</v>
+        <v>165.66</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2403.7</v>
+        <v>2413.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2400</v>
+        <v>2425</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1092</v>
+        <v>1090.05</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1824.6</v>
+        <v>1862.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>705.15</v>
+        <v>704.55</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2783</v>
+        <v>2803.2</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2775</v>
+        <v>2800</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>389.45</v>
+        <v>391</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4341.4</v>
+        <v>4351.6</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1272.2</v>
+        <v>1252.5</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1196</v>
+        <v>1200.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2760.2</v>
+        <v>2787.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>782.55</v>
+        <v>779</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>590.15</v>
+        <v>594.4</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5068</v>
+        <v>5114.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1074.3</v>
+        <v>1067.2</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>556.4</v>
+        <v>555.25</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>380.05</v>
+        <v>380.6</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2289.5</v>
+        <v>2314.4</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>68.70999999999999</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.94</v>
+        <v>126.05</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>166.45</v>
+        <v>167.55</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>652.45</v>
+        <v>644.65</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2129.3</v>
+        <v>2130.8</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4442.4</v>
+        <v>4345.2</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4450</v>
+        <v>4350</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>885.55</v>
+        <v>913.75</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>875</v>
+        <v>925</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>413.95</v>
+        <v>413.9</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1152.1</v>
+        <v>1167.5</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>145.39</v>
+        <v>144.19</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>543.85</v>
+        <v>550.1</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>304.45</v>
+        <v>316.25</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1265.5</v>
+        <v>1228.1</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1275</v>
+        <v>1225</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>580.9</v>
+        <v>560.4</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1281.6</v>
+        <v>1279.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>482.4</v>
+        <v>485.4</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>377.95</v>
+        <v>382</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>734.45</v>
+        <v>740.05</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1411.7</v>
+        <v>1397.8</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1090.45</v>
+        <v>1106.1</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1090</v>
+        <v>1105</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>550</v>
+        <v>562.15</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4037.7</v>
+        <v>4096.1</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>285.78</v>
+        <v>285.42</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>4346</v>
+        <v>4380.6</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>150</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3566.4</v>
+        <v>3559.6</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>200</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2302.7</v>
+        <v>2311.4</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>500</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>3088.1</v>
+        <v>3152.3</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>175</v>
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>292.75</v>
+        <v>295.35</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>4000</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>780.85</v>
+        <v>779.3</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>1200</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>12892</v>
+        <v>13257</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>100</v>
@@ -3287,7 +3287,7 @@
         <v>100</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>12900</v>
+        <v>13300</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>2898</v>
+        <v>2968.3</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>2900</v>
+        <v>2975</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>480.85</v>
+        <v>478.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>400</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1610.8</v>
+        <v>1610.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>1100</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>550</v>
@@ -3395,7 +3395,7 @@
         <v>25</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>125.22</v>
+        <v>123.24</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>14000</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2270.3</v>
+        <v>2250.7</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>300</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>130120</v>
+        <v>130425</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>5</v>
@@ -3476,7 +3476,7 @@
         <v>500</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>130000</v>
+        <v>130500</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>3496</v>
+        <v>3461.1</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>600</v>
@@ -3503,7 +3503,7 @@
         <v>25</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>441.5</v>
+        <v>433.3</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>7500</v>
@@ -3530,7 +3530,7 @@
         <v>5</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1004.6</v>
+        <v>991.65</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>150</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>6627</v>
+        <v>6758.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>200</v>
@@ -3584,7 +3584,7 @@
         <v>100</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>6600</v>
+        <v>6800</v>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1440</v>
+        <v>1465.6</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>50</v>
@@ -3611,7 +3611,7 @@
         <v>100</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>90.90000000000001</v>
+        <v>91.73</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>6750</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>406.85</v>
+        <v>401.3</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>2250</v>
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1710.3</v>
+        <v>1700.3</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>700</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>9570</v>
+        <v>9688</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>75</v>
@@ -3719,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>301.3</v>
+        <v>301.4</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>1925</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>37505</v>
+        <v>36845</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
         <v>500</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>37500</v>
+        <v>37000</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>4803.5</v>
+        <v>4805.8</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>175</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>277.72</v>
+        <v>280.12</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>3000</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>481.4</v>
+        <v>464.75</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>2700</v>
@@ -3854,7 +3854,7 @@
         <v>5</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1392.6</v>
+        <v>1389</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>3097.6</v>
+        <v>3091.1</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>250</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>111.39</v>
+        <v>111.18</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>8000</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>8254</v>
+        <v>8148.5</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>175</v>
@@ -3962,7 +3962,7 @@
         <v>100</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>319</v>
+        <v>320.35</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>2700</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>320.75</v>
+        <v>341.2</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>5000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>375.8</v>
+        <v>363.55</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>3000</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1388.9</v>
+        <v>1425.4</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1250</v>
@@ -4070,7 +4070,7 @@
         <v>50</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>185.63</v>
+        <v>186.16</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>8500</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>647.45</v>
+        <v>651.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1000</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1808.3</v>
+        <v>1816.2</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>750</v>
@@ -4151,7 +4151,7 @@
         <v>25</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1091.3</v>
+        <v>1086.9</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>1500</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>24890</v>
+        <v>24555</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>25</v>
@@ -4205,7 +4205,7 @@
         <v>500</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>25000</v>
+        <v>24500</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>953.25</v>
+        <v>956.85</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>300</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3827.3</v>
+        <v>3776.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>275</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>3850</v>
+        <v>3800</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2532.8</v>
+        <v>2543.6</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>375</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1747.3</v>
+        <v>1778.7</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>350</v>
@@ -4313,7 +4313,7 @@
         <v>25</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>595.05</v>
+        <v>586.25</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>440.25</v>
+        <v>432.15</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1500</v>
@@ -4367,7 +4367,7 @@
         <v>10</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>802.15</v>
+        <v>799.75</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1598.6</v>
+        <v>1602.2</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>700</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1147.7</v>
+        <v>1168</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>1100</v>
@@ -4448,7 +4448,7 @@
         <v>10</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1150</v>
+        <v>1170</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>461.8</v>
+        <v>451.5</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>3375</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>215.05</v>
+        <v>215.88</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>5500</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>2444.7</v>
+        <v>2474.7</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>150</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1408.1</v>
+        <v>1459.8</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>400</v>
@@ -4556,7 +4556,7 @@
         <v>25</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4417</v>
+        <v>4439.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>375</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4400</v>
+        <v>4450</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>4182.9</v>
+        <v>4231.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>500</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>4200</v>
+        <v>4250</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1754.9</v>
+        <v>1701.7</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>1500</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4253.9</v>
+        <v>4228.3</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>375</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>3495.9</v>
+        <v>3553.9</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>350</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>3500</v>
+        <v>3550</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1477.2</v>
+        <v>1469.6</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>700</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>11817</v>
+        <v>11833</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>200</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>170.48</v>
+        <v>167.31</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>8400</v>
@@ -4772,7 +4772,7 @@
         <v>5</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>645.5</v>
+        <v>644.1</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1300</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>739.3</v>
+        <v>773.6</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>2750</v>
@@ -4826,7 +4826,7 @@
         <v>10</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1511.1</v>
+        <v>1474.8</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1000</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1500</v>
+        <v>1475</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>201.58</v>
+        <v>200.68</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>1500</v>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>911.3</v>
+        <v>910.85</v>
       </c>
       <c r="D163" s="3" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  29-Apr-2026 15:18</t>
+          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  30-Apr-2026 15:14</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>502.35</v>
+        <v>507.5</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7264.5</v>
+        <v>7230</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25475</v>
+        <v>25435</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>348.45</v>
+        <v>345.5</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>65.05</v>
+        <v>64.2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1436.6</v>
+        <v>1422.1</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2425.9</v>
+        <v>2408.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1661.1</v>
+        <v>1657.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5344</v>
+        <v>5400</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>454.6</v>
+        <v>444.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>313.1</v>
+        <v>308.71</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7709</v>
+        <v>7636.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>424.15</v>
+        <v>408.4</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>165.73</v>
+        <v>162.09</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2447.3</v>
+        <v>2444.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1552.8</v>
+        <v>1529.7</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>656.95</v>
+        <v>634.7</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1396.8</v>
+        <v>1389.5</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1017.65</v>
+        <v>1015.95</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1296.4</v>
+        <v>1268.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9543.5</v>
+        <v>9994</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>9500</v>
+        <v>10000</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1764.2</v>
+        <v>1747.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2199.9</v>
+        <v>2160.8</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>198.3</v>
+        <v>199.72</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>268.25</v>
+        <v>263.46</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>437.55</v>
+        <v>431.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>463.8</v>
+        <v>473.1</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1888.1</v>
+        <v>1886.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>344.5</v>
+        <v>352.41</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>362.25</v>
+        <v>359.65</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36345</v>
+        <v>35995</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36400</v>
+        <v>36000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>303.9</v>
+        <v>300.45</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5709</v>
+        <v>5726</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5700</v>
+        <v>5750</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>137.06</v>
+        <v>134.65</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1553.3</v>
+        <v>1562.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1317.6</v>
+        <v>1309.6</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>479.9</v>
+        <v>481.45</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1204</v>
+        <v>1195.9</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2132.5</v>
+        <v>2096.2</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2125</v>
+        <v>2100</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>514.6</v>
+        <v>508.85</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>276.01</v>
+        <v>272.36</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5288</v>
+        <v>5266.4</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>456</v>
+        <v>441.5</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1724.1</v>
+        <v>1736.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6534</v>
+        <v>6502.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11325</v>
+        <v>11166.5</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11300</v>
+        <v>11200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>594.45</v>
+        <v>587</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1329.8</v>
+        <v>1322.9</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7189.5</v>
+        <v>7109</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3302.1</v>
+        <v>3241.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3300</v>
+        <v>3250</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>363.45</v>
+        <v>360.55</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>284.75</v>
+        <v>286.95</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>165.66</v>
+        <v>163.23</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2413.9</v>
+        <v>2406.3</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2425</v>
+        <v>2400</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1090.05</v>
+        <v>1067.1</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1862.3</v>
+        <v>1835.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>704.55</v>
+        <v>699.7</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2803.2</v>
+        <v>2794.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>391</v>
+        <v>380.05</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4351.6</v>
+        <v>4338.8</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1252.5</v>
+        <v>1240.6</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1200.2</v>
+        <v>1199.1</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2787.9</v>
+        <v>2712.6</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>779</v>
+        <v>771.7</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>594.4</v>
+        <v>586.9</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5114.5</v>
+        <v>5099</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1067.2</v>
+        <v>1038</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1070</v>
+        <v>1040</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>555.25</v>
+        <v>534.85</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>380.6</v>
+        <v>374.55</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2314.4</v>
+        <v>2250.9</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>70.15000000000001</v>
+        <v>69.64</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>126.05</v>
+        <v>125.19</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>167.55</v>
+        <v>166.02</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>644.65</v>
+        <v>635.85</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2130.8</v>
+        <v>2103.6</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4345.2</v>
+        <v>4295.3</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4350</v>
+        <v>4300</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>913.75</v>
+        <v>916.05</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>413.9</v>
+        <v>409.95</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1167.5</v>
+        <v>1181.8</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>144.19</v>
+        <v>142.25</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>550.1</v>
+        <v>539.55</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>316.25</v>
+        <v>314.9</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1228.1</v>
+        <v>1223.1</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>560.4</v>
+        <v>561.15</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1279.7</v>
+        <v>1264.5</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>485.4</v>
+        <v>478.6</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>382</v>
+        <v>383.3</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>740.05</v>
+        <v>759.05</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1397.8</v>
+        <v>1367.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1106.1</v>
+        <v>1100.95</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>562.15</v>
+        <v>554.7</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4096.1</v>
+        <v>4014</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>285.42</v>
+        <v>279.73</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>4380.6</v>
+        <v>4323.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>150</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3559.6</v>
+        <v>3626.3</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>200</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2311.4</v>
+        <v>2305.2</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>500</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>3152.3</v>
+        <v>3097.5</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>175</v>
@@ -3206,7 +3206,7 @@
         <v>50</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>295.35</v>
+        <v>294.35</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>4000</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>779.3</v>
+        <v>775</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>1200</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>13257</v>
+        <v>13314</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>100</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>2968.3</v>
+        <v>2971.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>478.8</v>
+        <v>476.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>400</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1610.4</v>
+        <v>1585.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>1100</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1146</v>
+        <v>1135.65</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>550</v>
@@ -3395,7 +3395,7 @@
         <v>25</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>123.24</v>
+        <v>121.21</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>14000</v>
@@ -3422,7 +3422,7 @@
         <v>5</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2250.7</v>
+        <v>2276.7</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>300</v>
@@ -3449,7 +3449,7 @@
         <v>50</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>130425</v>
+        <v>129710</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>5</v>
@@ -3476,7 +3476,7 @@
         <v>500</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>130500</v>
+        <v>129500</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>3461.1</v>
+        <v>3424.2</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>600</v>
@@ -3503,7 +3503,7 @@
         <v>25</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>3450</v>
+        <v>3425</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>433.3</v>
+        <v>399.3</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>7500</v>
@@ -3530,7 +3530,7 @@
         <v>5</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>991.65</v>
+        <v>972.85</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>150</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>6758.5</v>
+        <v>6821</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>200</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1465.6</v>
+        <v>1458.6</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>50</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>91.73</v>
+        <v>90.37</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>6750</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>401.3</v>
+        <v>399.15</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>2250</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1700.3</v>
+        <v>1669.6</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>700</v>
@@ -3692,7 +3692,7 @@
         <v>25</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>9688</v>
+        <v>9726.5</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>75</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>301.4</v>
+        <v>299.55</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>1925</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>36845</v>
+        <v>36785</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>15</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>4805.8</v>
+        <v>4800</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>175</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>280.12</v>
+        <v>276.76</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>3000</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>464.75</v>
+        <v>448.4</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>2700</v>
@@ -3854,7 +3854,7 @@
         <v>5</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1389</v>
+        <v>1375.7</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>3091.1</v>
+        <v>3054.8</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>250</v>
@@ -3908,7 +3908,7 @@
         <v>50</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>111.18</v>
+        <v>109.36</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>8000</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>8148.5</v>
+        <v>8110.5</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>175</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>320.35</v>
+        <v>318.35</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>2700</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>341.2</v>
+        <v>336.55</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>5000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>363.55</v>
+        <v>354.3</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>3000</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1425.4</v>
+        <v>1430.8</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1250</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>186.16</v>
+        <v>184.62</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>8500</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>651.2</v>
+        <v>643.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1000</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1816.2</v>
+        <v>1819</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>750</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1086.9</v>
+        <v>1068.45</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>1500</v>
@@ -4178,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>1090</v>
+        <v>1070</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>24555</v>
+        <v>24195</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>25</v>
@@ -4205,7 +4205,7 @@
         <v>500</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>24500</v>
+        <v>24000</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>956.85</v>
+        <v>937.35</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>300</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3776.8</v>
+        <v>3808.2</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>275</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2543.6</v>
+        <v>2518.6</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>375</v>
@@ -4286,7 +4286,7 @@
         <v>50</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1778.7</v>
+        <v>1808.3</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>350</v>
@@ -4313,7 +4313,7 @@
         <v>25</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>586.25</v>
+        <v>605.6</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>432.15</v>
+        <v>467.65</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1500</v>
@@ -4367,7 +4367,7 @@
         <v>10</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>799.75</v>
+        <v>809</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1602.2</v>
+        <v>1580.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>700</v>
@@ -4421,7 +4421,7 @@
         <v>25</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1168</v>
+        <v>1144.6</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>1100</v>
@@ -4448,7 +4448,7 @@
         <v>10</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1170</v>
+        <v>1140</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>451.5</v>
+        <v>444.55</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>3375</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>215.88</v>
+        <v>211.36</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>5500</v>
@@ -4502,7 +4502,7 @@
         <v>5</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>2474.7</v>
+        <v>2473.9</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>150</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1459.8</v>
+        <v>1473.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>400</v>
@@ -4556,7 +4556,7 @@
         <v>25</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4439.8</v>
+        <v>4385.2</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>375</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4450</v>
+        <v>4400</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>4231.5</v>
+        <v>4185.1</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>500</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>4250</v>
+        <v>4200</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1701.7</v>
+        <v>1736</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>1500</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4228.3</v>
+        <v>4144.6</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>375</v>
@@ -4664,7 +4664,7 @@
         <v>50</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4250</v>
+        <v>4150</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>3553.9</v>
+        <v>3492.9</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>350</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>3550</v>
+        <v>3500</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1469.6</v>
+        <v>1458.6</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>700</v>
@@ -4718,7 +4718,7 @@
         <v>25</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>11833</v>
+        <v>11586</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>200</v>
@@ -4745,7 +4745,7 @@
         <v>100</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>11800</v>
+        <v>11600</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>167.31</v>
+        <v>165.94</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>8400</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>644.1</v>
+        <v>641.85</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1300</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>773.6</v>
+        <v>271.55</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>2750</v>
@@ -4826,7 +4826,7 @@
         <v>10</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>770</v>
+        <v>270</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1474.8</v>
+        <v>1430.4</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1000</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1475</v>
+        <v>1425</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>200.68</v>
+        <v>200.65</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>1500</v>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>910.85</v>
+        <v>891.9</v>
       </c>
       <c r="D163" s="3" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Apr-2026  NM:28-May-2026  |  30-Apr-2026 15:14</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  01-May-2026 14:19</t>
         </is>
       </c>
     </row>
@@ -3112,24 +3112,24 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>4323.1</v>
+        <v>3626.3</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E97" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>LTIM_CM | LTIM_NM</t>
+          <t>LTTS_CM | LTTS_NM</t>
         </is>
       </c>
     </row>
@@ -3139,24 +3139,24 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3626.3</v>
+        <v>2305.2</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3600</v>
+        <v>2300</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>LTTS_CM | LTTS_NM</t>
+          <t>LUPIN_CM | LUPIN_NM</t>
         </is>
       </c>
     </row>
@@ -3166,24 +3166,24 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2305.2</v>
+        <v>3097.5</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>500</v>
+        <v>175</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>2300</v>
+        <v>3100</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>LUPIN_CM | LUPIN_NM</t>
+          <t>M&amp;M_CM | M&amp;M_NM</t>
         </is>
       </c>
     </row>
@@ -3193,24 +3193,24 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>3097.5</v>
+        <v>294.35</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>175</v>
+        <v>4000</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>3100</v>
+        <v>295</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>M&amp;M_CM | M&amp;M_NM</t>
+          <t>MANAPPURAM_CM | MANAPPURAM_NM</t>
         </is>
       </c>
     </row>
@@ -3220,24 +3220,24 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>294.35</v>
+        <v>775</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>295</v>
+        <v>780</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>MANAPPURAM_CM | MANAPPURAM_NM</t>
+          <t>MARICO_CM | MARICO_NM</t>
         </is>
       </c>
     </row>
@@ -3247,24 +3247,24 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>775</v>
+        <v>13314</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>780</v>
+        <v>13300</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>MARICO_CM | MARICO_NM</t>
+          <t>MARUTI_CM | MARUTI_NM</t>
         </is>
       </c>
     </row>
@@ -3274,24 +3274,24 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>13314</v>
+        <v>2971.5</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>13300</v>
+        <v>2975</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>MARUTI_CM | MARUTI_NM</t>
+          <t>MCX_CM | MCX_NM</t>
         </is>
       </c>
     </row>
@@ -3301,24 +3301,24 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>2971.5</v>
+        <v>476.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>2975</v>
+        <v>500</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>MCX_CM | MCX_NM</t>
+          <t>METROPOLIS_CM | METROPOLIS_NM</t>
         </is>
       </c>
     </row>
@@ -3328,24 +3328,24 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>476.5</v>
+        <v>1585.7</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>500</v>
+        <v>1575</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>METROPOLIS_CM | METROPOLIS_NM</t>
+          <t>MFSL_CM | MFSL_NM</t>
         </is>
       </c>
     </row>
@@ -3355,24 +3355,24 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1585.7</v>
+        <v>1135.65</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="E106" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1575</v>
+        <v>1125</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>MFSL_CM | MFSL_NM</t>
+          <t>MGL_CM | MGL_NM</t>
         </is>
       </c>
     </row>
@@ -3382,24 +3382,24 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>1135.65</v>
+        <v>121.21</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>550</v>
+        <v>14000</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>1125</v>
+        <v>120</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>MGL_CM | MGL_NM</t>
+          <t>MOTHERSON_CM | MOTHERSON_NM</t>
         </is>
       </c>
     </row>
@@ -3409,24 +3409,24 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>121.21</v>
+        <v>2276.7</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>14000</v>
+        <v>300</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>120</v>
+        <v>2300</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>MOTHERSON_CM | MOTHERSON_NM</t>
+          <t>MPHASIS_CM | MPHASIS_NM</t>
         </is>
       </c>
     </row>
@@ -3436,24 +3436,24 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2276.7</v>
+        <v>129710</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2300</v>
+        <v>129500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>MPHASIS_CM | MPHASIS_NM</t>
+          <t>MRF_CM | MRF_NM</t>
         </is>
       </c>
     </row>
@@ -3463,24 +3463,24 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>129710</v>
+        <v>3424.2</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>5</v>
+        <v>600</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>129500</v>
+        <v>3425</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>MRF_CM | MRF_NM</t>
+          <t>MUTHOOTFIN_CM | MUTHOOTFIN_NM</t>
         </is>
       </c>
     </row>
@@ -3490,24 +3490,24 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>3424.2</v>
+        <v>399.3</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>600</v>
+        <v>7500</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>3425</v>
+        <v>400</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN_CM | MUTHOOTFIN_NM</t>
+          <t>NATIONALUM_CM | NATIONALUM_NM</t>
         </is>
       </c>
     </row>
@@ -3517,24 +3517,24 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>399.3</v>
+        <v>972.85</v>
       </c>
       <c r="D112" s="7" t="n">
-        <v>7500</v>
+        <v>150</v>
       </c>
       <c r="E112" s="7" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>NATIONALUM_CM | NATIONALUM_NM</t>
+          <t>NAUKRI_CM | NAUKRI_NM</t>
         </is>
       </c>
     </row>
@@ -3544,24 +3544,24 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>972.85</v>
+        <v>6821</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1000</v>
+        <v>6800</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>NAUKRI_CM | NAUKRI_NM</t>
+          <t>NAVINFLUOR_CM | NAVINFLUOR_NM</t>
         </is>
       </c>
     </row>
@@ -3571,24 +3571,24 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>6821</v>
+        <v>1458.6</v>
       </c>
       <c r="D114" s="7" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E114" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>6800</v>
+        <v>1500</v>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>NAVINFLUOR_CM | NAVINFLUOR_NM</t>
+          <t>NESTLEIND_CM | NESTLEIND_NM</t>
         </is>
       </c>
     </row>
@@ -3598,24 +3598,24 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1458.6</v>
+        <v>90.37</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>50</v>
+        <v>6750</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>1500</v>
+        <v>90</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>NESTLEIND_CM | NESTLEIND_NM</t>
+          <t>NMDC_CM | NMDC_NM</t>
         </is>
       </c>
     </row>
@@ -3625,24 +3625,24 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>90.37</v>
+        <v>399.15</v>
       </c>
       <c r="D116" s="7" t="n">
-        <v>6750</v>
+        <v>2250</v>
       </c>
       <c r="E116" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>NMDC_CM | NMDC_NM</t>
+          <t>NTPC_CM | NTPC_NM</t>
         </is>
       </c>
     </row>
@@ -3652,24 +3652,24 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>399.15</v>
+        <v>1669.6</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>2250</v>
+        <v>700</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>400</v>
+        <v>1675</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>NTPC_CM | NTPC_NM</t>
+          <t>OBEROIRLTY_CM | OBEROIRLTY_NM</t>
         </is>
       </c>
     </row>
@@ -3679,24 +3679,24 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>1669.6</v>
+        <v>9726.5</v>
       </c>
       <c r="D118" s="7" t="n">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="E118" s="7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>1675</v>
+        <v>9700</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>OBEROIRLTY_CM | OBEROIRLTY_NM</t>
+          <t>OFSS_CM | OFSS_NM</t>
         </is>
       </c>
     </row>
@@ -3706,24 +3706,24 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>9726.5</v>
+        <v>299.55</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>75</v>
+        <v>1925</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>9700</v>
+        <v>300</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>OFSS_CM | OFSS_NM</t>
+          <t>ONGC_CM | ONGC_NM</t>
         </is>
       </c>
     </row>
@@ -3733,24 +3733,24 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>299.55</v>
+        <v>36785</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>1925</v>
+        <v>15</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>300</v>
+        <v>37000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>ONGC_CM | ONGC_NM</t>
+          <t>PAGEIND_CM | PAGEIND_NM</t>
         </is>
       </c>
     </row>
@@ -3760,24 +3760,24 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>36785</v>
+        <v>4800</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>37000</v>
+        <v>4800</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>PAGEIND_CM | PAGEIND_NM</t>
+          <t>PERSISTENT_CM | PERSISTENT_NM</t>
         </is>
       </c>
     </row>
@@ -3787,24 +3787,24 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>4800</v>
+        <v>276.76</v>
       </c>
       <c r="D122" s="7" t="n">
-        <v>175</v>
+        <v>3000</v>
       </c>
       <c r="E122" s="7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>4800</v>
+        <v>280</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>PERSISTENT_CM | PERSISTENT_NM</t>
+          <t>PETRONET_CM | PETRONET_NM</t>
         </is>
       </c>
     </row>
@@ -3814,24 +3814,24 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>276.76</v>
+        <v>448.4</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>PETRONET_CM | PETRONET_NM</t>
+          <t>PFC_CM | PFC_NM</t>
         </is>
       </c>
     </row>
@@ -3841,24 +3841,24 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>448.4</v>
+        <v>1375.7</v>
       </c>
       <c r="D124" s="7" t="n">
-        <v>2700</v>
+        <v>250</v>
       </c>
       <c r="E124" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>450</v>
+        <v>1400</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>PFC_CM | PFC_NM</t>
+          <t>PIDILITIND_CM | PIDILITIND_NM</t>
         </is>
       </c>
     </row>
@@ -3868,11 +3868,11 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1375.7</v>
+        <v>3054.8</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,11 +3881,11 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>1400</v>
+        <v>3050</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND_CM | PIDILITIND_NM</t>
+          <t>PIIND_CM | PIIND_NM</t>
         </is>
       </c>
     </row>
@@ -3895,24 +3895,24 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>3054.8</v>
+        <v>109.36</v>
       </c>
       <c r="D126" s="7" t="n">
-        <v>250</v>
+        <v>8000</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>3050</v>
+        <v>110</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>PIIND_CM | PIIND_NM</t>
+          <t>PNB_CM | PNB_NM</t>
         </is>
       </c>
     </row>
@@ -3922,24 +3922,24 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>109.36</v>
+        <v>8110.5</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>8000</v>
+        <v>175</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>110</v>
+        <v>8100</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>PNB_CM | PNB_NM</t>
+          <t>POLYCAB_CM | POLYCAB_NM</t>
         </is>
       </c>
     </row>
@@ -3949,24 +3949,24 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>8110.5</v>
+        <v>318.35</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>175</v>
+        <v>2700</v>
       </c>
       <c r="E128" s="7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>8100</v>
+        <v>320</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>POLYCAB_CM | POLYCAB_NM</t>
+          <t>POWERGRID_CM | POWERGRID_NM</t>
         </is>
       </c>
     </row>
@@ -3976,24 +3976,24 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>318.35</v>
+        <v>336.55</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>2700</v>
+        <v>5000</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>POWERGRID_CM | POWERGRID_NM</t>
+          <t>RBLBANK_CM | RBLBANK_NM</t>
         </is>
       </c>
     </row>
@@ -4003,24 +4003,24 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>336.55</v>
+        <v>354.3</v>
       </c>
       <c r="D130" s="7" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E130" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>RBLBANK_CM | RBLBANK_NM</t>
+          <t>RECLTD_CM | RECLTD_NM</t>
         </is>
       </c>
     </row>
@@ -4030,24 +4030,24 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>354.3</v>
+        <v>1430.8</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>3000</v>
+        <v>1250</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>355</v>
+        <v>1450</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>RECLTD_CM | RECLTD_NM</t>
+          <t>RELIANCE_CM | RELIANCE_NM</t>
         </is>
       </c>
     </row>
@@ -4057,24 +4057,24 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1430.8</v>
+        <v>184.62</v>
       </c>
       <c r="D132" s="7" t="n">
-        <v>1250</v>
+        <v>8500</v>
       </c>
       <c r="E132" s="7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>1450</v>
+        <v>185</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>RELIANCE_CM | RELIANCE_NM</t>
+          <t>SAIL_CM | SAIL_NM</t>
         </is>
       </c>
     </row>
@@ -4084,24 +4084,24 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>184.62</v>
+        <v>643.9</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>8500</v>
+        <v>1000</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>185</v>
+        <v>650</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>SAIL_CM | SAIL_NM</t>
+          <t>SBICARD_CM | SBICARD_NM</t>
         </is>
       </c>
     </row>
@@ -4111,24 +4111,24 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>643.9</v>
+        <v>1819</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="E134" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>650</v>
+        <v>1825</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>SBICARD_CM | SBICARD_NM</t>
+          <t>SBILIFE_CM | SBILIFE_NM</t>
         </is>
       </c>
     </row>
@@ -4138,24 +4138,24 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1819</v>
+        <v>1068.45</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1825</v>
+        <v>1070</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>SBILIFE_CM | SBILIFE_NM</t>
+          <t>SBIN_CM | SBIN_NM</t>
         </is>
       </c>
     </row>
@@ -4165,24 +4165,24 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1068.45</v>
+        <v>24195</v>
       </c>
       <c r="D136" s="7" t="n">
-        <v>1500</v>
+        <v>25</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>1070</v>
+        <v>24000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>SBIN_CM | SBIN_NM</t>
+          <t>SHREECEM_CM | SHREECEM_NM</t>
         </is>
       </c>
     </row>
@@ -4192,24 +4192,24 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>24195</v>
+        <v>937.35</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>24000</v>
+        <v>950</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>SHREECEM_CM | SHREECEM_NM</t>
+          <t>SHRIRAMFIN_CM | SHRIRAMFIN_NM</t>
         </is>
       </c>
     </row>
@@ -4219,24 +4219,24 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>937.35</v>
+        <v>3808.2</v>
       </c>
       <c r="D138" s="7" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="E138" s="7" t="n">
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>950</v>
+        <v>3800</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN_CM | SHRIRAMFIN_NM</t>
+          <t>SIEMENS_CM | SIEMENS_NM</t>
         </is>
       </c>
     </row>
@@ -4246,24 +4246,24 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3808.2</v>
+        <v>2518.6</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="E139" s="3" t="n">
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>SIEMENS_CM | SIEMENS_NM</t>
+          <t>SRF_CM | SRF_NM</t>
         </is>
       </c>
     </row>
@@ -4273,24 +4273,24 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2518.6</v>
+        <v>1808.3</v>
       </c>
       <c r="D140" s="7" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E140" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>SRF_CM | SRF_NM</t>
+          <t>SUNPHARMA_CM | SUNPHARMA_NM</t>
         </is>
       </c>
     </row>
@@ -4300,24 +4300,24 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>1808.3</v>
+        <v>605.6</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>1800</v>
+        <v>610</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>SUNPHARMA_CM | SUNPHARMA_NM</t>
+          <t>SUNTV_CM | SUNTV_NM</t>
         </is>
       </c>
     </row>
@@ -4327,11 +4327,11 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>605.6</v>
+        <v>467.65</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,11 +4340,11 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>610</v>
+        <v>470</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>SUNTV_CM | SUNTV_NM</t>
+          <t>SYNGENE_CM | SYNGENE_NM</t>
         </is>
       </c>
     </row>
@@ -4354,24 +4354,24 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>467.65</v>
+        <v>809</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>470</v>
+        <v>800</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>SYNGENE_CM | SYNGENE_NM</t>
+          <t>TATACHEM_CM | TATACHEM_NM</t>
         </is>
       </c>
     </row>
@@ -4381,24 +4381,24 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>809</v>
+        <v>1580.5</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="E144" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>800</v>
+        <v>1575</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>TATACHEM_CM | TATACHEM_NM</t>
+          <t>TATACOMM_CM | TATACOMM_NM</t>
         </is>
       </c>
     </row>
@@ -4408,24 +4408,24 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1580.5</v>
+        <v>1144.6</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1575</v>
+        <v>1140</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>TATACOMM_CM | TATACOMM_NM</t>
+          <t>TATACONSUM_CM | TATACONSUM_NM</t>
         </is>
       </c>
     </row>
@@ -4435,24 +4435,24 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>1144.6</v>
+        <v>444.55</v>
       </c>
       <c r="D146" s="7" t="n">
-        <v>1100</v>
+        <v>3375</v>
       </c>
       <c r="E146" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1140</v>
+        <v>445</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>TATACONSUM_CM | TATACONSUM_NM</t>
+          <t>TATAPOWER_CM | TATAPOWER_NM</t>
         </is>
       </c>
     </row>
@@ -4462,24 +4462,24 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>444.55</v>
+        <v>211.36</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>3375</v>
+        <v>5500</v>
       </c>
       <c r="E147" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>445</v>
+        <v>210</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>TATAPOWER_CM | TATAPOWER_NM</t>
+          <t>TATASTEEL_CM | TATASTEEL_NM</t>
         </is>
       </c>
     </row>
@@ -4489,24 +4489,24 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>211.36</v>
+        <v>2473.9</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>5500</v>
+        <v>150</v>
       </c>
       <c r="E148" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>210</v>
+        <v>2450</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>TATASTEEL_CM | TATASTEEL_NM</t>
+          <t>TCS_CM | TCS_NM</t>
         </is>
       </c>
     </row>
@@ -4516,24 +4516,24 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>2473.9</v>
+        <v>1473.5</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>2450</v>
+        <v>1475</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>TCS_CM | TCS_NM</t>
+          <t>TECHM_CM | TECHM_NM</t>
         </is>
       </c>
     </row>
@@ -4543,24 +4543,24 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>1473.5</v>
+        <v>4385.2</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="E150" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>1475</v>
+        <v>4400</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>TECHM_CM | TECHM_NM</t>
+          <t>TITAN_CM | TITAN_NM</t>
         </is>
       </c>
     </row>
@@ -4570,24 +4570,24 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4385.2</v>
+        <v>4185.1</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="E151" s="3" t="n">
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>TITAN_CM | TITAN_NM</t>
+          <t>TORNTPHARM_CM | TORNTPHARM_NM</t>
         </is>
       </c>
     </row>
@@ -4597,24 +4597,24 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>4185.1</v>
+        <v>1736</v>
       </c>
       <c r="D152" s="7" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>4200</v>
+        <v>1725</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>TORNTPHARM_CM | TORNTPHARM_NM</t>
+          <t>TORNTPOWER_CM | TORNTPOWER_NM</t>
         </is>
       </c>
     </row>
@@ -4624,24 +4624,24 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1736</v>
+        <v>4144.6</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>1500</v>
+        <v>375</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>1725</v>
+        <v>4150</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>TORNTPOWER_CM | TORNTPOWER_NM</t>
+          <t>TRENT_CM | TRENT_NM</t>
         </is>
       </c>
     </row>
@@ -4651,24 +4651,24 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4144.6</v>
+        <v>3492.9</v>
       </c>
       <c r="D154" s="7" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E154" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4150</v>
+        <v>3500</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>TRENT_CM | TRENT_NM</t>
+          <t>TVSMOTOR_CM | TVSMOTOR_NM</t>
         </is>
       </c>
     </row>
@@ -4678,24 +4678,24 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>3492.9</v>
+        <v>1458.6</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E155" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>3500</v>
+        <v>1450</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>TVSMOTOR_CM | TVSMOTOR_NM</t>
+          <t>UBL_CM | UBL_NM</t>
         </is>
       </c>
     </row>
@@ -4705,24 +4705,24 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>1458.6</v>
+        <v>11586</v>
       </c>
       <c r="D156" s="7" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>1450</v>
+        <v>11600</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>UBL_CM | UBL_NM</t>
+          <t>ULTRACEMCO_CM | ULTRACEMCO_NM</t>
         </is>
       </c>
     </row>
@@ -4732,24 +4732,24 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>11586</v>
+        <v>165.94</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>200</v>
+        <v>8400</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>11600</v>
+        <v>165</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>ULTRACEMCO_CM | ULTRACEMCO_NM</t>
+          <t>UNIONBANK_CM | UNIONBANK_NM</t>
         </is>
       </c>
     </row>
@@ -4759,24 +4759,24 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>165.94</v>
+        <v>641.85</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>8400</v>
+        <v>1300</v>
       </c>
       <c r="E158" s="7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>165</v>
+        <v>650</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>UNIONBANK_CM | UNIONBANK_NM</t>
+          <t>UPL_CM | UPL_NM</t>
         </is>
       </c>
     </row>
@@ -4786,24 +4786,24 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>641.85</v>
+        <v>271.55</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>1300</v>
+        <v>2750</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>650</v>
+        <v>270</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>UPL_CM | UPL_NM</t>
+          <t>VEDL_CM | VEDL_NM</t>
         </is>
       </c>
     </row>
@@ -4813,24 +4813,24 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>271.55</v>
+        <v>1430.4</v>
       </c>
       <c r="D160" s="7" t="n">
-        <v>2750</v>
+        <v>1000</v>
       </c>
       <c r="E160" s="7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>270</v>
+        <v>1425</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>VEDL_CM | VEDL_NM</t>
+          <t>VOLTAS_CM | VOLTAS_NM</t>
         </is>
       </c>
     </row>
@@ -4840,24 +4840,24 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1430.4</v>
+        <v>200.65</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1425</v>
+        <v>200</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>VOLTAS_CM | VOLTAS_NM</t>
+          <t>WIPRO_CM | WIPRO_NM</t>
         </is>
       </c>
     </row>
@@ -4867,49 +4867,22 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>200.65</v>
+        <v>891.9</v>
       </c>
       <c r="D162" s="7" t="n">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="E162" s="7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>WIPRO_CM | WIPRO_NM</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="n">
-        <v>891.9</v>
-      </c>
-      <c r="D163" s="3" t="n">
-        <v>700</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F163" s="6" t="n">
-        <v>900</v>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
         <is>
           <t>ZYDUSLIFE_CM | ZYDUSLIFE_NM</t>
         </is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  01-May-2026 14:19</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  04-May-2026 15:13</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>507.5</v>
+        <v>513.1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7230</v>
+        <v>7236.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25435</v>
+        <v>25415</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>345.5</v>
+        <v>345.85</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>64.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1422.1</v>
+        <v>1398.2</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2408.4</v>
+        <v>2485.7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1657.3</v>
+        <v>1742.6</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5400</v>
+        <v>5360.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>444.2</v>
+        <v>445.3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>308.71</v>
+        <v>307.7</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7636.5</v>
+        <v>7737.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>408.4</v>
+        <v>409.45</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>162.09</v>
+        <v>160.77</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2444.5</v>
+        <v>2448.1</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1529.7</v>
+        <v>1559.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>634.7</v>
+        <v>643.15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1389.5</v>
+        <v>1376</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1015.95</v>
+        <v>1015</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1268.3</v>
+        <v>1275.1</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9994</v>
+        <v>10132</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1747.2</v>
+        <v>1770.4</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>937</v>
+        <v>950.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2160.8</v>
+        <v>2205</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>199.72</v>
+        <v>206.76</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>263.46</v>
+        <v>265.1</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>431.3</v>
+        <v>433.55</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>473.1</v>
+        <v>470.3</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1886.8</v>
+        <v>1827.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1875</v>
+        <v>1825</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>352.41</v>
+        <v>377.05</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>359.65</v>
+        <v>360.6</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>35995</v>
+        <v>35850</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36000</v>
+        <v>35800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>300.45</v>
+        <v>301.7</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5726</v>
+        <v>5792.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5750</v>
+        <v>5800</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>134.65</v>
+        <v>134.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1562.9</v>
+        <v>1639.5</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1575</v>
+        <v>1650</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1309.6</v>
+        <v>1335</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>481.45</v>
+        <v>479.95</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1195.9</v>
+        <v>1151.6</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2096.2</v>
+        <v>2172.9</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2100</v>
+        <v>2175</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>508.85</v>
+        <v>516.35</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>272.36</v>
+        <v>277.95</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5266.4</v>
+        <v>5289</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5250</v>
+        <v>5300</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>441.5</v>
+        <v>445.65</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1736.9</v>
+        <v>1752.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6502.5</v>
+        <v>6619.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11166.5</v>
+        <v>11408</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11200</v>
+        <v>11400</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>587</v>
+        <v>607.2</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1322.9</v>
+        <v>1287.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7109</v>
+        <v>7329</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7100</v>
+        <v>7300</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3241.6</v>
+        <v>3205.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3250</v>
+        <v>3200</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>360.55</v>
+        <v>359.05</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>286.95</v>
+        <v>289.15</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>163.23</v>
+        <v>164.48</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2406.3</v>
+        <v>2393.7</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1067.1</v>
+        <v>1072.5</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1835.2</v>
+        <v>1899.8</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>699.7</v>
+        <v>703.4</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2794.5</v>
+        <v>2856</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>380.05</v>
+        <v>390.25</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4338.8</v>
+        <v>4559.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1240.6</v>
+        <v>1256.6</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1199.1</v>
+        <v>1200.5</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2712.6</v>
+        <v>2753.6</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>771.7</v>
+        <v>779.4</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>586.9</v>
+        <v>588.35</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5099</v>
+        <v>5066.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1038</v>
+        <v>1042.7</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>534.85</v>
+        <v>537.4</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>374.55</v>
+        <v>373.85</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2250.9</v>
+        <v>2309.3</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>69.64</v>
+        <v>69.59</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.19</v>
+        <v>126.97</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>166.02</v>
+        <v>166.91</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>635.85</v>
+        <v>643.7</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2103.6</v>
+        <v>2094.5</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4295.3</v>
+        <v>4262.4</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4300</v>
+        <v>4250</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>916.05</v>
+        <v>913.9</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>409.95</v>
+        <v>400.25</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1181.8</v>
+        <v>1168.4</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>142.25</v>
+        <v>142.26</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>539.55</v>
+        <v>555.25</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>314.9</v>
+        <v>311.1</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1223.1</v>
+        <v>1261.4</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>561.15</v>
+        <v>562.3</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1264.5</v>
+        <v>1266.6</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>478.6</v>
+        <v>476.4</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>383.3</v>
+        <v>371.65</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>759.05</v>
+        <v>768.55</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1367.2</v>
+        <v>1573.4</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1100.95</v>
+        <v>1166.4</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1100</v>
+        <v>1165</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>554.7</v>
+        <v>557</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4014</v>
+        <v>4100.8</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>279.73</v>
+        <v>285.65</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3626.3</v>
+        <v>3706.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2305.2</v>
+        <v>2348.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3097.5</v>
+        <v>3106.5</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>294.35</v>
+        <v>305.15</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>775</v>
+        <v>784.55</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13314</v>
+        <v>13580</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13300</v>
+        <v>13600</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2971.5</v>
+        <v>2912.9</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2975</v>
+        <v>2925</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>476.5</v>
+        <v>492.4</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1585.7</v>
+        <v>1606.7</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1135.65</v>
+        <v>1135.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>121.21</v>
+        <v>120.21</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2276.7</v>
+        <v>2276.6</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>129710</v>
+        <v>129235</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>129500</v>
+        <v>129000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3424.2</v>
+        <v>3487.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3425</v>
+        <v>3500</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>399.3</v>
+        <v>407.8</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>972.85</v>
+        <v>976.65</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6821</v>
+        <v>6796.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1458.6</v>
+        <v>1457.1</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>90.37</v>
+        <v>89.09</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>399.15</v>
+        <v>400.05</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1669.6</v>
+        <v>1693.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9726.5</v>
+        <v>9730</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>299.55</v>
+        <v>292.9</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>36785</v>
+        <v>36955</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4800</v>
+        <v>4788.1</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>276.76</v>
+        <v>276.7</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>448.4</v>
+        <v>448.25</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1375.7</v>
+        <v>1364.6</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3054.8</v>
+        <v>3047.5</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>109.36</v>
+        <v>108.68</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8110.5</v>
+        <v>8344.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>318.35</v>
+        <v>319.05</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>336.55</v>
+        <v>330.2</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>354.3</v>
+        <v>353.5</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1430.8</v>
+        <v>1463.1</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>184.62</v>
+        <v>186.15</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>643.9</v>
+        <v>644.8</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1819</v>
+        <v>1820.1</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1068.45</v>
+        <v>1068.4</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24195</v>
+        <v>24740</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>937.35</v>
+        <v>960.45</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3808.2</v>
+        <v>3834.1</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3800</v>
+        <v>3850</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2518.6</v>
+        <v>2551.4</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2500</v>
+        <v>2550</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1808.3</v>
+        <v>1823.5</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>605.6</v>
+        <v>575.85</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>610</v>
+        <v>580</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>467.65</v>
+        <v>477.35</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>809</v>
+        <v>805.75</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1580.5</v>
+        <v>1569.6</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1144.6</v>
+        <v>1160.4</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1140</v>
+        <v>1160</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>444.55</v>
+        <v>441.4</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>211.36</v>
+        <v>212.24</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2473.9</v>
+        <v>2431.3</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1473.5</v>
+        <v>1471.6</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4385.2</v>
+        <v>4363</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4400</v>
+        <v>4350</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4185.1</v>
+        <v>4251.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4200</v>
+        <v>4250</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1736</v>
+        <v>1724</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4144.6</v>
+        <v>4158.5</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3492.9</v>
+        <v>3495.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1458.6</v>
+        <v>1463.1</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11586</v>
+        <v>11758</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>165.94</v>
+        <v>163.77</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>641.85</v>
+        <v>643.35</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>271.55</v>
+        <v>294.65</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1430.4</v>
+        <v>1454.2</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>200.65</v>
+        <v>200.75</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>891.9</v>
+        <v>902.35</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  04-May-2026 15:13</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  05-May-2026 18:29</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>513.1</v>
+        <v>488</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7236.5</v>
+        <v>7328</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7250</v>
+        <v>7350</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25415</v>
+        <v>25305</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>345.85</v>
+        <v>360.85</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>65.93000000000001</v>
+        <v>63.99</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1398.2</v>
+        <v>1392.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2485.7</v>
+        <v>2462</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1742.6</v>
+        <v>1725</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5360.5</v>
+        <v>5403</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>445.3</v>
+        <v>433.1</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>307.7</v>
+        <v>314.4</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7737.5</v>
+        <v>7772</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7700</v>
+        <v>7800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>409.45</v>
+        <v>402.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>160.77</v>
+        <v>160.25</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2448.1</v>
+        <v>2430</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1559.6</v>
+        <v>1531.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>643.15</v>
+        <v>647.2</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1376</v>
+        <v>1428.1</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1375</v>
+        <v>1425</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1015</v>
+        <v>1007.1</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1275.1</v>
+        <v>1259.7</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10132</v>
+        <v>10046</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10100</v>
+        <v>10000</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1770.4</v>
+        <v>1794.6</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>950.2</v>
+        <v>958.6</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2205</v>
+        <v>2172</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>206.76</v>
+        <v>206.44</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>265.1</v>
+        <v>263.4</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>433.55</v>
+        <v>433.35</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>470.3</v>
+        <v>470.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1827.1</v>
+        <v>1806.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>377.05</v>
+        <v>374.95</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>360.6</v>
+        <v>368.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>35850</v>
+        <v>35870</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>301.7</v>
+        <v>298.5</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5792.5</v>
+        <v>5834.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5800</v>
+        <v>5850</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>134.8</v>
+        <v>134.31</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1639.5</v>
+        <v>1657.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1335</v>
+        <v>1333.7</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>479.95</v>
+        <v>472.6</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1151.6</v>
+        <v>1168.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2172.9</v>
+        <v>2178.9</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>516.35</v>
+        <v>518.05</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>277.95</v>
+        <v>275.5</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5289</v>
+        <v>5260</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>445.65</v>
+        <v>460.55</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1752.3</v>
+        <v>1771.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6619.5</v>
+        <v>6651</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11408</v>
+        <v>11253</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>607.2</v>
+        <v>597.3</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1287.2</v>
+        <v>1271.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7329</v>
+        <v>7301.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3205.1</v>
+        <v>3207.5</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>359.05</v>
+        <v>361.15</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>289.15</v>
+        <v>292.6</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>164.48</v>
+        <v>163.7</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2393.7</v>
+        <v>2417.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2400</v>
+        <v>2425</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1072.5</v>
+        <v>1101.5</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1899.8</v>
+        <v>1809.5</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>703.4</v>
+        <v>711.8</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2856</v>
+        <v>2871.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2850</v>
+        <v>2875</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>390.25</v>
+        <v>388.25</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4559.5</v>
+        <v>4610.4</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1256.6</v>
+        <v>1239.6</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1200.5</v>
+        <v>1200.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2753.6</v>
+        <v>2806.3</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>779.4</v>
+        <v>772.3</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>588.35</v>
+        <v>594.1</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5066.5</v>
+        <v>5109</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1042.7</v>
+        <v>1054.7</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>537.4</v>
+        <v>532.05</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>373.85</v>
+        <v>373.9</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2309.3</v>
+        <v>2327.4</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>69.59</v>
+        <v>68.75</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>126.97</v>
+        <v>127.62</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>166.91</v>
+        <v>166.24</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>643.7</v>
+        <v>647.8</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2094.5</v>
+        <v>2052.9</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4262.4</v>
+        <v>4238.4</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>913.9</v>
+        <v>910.7</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>400.25</v>
+        <v>402.7</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1168.4</v>
+        <v>1178.1</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>142.26</v>
+        <v>142.14</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>555.25</v>
+        <v>569.1</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>311.1</v>
+        <v>311.45</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1261.4</v>
+        <v>1261.2</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>562.3</v>
+        <v>561.95</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1266.6</v>
+        <v>1252.4</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>476.4</v>
+        <v>465.35</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>371.65</v>
+        <v>371.35</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>768.55</v>
+        <v>772.5</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1573.4</v>
+        <v>1536.7</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1166.4</v>
+        <v>1164.1</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>557</v>
+        <v>558.15</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4100.8</v>
+        <v>4054.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>285.65</v>
+        <v>290.45</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3706.7</v>
+        <v>3739.8</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2348.8</v>
+        <v>2343.3</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3106.5</v>
+        <v>3210.8</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>305.15</v>
+        <v>307.25</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>784.55</v>
+        <v>807.2</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13580</v>
+        <v>13426</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13600</v>
+        <v>13400</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2912.9</v>
+        <v>2902.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2925</v>
+        <v>2900</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>492.4</v>
+        <v>506.3</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1606.7</v>
+        <v>1596.2</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1135.4</v>
+        <v>1133.5</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>120.21</v>
+        <v>120.24</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2276.6</v>
+        <v>2209.8</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>129235</v>
+        <v>128270</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>129000</v>
+        <v>128500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3487.7</v>
+        <v>3446.4</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>407.8</v>
+        <v>413.6</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>976.65</v>
+        <v>963.95</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6796.5</v>
+        <v>7005</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1457.1</v>
+        <v>1477.8</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>89.09</v>
+        <v>88.83</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>400.05</v>
+        <v>398.65</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1693.7</v>
+        <v>1666.3</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9730</v>
+        <v>9707</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>292.9</v>
+        <v>289.95</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>36955</v>
+        <v>37400</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>37000</v>
+        <v>37500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4788.1</v>
+        <v>4816.3</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>276.7</v>
+        <v>282.55</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>448.25</v>
+        <v>456.9</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1364.6</v>
+        <v>1364.2</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3047.5</v>
+        <v>3014.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>3050</v>
+        <v>3000</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>108.68</v>
+        <v>107.89</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8344.5</v>
+        <v>8337</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>319.05</v>
+        <v>319.45</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>330.2</v>
+        <v>332.95</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>353.5</v>
+        <v>356.4</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1463.1</v>
+        <v>1463.6</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>186.15</v>
+        <v>187.31</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>644.8</v>
+        <v>645.65</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1820.1</v>
+        <v>1821.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1068.4</v>
+        <v>1059.9</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24740</v>
+        <v>24845</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24500</v>
+        <v>25000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>960.45</v>
+        <v>964.4</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3834.1</v>
+        <v>3846.6</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2551.4</v>
+        <v>2522.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1823.5</v>
+        <v>1820.8</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>575.85</v>
+        <v>580.1</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>477.35</v>
+        <v>451.4</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>805.75</v>
+        <v>801.45</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1569.6</v>
+        <v>1559</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1160.4</v>
+        <v>1153.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1160</v>
+        <v>1150</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>441.4</v>
+        <v>442.65</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>212.24</v>
+        <v>211.32</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2431.3</v>
+        <v>2427.3</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1471.6</v>
+        <v>1452.2</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4363</v>
+        <v>4373.6</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4251.8</v>
+        <v>4275.1</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4250</v>
+        <v>4300</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1724</v>
+        <v>1734.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4158.5</v>
+        <v>4135.4</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3495.5</v>
+        <v>3534.4</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3500</v>
+        <v>3525</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1463.1</v>
+        <v>1453.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11758</v>
+        <v>11963</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11800</v>
+        <v>12000</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>163.77</v>
+        <v>163.74</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>643.35</v>
+        <v>642.05</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>294.65</v>
+        <v>303.9</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1454.2</v>
+        <v>1375.9</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1450</v>
+        <v>1375</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>200.75</v>
+        <v>199.78</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>902.35</v>
+        <v>912.25</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  05-May-2026 18:29</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  06-May-2026 14:48</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>488</v>
+        <v>497.85</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7328</v>
+        <v>7182.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7350</v>
+        <v>7200</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25305</v>
+        <v>26300</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25400</v>
+        <v>26400</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>360.85</v>
+        <v>369.3</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63.99</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1392.6</v>
+        <v>1414</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1400</v>
+        <v>1425</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2462</v>
+        <v>2540.3</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2450</v>
+        <v>2550</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1725</v>
+        <v>1748.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5403</v>
+        <v>5557</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>433.1</v>
+        <v>446.9</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>314.4</v>
+        <v>316.85</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7772</v>
+        <v>7760.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>402.6</v>
+        <v>412.65</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>160.25</v>
+        <v>167.8</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2430</v>
+        <v>2519</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1531.6</v>
+        <v>1576.1</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1575</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>647.2</v>
+        <v>651</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1428.1</v>
+        <v>1484</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1425</v>
+        <v>1475</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1007.1</v>
+        <v>1024</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1259.7</v>
+        <v>1294.2</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10046</v>
+        <v>10319</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10000</v>
+        <v>10300</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1794.6</v>
+        <v>1836.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>958.6</v>
+        <v>980.75</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2172</v>
+        <v>2230.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>206.44</v>
+        <v>208.88</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>263.4</v>
+        <v>270.3</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>433.35</v>
+        <v>438.2</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>470.6</v>
+        <v>478.45</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1806.1</v>
+        <v>1833.7</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>374.95</v>
+        <v>385.95</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>368.25</v>
+        <v>380.6</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>35870</v>
+        <v>36645</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>35800</v>
+        <v>36600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>298.5</v>
+        <v>314.05</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5834.5</v>
+        <v>5783</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5850</v>
+        <v>5800</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>134.31</v>
+        <v>138.04</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1657.4</v>
+        <v>1711.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1333.7</v>
+        <v>1364.4</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1325</v>
+        <v>1375</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>472.6</v>
+        <v>470.2</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1168.8</v>
+        <v>1280.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2178.9</v>
+        <v>2157.1</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2175</v>
+        <v>2150</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>518.05</v>
+        <v>524.2</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>275.5</v>
+        <v>284.05</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5260</v>
+        <v>5324.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5250</v>
+        <v>5300</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>460.55</v>
+        <v>466.25</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1771.3</v>
+        <v>1821.6</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6651</v>
+        <v>6702</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11253</v>
+        <v>11299</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>597.3</v>
+        <v>609.6</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1271.2</v>
+        <v>1311</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7301.5</v>
+        <v>7310.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3207.5</v>
+        <v>3317.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>361.15</v>
+        <v>351.7</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>292.6</v>
+        <v>293</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>163.7</v>
+        <v>165.68</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2417.9</v>
+        <v>2377.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2425</v>
+        <v>2375</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1101.5</v>
+        <v>1094.1</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1809.5</v>
+        <v>1867.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>711.8</v>
+        <v>736</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2871.5</v>
+        <v>2914.8</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2875</v>
+        <v>2925</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>388.25</v>
+        <v>397.55</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4610.4</v>
+        <v>4626.9</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1239.6</v>
+        <v>1257.3</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1200.2</v>
+        <v>1189.1</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2806.3</v>
+        <v>2815.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>772.3</v>
+        <v>796.55</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>594.1</v>
+        <v>606.35</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5109</v>
+        <v>5170</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5100</v>
+        <v>5150</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1054.7</v>
+        <v>1045.8</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>532.05</v>
+        <v>550.5</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>373.9</v>
+        <v>399.2</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2327.4</v>
+        <v>2317.1</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>68.75</v>
+        <v>69.59</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>127.62</v>
+        <v>129.8</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>166.24</v>
+        <v>169.46</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>647.8</v>
+        <v>666.15</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2052.9</v>
+        <v>2056.9</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4238.4</v>
+        <v>4520.2</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4250</v>
+        <v>4500</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>910.7</v>
+        <v>946.75</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>402.7</v>
+        <v>408.3</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1178.1</v>
+        <v>1167.2</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>142.14</v>
+        <v>148.21</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>569.1</v>
+        <v>572.75</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>311.45</v>
+        <v>310.7</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1261.2</v>
+        <v>1264.3</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>561.95</v>
+        <v>567.9</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1252.4</v>
+        <v>1273.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>465.35</v>
+        <v>471.25</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>371.35</v>
+        <v>376.6</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>772.5</v>
+        <v>748.6</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1536.7</v>
+        <v>1586.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1164.1</v>
+        <v>1177.6</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1165</v>
+        <v>1180</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>558.15</v>
+        <v>582.15</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4054.5</v>
+        <v>4008.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4000</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>290.45</v>
+        <v>300.3</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3739.8</v>
+        <v>3804.8</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2343.3</v>
+        <v>2442.9</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2350</v>
+        <v>2450</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3210.8</v>
+        <v>3300.8</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>307.25</v>
+        <v>309.95</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>807.2</v>
+        <v>814.8</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13426</v>
+        <v>13722</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13400</v>
+        <v>13700</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2902.5</v>
+        <v>2973.2</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2900</v>
+        <v>2975</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>506.3</v>
+        <v>506.4</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1596.2</v>
+        <v>1652.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1133.5</v>
+        <v>1166.8</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1125</v>
+        <v>1175</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>120.24</v>
+        <v>127.41</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2209.8</v>
+        <v>2218.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>128270</v>
+        <v>130335</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>128500</v>
+        <v>130500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3446.4</v>
+        <v>3533.6</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3450</v>
+        <v>3525</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>413.6</v>
+        <v>406.55</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>963.95</v>
+        <v>981.4</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7005</v>
+        <v>7043</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1477.8</v>
+        <v>1486.1</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.83</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>398.65</v>
+        <v>394.85</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1666.3</v>
+        <v>1673.4</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9707</v>
+        <v>9694.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>289.95</v>
+        <v>280.8</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37400</v>
+        <v>37540</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4816.3</v>
+        <v>5014</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>282.55</v>
+        <v>283.3</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>456.9</v>
+        <v>463.9</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1364.2</v>
+        <v>1421.5</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3014.3</v>
+        <v>3071</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>107.89</v>
+        <v>110.18</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8337</v>
+        <v>8415.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>319.45</v>
+        <v>315.95</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>332.95</v>
+        <v>335.85</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>356.4</v>
+        <v>359.1</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1463.6</v>
+        <v>1437.9</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>187.31</v>
+        <v>186.04</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>645.65</v>
+        <v>649.65</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1821.2</v>
+        <v>1859</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1059.9</v>
+        <v>1096</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24845</v>
+        <v>24975</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>964.4</v>
+        <v>1004.1</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3846.6</v>
+        <v>3841.8</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2522.8</v>
+        <v>2719.6</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1820.8</v>
+        <v>1850.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>580.1</v>
+        <v>570.75</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>451.4</v>
+        <v>450.1</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>801.45</v>
+        <v>815.95</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1559</v>
+        <v>1591</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1153.5</v>
+        <v>1152.2</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>442.65</v>
+        <v>443.25</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>211.32</v>
+        <v>215.47</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2427.3</v>
+        <v>2435.4</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1452.2</v>
+        <v>1466.7</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4373.6</v>
+        <v>4359.6</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4275.1</v>
+        <v>4358.3</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4300</v>
+        <v>4350</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1734.7</v>
+        <v>1734</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4135.4</v>
+        <v>4289.8</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4150</v>
+        <v>4300</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3534.4</v>
+        <v>3617.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3525</v>
+        <v>3625</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1453.8</v>
+        <v>1412.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11963</v>
+        <v>12093</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12000</v>
+        <v>12100</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>163.74</v>
+        <v>168.75</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>642.05</v>
+        <v>660</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>303.9</v>
+        <v>316.4</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1375.9</v>
+        <v>1379.6</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>199.78</v>
+        <v>199.12</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>912.25</v>
+        <v>938.8</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  06-May-2026 14:48</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  06-May-2026 15:29</t>
         </is>
       </c>
     </row>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  06-May-2026 15:29</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  07-May-2026 15:31</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>497.85</v>
+        <v>488.15</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7182.5</v>
+        <v>7188</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26300</v>
+        <v>26700</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26400</v>
+        <v>26800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>369.3</v>
+        <v>369</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>66.20999999999999</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1414</v>
+        <v>1414.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2540.3</v>
+        <v>2513.7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1748.3</v>
+        <v>1732.8</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5557</v>
+        <v>5590.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>446.9</v>
+        <v>450.65</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>316.85</v>
+        <v>322.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7760.5</v>
+        <v>7837</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>412.65</v>
+        <v>410.05</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>167.8</v>
+        <v>170.78</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2519</v>
+        <v>2530.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2500</v>
+        <v>2550</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1576.1</v>
+        <v>1569.1</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>651</v>
+        <v>644.25</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1484</v>
+        <v>1478.7</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1024</v>
+        <v>1032.4</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1294.2</v>
+        <v>1292.7</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10319</v>
+        <v>10605</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10300</v>
+        <v>10600</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1836.1</v>
+        <v>1824.5</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>980.75</v>
+        <v>972.75</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2230.3</v>
+        <v>2258.4</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>208.88</v>
+        <v>207.63</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>270.3</v>
+        <v>270.35</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>438.2</v>
+        <v>439.45</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>478.45</v>
+        <v>488.25</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1833.7</v>
+        <v>1826.6</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>385.95</v>
+        <v>406.45</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>380.6</v>
+        <v>382.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36645</v>
+        <v>37895</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36600</v>
+        <v>37800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>314.05</v>
+        <v>307.6</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5783</v>
+        <v>5814</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>138.04</v>
+        <v>135.93</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1711.9</v>
+        <v>1689.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1364.4</v>
+        <v>1362.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>470.2</v>
+        <v>466.65</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1280.4</v>
+        <v>1285.3</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2157.1</v>
+        <v>2167</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2150</v>
+        <v>2175</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>524.2</v>
+        <v>526.7</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>284.05</v>
+        <v>290.75</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5324.5</v>
+        <v>5403</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>466.25</v>
+        <v>470</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1821.6</v>
+        <v>1854.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6702</v>
+        <v>6702.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11299</v>
+        <v>11048</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11300</v>
+        <v>11000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>609.6</v>
+        <v>618.85</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1311</v>
+        <v>1307.6</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7310.5</v>
+        <v>7327.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3317.1</v>
+        <v>3345.9</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3300</v>
+        <v>3350</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>351.7</v>
+        <v>364.45</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>293</v>
+        <v>297.05</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>165.68</v>
+        <v>167.26</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2377.6</v>
+        <v>2371.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1094.1</v>
+        <v>1036.6</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1100</v>
+        <v>1025</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1867.2</v>
+        <v>1878.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>736</v>
+        <v>743.5</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2914.8</v>
+        <v>2960.6</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2925</v>
+        <v>2950</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>397.55</v>
+        <v>408.95</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4626.9</v>
+        <v>4782.1</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1257.3</v>
+        <v>1268.9</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1189.1</v>
+        <v>1183.4</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2815.9</v>
+        <v>2834.6</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>796.55</v>
+        <v>796.05</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>606.35</v>
+        <v>625.4</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5170</v>
+        <v>5343</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5150</v>
+        <v>5350</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1045.8</v>
+        <v>1055.7</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>550.5</v>
+        <v>568.6</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>399.2</v>
+        <v>396.5</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2317.1</v>
+        <v>2272.2</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>69.59</v>
+        <v>70.39</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>129.8</v>
+        <v>133.81</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>169.46</v>
+        <v>169.84</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>666.15</v>
+        <v>669.1</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2056.9</v>
+        <v>2091</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4520.2</v>
+        <v>4506.9</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>946.75</v>
+        <v>946.95</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>408.3</v>
+        <v>402.9</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1167.2</v>
+        <v>1162.7</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>148.21</v>
+        <v>146.89</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>572.75</v>
+        <v>568.5</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>310.7</v>
+        <v>307.4</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1264.3</v>
+        <v>1258.2</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>567.9</v>
+        <v>575.9</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1273.3</v>
+        <v>1283.4</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>471.25</v>
+        <v>479</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>376.6</v>
+        <v>379.4</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>748.6</v>
+        <v>722.65</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1586.2</v>
+        <v>1565.5</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1177.6</v>
+        <v>1206.5</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1180</v>
+        <v>1205</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>582.15</v>
+        <v>586.35</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4008.5</v>
+        <v>4023</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>300.3</v>
+        <v>303.65</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3804.8</v>
+        <v>3772.9</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2442.9</v>
+        <v>2460.1</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3300.8</v>
+        <v>3370.7</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3300</v>
+        <v>3350</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>309.95</v>
+        <v>316.3</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>814.8</v>
+        <v>832.15</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13722</v>
+        <v>13770</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13700</v>
+        <v>13800</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2973.2</v>
+        <v>3042.6</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2975</v>
+        <v>3050</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>506.4</v>
+        <v>505.6</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1652.8</v>
+        <v>1707.4</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1166.8</v>
+        <v>1179.8</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>127.41</v>
+        <v>130.43</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2218.5</v>
+        <v>2193.1</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>130335</v>
+        <v>129965</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>130500</v>
+        <v>130000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3533.6</v>
+        <v>3584.3</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3525</v>
+        <v>3575</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>406.55</v>
+        <v>403.5</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>981.4</v>
+        <v>981.85</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7043</v>
+        <v>7085</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1486.1</v>
+        <v>1476</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>89.18000000000001</v>
+        <v>90.14</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>394.85</v>
+        <v>400.35</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1673.4</v>
+        <v>1675</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9694.5</v>
+        <v>9498.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>280.8</v>
+        <v>283.9</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37540</v>
+        <v>37345</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5014</v>
+        <v>4984</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>283.3</v>
+        <v>282.1</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>463.9</v>
+        <v>457.55</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1421.5</v>
+        <v>1450.4</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3071</v>
+        <v>3101.5</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>110.18</v>
+        <v>109.11</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8415.5</v>
+        <v>9003</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>8400</v>
+        <v>9000</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>315.95</v>
+        <v>313.8</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>335.85</v>
+        <v>345.75</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>359.1</v>
+        <v>359.75</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1437.9</v>
+        <v>1436.2</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>186.04</v>
+        <v>187.28</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>649.65</v>
+        <v>648.15</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1859</v>
+        <v>1872.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24975</v>
+        <v>25595</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1004.1</v>
+        <v>1015.65</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3841.8</v>
+        <v>3871.5</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2719.6</v>
+        <v>2771.3</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1850.2</v>
+        <v>1834.4</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>570.75</v>
+        <v>571.1</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>450.1</v>
+        <v>467.35</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>815.95</v>
+        <v>805.35</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1591</v>
+        <v>1593.5</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1152.2</v>
+        <v>1151.7</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>443.25</v>
+        <v>439.25</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>215.47</v>
+        <v>217.09</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2435.4</v>
+        <v>2401.4</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1466.7</v>
+        <v>1448.2</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4359.6</v>
+        <v>4307.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4350</v>
+        <v>4300</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4358.3</v>
+        <v>4362.7</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1734</v>
+        <v>1712.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4289.8</v>
+        <v>4294.1</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3617.9</v>
+        <v>3706.7</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3625</v>
+        <v>3700</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1412.8</v>
+        <v>1428.2</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>12093</v>
+        <v>12146</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>168.75</v>
+        <v>167.28</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>660</v>
+        <v>650.45</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>316.4</v>
+        <v>305.4</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1379.6</v>
+        <v>1363.9</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>199.12</v>
+        <v>197.36</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>938.8</v>
+        <v>940.3</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  07-May-2026 15:31</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  08-May-2026 14:55</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>488.15</v>
+        <v>485.45</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7188</v>
+        <v>7012.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7200</v>
+        <v>7000</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>369</v>
+        <v>362.95</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>67.79000000000001</v>
+        <v>66.33</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1414.6</v>
+        <v>1391.9</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2513.7</v>
+        <v>2505.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1732.8</v>
+        <v>1760.4</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5590.5</v>
+        <v>5585.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>450.65</v>
+        <v>444.3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>322.6</v>
+        <v>326</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -857,7 +857,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>7837</v>
+        <v>8097</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>410.05</v>
+        <v>409.25</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>170.78</v>
+        <v>168.57</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2530.6</v>
+        <v>2599.9</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2550</v>
+        <v>2600</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1569.1</v>
+        <v>1569.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>644.25</v>
+        <v>633.05</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1478.7</v>
+        <v>1487.3</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1032.4</v>
+        <v>1050.4</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1292.7</v>
+        <v>1268.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10605</v>
+        <v>10711.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1824.5</v>
+        <v>1818.3</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>972.75</v>
+        <v>955.35</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2258.4</v>
+        <v>2262.5</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>207.63</v>
+        <v>206.11</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>270.35</v>
+        <v>263.9</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>439.45</v>
+        <v>439.7</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>488.25</v>
+        <v>515.75</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1826.6</v>
+        <v>1834.5</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>406.45</v>
+        <v>404.6</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>382.25</v>
+        <v>380.4</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37895</v>
+        <v>38145</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37800</v>
+        <v>38200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>307.6</v>
+        <v>302.75</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5814</v>
+        <v>5520</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5800</v>
+        <v>5500</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>135.93</v>
+        <v>134.34</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1689.2</v>
+        <v>1674.1</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1362.3</v>
+        <v>1347</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>466.65</v>
+        <v>456.4</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1285.3</v>
+        <v>1368.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2167</v>
+        <v>2197.4</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2175</v>
+        <v>2200</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>526.7</v>
+        <v>534.75</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>290.75</v>
+        <v>293.3</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5403</v>
+        <v>5401</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>470</v>
+        <v>487.7</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1854.4</v>
+        <v>1875.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6702.5</v>
+        <v>6710.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11048</v>
+        <v>10803</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11000</v>
+        <v>10800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>618.85</v>
+        <v>608.25</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1307.6</v>
+        <v>1293.9</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7327.5</v>
+        <v>7302.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3345.9</v>
+        <v>3146.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3350</v>
+        <v>3150</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>364.45</v>
+        <v>362.25</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>297.05</v>
+        <v>297.25</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>167.26</v>
+        <v>166.49</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2371.6</v>
+        <v>2366.4</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1036.6</v>
+        <v>1042.4</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1878.6</v>
+        <v>1873.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1900</v>
+        <v>1850</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>743.5</v>
+        <v>752.95</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2960.6</v>
+        <v>2968.6</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2950</v>
+        <v>2975</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>408.95</v>
+        <v>396.45</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4782.1</v>
+        <v>4788.1</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1268.9</v>
+        <v>1255.2</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1183.4</v>
+        <v>1198.4</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2834.6</v>
+        <v>2854</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>796.05</v>
+        <v>780.85</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>625.4</v>
+        <v>621.7</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5343</v>
+        <v>5322</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5350</v>
+        <v>5300</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1055.7</v>
+        <v>1044.4</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>568.6</v>
+        <v>569.2</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>396.5</v>
+        <v>387</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2272.2</v>
+        <v>2287.7</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>70.39</v>
+        <v>71.27</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>133.81</v>
+        <v>134.12</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>169.84</v>
+        <v>165.99</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>669.1</v>
+        <v>673.05</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2091</v>
+        <v>2091.8</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4506.9</v>
+        <v>4522.7</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>946.95</v>
+        <v>950.75</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>402.9</v>
+        <v>404.3</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1162.7</v>
+        <v>1179.2</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>146.89</v>
+        <v>144.69</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>568.5</v>
+        <v>564.9</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>307.4</v>
+        <v>307.45</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1258.2</v>
+        <v>1248.4</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>575.9</v>
+        <v>571.2</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1283.4</v>
+        <v>1277.8</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>479</v>
+        <v>473.3</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>379.4</v>
+        <v>380.8</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>722.65</v>
+        <v>729.15</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1565.5</v>
+        <v>1649.8</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1206.5</v>
+        <v>1228.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1205</v>
+        <v>1230</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>586.35</v>
+        <v>581.5</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4023</v>
+        <v>3974.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>303.65</v>
+        <v>303.4</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3772.9</v>
+        <v>3802.6</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2460.1</v>
+        <v>2379.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2450</v>
+        <v>2375</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3370.7</v>
+        <v>3330.4</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>316.3</v>
+        <v>316</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>832.15</v>
+        <v>831.3</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13770</v>
+        <v>13726</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13800</v>
+        <v>13700</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3042.6</v>
+        <v>3097.8</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>505.6</v>
+        <v>549.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1707.4</v>
+        <v>1699.7</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1179.8</v>
+        <v>1172.9</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>130.43</v>
+        <v>132.03</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2193.1</v>
+        <v>2214.2</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>129965</v>
+        <v>130425</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>130000</v>
+        <v>130500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3584.3</v>
+        <v>3528.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3575</v>
+        <v>3525</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>403.5</v>
+        <v>401.95</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>981.85</v>
+        <v>978.35</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7085</v>
+        <v>7041.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1476</v>
+        <v>1482.4</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>90.14</v>
+        <v>88.8</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>400.35</v>
+        <v>402.15</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1675</v>
+        <v>1703</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9498.5</v>
+        <v>9345.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9500</v>
+        <v>9300</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>283.9</v>
+        <v>279.2</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37345</v>
+        <v>37365</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4984</v>
+        <v>5113.6</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>282.1</v>
+        <v>283.8</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>457.55</v>
+        <v>461.35</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1450.4</v>
+        <v>1476</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3101.5</v>
+        <v>3110.8</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>109.11</v>
+        <v>107.24</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9003</v>
+        <v>9083</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>313.8</v>
+        <v>313.95</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>345.75</v>
+        <v>343.45</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>359.75</v>
+        <v>359.4</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1436.2</v>
+        <v>1435.2</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>187.28</v>
+        <v>184.88</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>648.15</v>
+        <v>645.4</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1872.2</v>
+        <v>1872.1</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1092</v>
+        <v>1019.3</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1090</v>
+        <v>1020</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25595</v>
+        <v>25435</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1015.65</v>
+        <v>1007.75</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3871.5</v>
+        <v>3822.6</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3850</v>
+        <v>3800</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2771.3</v>
+        <v>2780.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1834.4</v>
+        <v>1847.9</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>571.1</v>
+        <v>573.55</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>467.35</v>
+        <v>458.1</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>805.35</v>
+        <v>781.55</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1593.5</v>
+        <v>1592.3</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1151.7</v>
+        <v>1176.2</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>439.25</v>
+        <v>436</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>217.09</v>
+        <v>214.49</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2401.4</v>
+        <v>2394.4</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1448.2</v>
+        <v>1463</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4307.5</v>
+        <v>4509</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4300</v>
+        <v>4500</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4362.7</v>
+        <v>4380.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4350</v>
+        <v>4400</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1712.5</v>
+        <v>1724.4</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4294.1</v>
+        <v>4242.3</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4300</v>
+        <v>4250</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3706.7</v>
+        <v>3695.2</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1428.2</v>
+        <v>1419.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>12146</v>
+        <v>11950</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12100</v>
+        <v>12000</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>167.28</v>
+        <v>166.24</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>650.45</v>
+        <v>646</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>305.4</v>
+        <v>296.45</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1363.9</v>
+        <v>1324.8</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1375</v>
+        <v>1325</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>197.36</v>
+        <v>197.91</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>940.3</v>
+        <v>940.05</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  08-May-2026 14:55</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  11-May-2026 15:59</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>485.45</v>
+        <v>487.45</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7012.5</v>
+        <v>6387.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26700</v>
+        <v>27795</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26800</v>
+        <v>27800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>362.95</v>
+        <v>352.95</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>66.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1391.9</v>
+        <v>1357.9</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2505.9</v>
+        <v>2500.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1760.4</v>
+        <v>1767.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5585.5</v>
+        <v>5599.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>444.3</v>
+        <v>436.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>326</v>
+        <v>317.2</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -857,7 +857,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8097</v>
+        <v>8082</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>409.25</v>
+        <v>405.7</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>168.57</v>
+        <v>161.52</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2599.9</v>
+        <v>2566.1</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1569.8</v>
+        <v>1572.1</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>633.05</v>
+        <v>620.5</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1487.3</v>
+        <v>1486.6</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1050.4</v>
+        <v>1021.4</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1268.3</v>
+        <v>1272.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10711.5</v>
+        <v>10595.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10700</v>
+        <v>10600</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1818.3</v>
+        <v>1794.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>955.35</v>
+        <v>936.05</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2262.5</v>
+        <v>2181.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>206.11</v>
+        <v>201.23</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>263.9</v>
+        <v>266</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>439.7</v>
+        <v>431.95</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>515.75</v>
+        <v>493.85</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1834.5</v>
+        <v>1759.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1750</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>404.6</v>
+        <v>401.35</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>380.4</v>
+        <v>390.45</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>38145</v>
+        <v>37315</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>38200</v>
+        <v>37400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>302.75</v>
+        <v>294.45</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5520</v>
+        <v>5410.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>134.34</v>
+        <v>129.43</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1674.1</v>
+        <v>1624.5</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1675</v>
+        <v>1625</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1347</v>
+        <v>1304.9</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>456.4</v>
+        <v>464.45</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1368.1</v>
+        <v>1375.2</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2197.4</v>
+        <v>2139</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>534.75</v>
+        <v>530</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>293.3</v>
+        <v>290.2</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5401</v>
+        <v>5238.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5400</v>
+        <v>5250</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>487.7</v>
+        <v>473.45</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1875.9</v>
+        <v>1863.6</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1900</v>
+        <v>1850</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6710.5</v>
+        <v>6714</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10803</v>
+        <v>10772</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>608.25</v>
+        <v>590.25</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1293.9</v>
+        <v>1279.9</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7302.5</v>
+        <v>7202.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7300</v>
+        <v>7200</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3146.6</v>
+        <v>2966.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3150</v>
+        <v>2950</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>362.25</v>
+        <v>352.7</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>297.25</v>
+        <v>292.45</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>166.49</v>
+        <v>162.51</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2366.4</v>
+        <v>2347.3</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2375</v>
+        <v>2350</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1042.4</v>
+        <v>1010.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1873.6</v>
+        <v>1794.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>752.95</v>
+        <v>755.6</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2968.6</v>
+        <v>2984.2</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>396.45</v>
+        <v>380.95</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4788.1</v>
+        <v>4756.3</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1255.2</v>
+        <v>1230</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1198.4</v>
+        <v>1194.9</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2854</v>
+        <v>2747.2</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2900</v>
+        <v>2700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>780.85</v>
+        <v>763.65</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>621.7</v>
+        <v>622.7</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5322</v>
+        <v>5228.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1044.4</v>
+        <v>1023.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>569.2</v>
+        <v>572.9</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>387</v>
+        <v>377.8</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2287.7</v>
+        <v>2307.2</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>71.27</v>
+        <v>69.22</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>134.12</v>
+        <v>130.71</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>165.99</v>
+        <v>160.69</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>673.05</v>
+        <v>661.3</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2091.8</v>
+        <v>2065</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4522.7</v>
+        <v>4299.4</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4500</v>
+        <v>4300</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>950.75</v>
+        <v>922.3</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>404.3</v>
+        <v>410.65</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1179.2</v>
+        <v>1177</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>144.69</v>
+        <v>140.37</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>564.9</v>
+        <v>556.8</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>307.45</v>
+        <v>305.85</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1248.4</v>
+        <v>1232</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>571.2</v>
+        <v>556.65</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1277.8</v>
+        <v>1262.6</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>473.3</v>
+        <v>460.5</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>380.8</v>
+        <v>381.05</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>729.15</v>
+        <v>733.45</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1649.8</v>
+        <v>1652.4</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1228.3</v>
+        <v>1266.8</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1230</v>
+        <v>1265</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>581.5</v>
+        <v>585.6</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3974.5</v>
+        <v>3940.2</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>303.4</v>
+        <v>295</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3802.6</v>
+        <v>3788.4</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2379.5</v>
+        <v>2255.9</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2375</v>
+        <v>2250</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3330.4</v>
+        <v>3245.9</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3350</v>
+        <v>3250</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>316</v>
+        <v>305.45</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>831.3</v>
+        <v>842.55</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13726</v>
+        <v>13483</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13700</v>
+        <v>13500</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3097.8</v>
+        <v>3187.9</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>549.5</v>
+        <v>559.9</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1699.7</v>
+        <v>1695.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1172.9</v>
+        <v>1106.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1175</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>132.03</v>
+        <v>130.3</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2214.2</v>
+        <v>2201.2</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>130425</v>
+        <v>128910</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>130500</v>
+        <v>129000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3528.9</v>
+        <v>3438.2</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3525</v>
+        <v>3450</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>401.95</v>
+        <v>393.05</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>978.35</v>
+        <v>961.2</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7041.5</v>
+        <v>7071.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1482.4</v>
+        <v>1481.9</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.8</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3611,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>402.15</v>
+        <v>392.95</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1703</v>
+        <v>1634.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1700</v>
+        <v>1625</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9345.5</v>
+        <v>9239.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9300</v>
+        <v>9200</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>279.2</v>
+        <v>281</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37365</v>
+        <v>36245</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>37500</v>
+        <v>36000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5113.6</v>
+        <v>5098.1</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>283.8</v>
+        <v>275.75</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>461.35</v>
+        <v>448.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1476</v>
+        <v>1437.2</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3110.8</v>
+        <v>3090.8</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>107.24</v>
+        <v>104.62</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9083</v>
+        <v>9065.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>313.95</v>
+        <v>310.9</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>343.45</v>
+        <v>337.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>359.4</v>
+        <v>351.55</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1435.2</v>
+        <v>1388.2</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>184.88</v>
+        <v>180.72</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>645.4</v>
+        <v>641.5</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1872.1</v>
+        <v>1884.4</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1019.3</v>
+        <v>973.6</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1020</v>
+        <v>970</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25435</v>
+        <v>25205</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25500</v>
+        <v>25000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1007.75</v>
+        <v>975.95</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3822.6</v>
+        <v>3605.6</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2780.8</v>
+        <v>2798.5</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1847.9</v>
+        <v>1872.7</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>573.55</v>
+        <v>567.75</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>458.1</v>
+        <v>482.5</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>781.55</v>
+        <v>761.35</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1592.3</v>
+        <v>1571.5</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1176.2</v>
+        <v>1271</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1180</v>
+        <v>1270</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>436</v>
+        <v>433.2</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>214.49</v>
+        <v>212.08</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2394.4</v>
+        <v>2392.9</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1463</v>
+        <v>1457.4</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4509</v>
+        <v>4205.6</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4380.8</v>
+        <v>4517.1</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1724.4</v>
+        <v>1680.9</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1725</v>
+        <v>1675</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4242.3</v>
+        <v>4181.1</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4250</v>
+        <v>4200</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3695.2</v>
+        <v>3613.7</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3700</v>
+        <v>3625</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1419.8</v>
+        <v>1412.2</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11950</v>
+        <v>11866</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>166.24</v>
+        <v>163.81</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>296.45</v>
+        <v>298.4</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1324.8</v>
+        <v>1306.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>197.91</v>
+        <v>196.68</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>940.05</v>
+        <v>956.95</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  11-May-2026 15:59</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  12-May-2026 15:42</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>487.45</v>
+        <v>468.5</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6387.5</v>
+        <v>6328.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6400</v>
+        <v>6350</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27795</v>
+        <v>26900</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27800</v>
+        <v>26800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>352.95</v>
+        <v>341.2</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>64.98999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1357.9</v>
+        <v>1347</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2500.2</v>
+        <v>2405.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1767.3</v>
+        <v>1688.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1775</v>
+        <v>1700</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5599.5</v>
+        <v>5496.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>436.2</v>
+        <v>426.95</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>317.2</v>
+        <v>299.1</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8082</v>
+        <v>8022.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>405.7</v>
+        <v>398.75</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>161.52</v>
+        <v>155.95</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2566.1</v>
+        <v>2505.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1572.1</v>
+        <v>1527.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1575</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>620.5</v>
+        <v>591.3</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1486.6</v>
+        <v>1488.2</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1475</v>
+        <v>1500</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1021.4</v>
+        <v>999.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1272.3</v>
+        <v>1260.1</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10595.5</v>
+        <v>10397</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10600</v>
+        <v>10400</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1794.2</v>
+        <v>1744.8</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>936.05</v>
+        <v>904.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2181.9</v>
+        <v>2110.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>201.23</v>
+        <v>196.07</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>266</v>
+        <v>259.95</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>431.95</v>
+        <v>416.5</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>493.85</v>
+        <v>488.1</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1759.8</v>
+        <v>1756.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>401.35</v>
+        <v>391.75</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>390.45</v>
+        <v>402.45</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37315</v>
+        <v>36510</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37400</v>
+        <v>36600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>294.45</v>
+        <v>287.85</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5410.5</v>
+        <v>5334</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5400</v>
+        <v>5350</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>129.43</v>
+        <v>130.01</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1624.5</v>
+        <v>1561</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1625</v>
+        <v>1550</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1304.9</v>
+        <v>1292.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>464.45</v>
+        <v>463.05</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1375.2</v>
+        <v>1320.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2139</v>
+        <v>2125.2</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2150</v>
+        <v>2125</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>290.2</v>
+        <v>282.05</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5238.5</v>
+        <v>5160</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5250</v>
+        <v>5150</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>473.45</v>
+        <v>473.25</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1863.6</v>
+        <v>1848.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6714</v>
+        <v>6644</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10772</v>
+        <v>10138</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>10800</v>
+        <v>10100</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>590.25</v>
+        <v>569.2</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1279.9</v>
+        <v>1270</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7202.5</v>
+        <v>7126</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2966.7</v>
+        <v>2960.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>352.7</v>
+        <v>346.3</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>292.45</v>
+        <v>284.8</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>162.51</v>
+        <v>160.35</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2347.3</v>
+        <v>2257.1</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2350</v>
+        <v>2250</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1010.9</v>
+        <v>1030.2</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1794.3</v>
+        <v>1712.4</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>755.6</v>
+        <v>729.05</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2984.2</v>
+        <v>2903</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2975</v>
+        <v>2900</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>380.95</v>
+        <v>368.25</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4756.3</v>
+        <v>4572.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4800</v>
+        <v>4600</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1230</v>
+        <v>1190.9</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1194.9</v>
+        <v>1145.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2747.2</v>
+        <v>2632.8</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>763.65</v>
+        <v>750.45</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>622.7</v>
+        <v>601.8</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5228.5</v>
+        <v>5082.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5250</v>
+        <v>5100</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1023.5</v>
+        <v>1041.4</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>572.9</v>
+        <v>564.2</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>377.8</v>
+        <v>369.9</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2307.2</v>
+        <v>2262</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>69.22</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>130.71</v>
+        <v>127.21</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>160.69</v>
+        <v>156.81</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>661.3</v>
+        <v>634.4</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>660</v>
+        <v>635</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2065</v>
+        <v>2011.8</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4299.4</v>
+        <v>4201.7</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4300</v>
+        <v>4200</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>922.3</v>
+        <v>892.85</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>410.65</v>
+        <v>400.8</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1177</v>
+        <v>1140.3</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>140.37</v>
+        <v>137.65</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>556.8</v>
+        <v>534</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>305.85</v>
+        <v>300.7</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1232</v>
+        <v>1214.3</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>556.65</v>
+        <v>517.95</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1262.6</v>
+        <v>1252.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>460.5</v>
+        <v>442.15</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>381.05</v>
+        <v>376</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>733.45</v>
+        <v>712.05</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1652.4</v>
+        <v>1587</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1266.8</v>
+        <v>1268</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>585.6</v>
+        <v>567.65</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3940.2</v>
+        <v>3856.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3950</v>
+        <v>3850</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>295</v>
+        <v>280.65</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3788.4</v>
+        <v>3603.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2255.9</v>
+        <v>2245.4</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3245.9</v>
+        <v>3176</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3250</v>
+        <v>3200</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>305.45</v>
+        <v>293.2</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>842.55</v>
+        <v>830</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13483</v>
+        <v>13172</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13500</v>
+        <v>13200</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3187.9</v>
+        <v>3156.9</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3200</v>
+        <v>3150</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>559.9</v>
+        <v>548.1</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1695.5</v>
+        <v>1653.7</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1106.4</v>
+        <v>1064.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>130.3</v>
+        <v>124.26</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2201.2</v>
+        <v>2146.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>128910</v>
+        <v>126505</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>129000</v>
+        <v>126500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3438.2</v>
+        <v>3353.4</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3450</v>
+        <v>3350</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>393.05</v>
+        <v>394.05</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>961.2</v>
+        <v>930.9</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7071.5</v>
+        <v>6950.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1481.9</v>
+        <v>1468.6</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>86.79000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>392.95</v>
+        <v>392.7</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1634.7</v>
+        <v>1626.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9239.5</v>
+        <v>9010.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>281</v>
+        <v>294.5</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>36245</v>
+        <v>35085</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>36000</v>
+        <v>35000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5098.1</v>
+        <v>4877.1</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5100</v>
+        <v>4900</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>275.75</v>
+        <v>271.15</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>448.5</v>
+        <v>440.7</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1437.2</v>
+        <v>1453</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3090.8</v>
+        <v>2997.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>104.62</v>
+        <v>102.78</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9065.5</v>
+        <v>9021.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>310.9</v>
+        <v>306.3</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>337.5</v>
+        <v>325.25</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>351.55</v>
+        <v>344.35</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1388.2</v>
+        <v>1364</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>180.72</v>
+        <v>176.09</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>641.5</v>
+        <v>625.1</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1884.4</v>
+        <v>1833.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1875</v>
+        <v>1825</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>973.6</v>
+        <v>974.6</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25205</v>
+        <v>24860</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>975.95</v>
+        <v>930.45</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3605.6</v>
+        <v>3574.4</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3600</v>
+        <v>3550</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2798.5</v>
+        <v>2721.2</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1872.7</v>
+        <v>1845.7</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>567.75</v>
+        <v>560.2</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>482.5</v>
+        <v>478.75</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>761.35</v>
+        <v>770.25</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1571.5</v>
+        <v>1539.9</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1271</v>
+        <v>1253</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1270</v>
+        <v>1250</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>433.2</v>
+        <v>418.4</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>212.08</v>
+        <v>212</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2392.9</v>
+        <v>2300.3</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1457.4</v>
+        <v>1392.9</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4205.6</v>
+        <v>4055.3</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4200</v>
+        <v>4050</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4517.1</v>
+        <v>4381.9</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1680.9</v>
+        <v>1597.6</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1675</v>
+        <v>1600</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4181.1</v>
+        <v>4050.6</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4200</v>
+        <v>4050</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3613.7</v>
+        <v>3561</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3625</v>
+        <v>3550</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1412.2</v>
+        <v>1410.5</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11866</v>
+        <v>11516</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11900</v>
+        <v>11500</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>163.81</v>
+        <v>162.19</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>669</v>
+        <v>626.15</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>675</v>
+        <v>625</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>298.4</v>
+        <v>305.05</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1306.5</v>
+        <v>1269.6</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>196.68</v>
+        <v>189.57</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>956.95</v>
+        <v>930.65</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  12-May-2026 15:42</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  13-May-2026 15:46</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>468.5</v>
+        <v>468.55</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6328.5</v>
+        <v>6305</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6350</v>
+        <v>6300</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26900</v>
+        <v>27280</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26800</v>
+        <v>27200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>341.2</v>
+        <v>344.3</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>62.4</v>
+        <v>63.59</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1347</v>
+        <v>1366.4</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2405.2</v>
+        <v>2498</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1688.2</v>
+        <v>1737.8</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5496.5</v>
+        <v>5462.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>426.95</v>
+        <v>438.4</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>299.1</v>
+        <v>298.15</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8022.5</v>
+        <v>8004.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>398.75</v>
+        <v>396.45</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>155.95</v>
+        <v>153.21</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2505.5</v>
+        <v>2617.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1527.6</v>
+        <v>1544</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>591.3</v>
+        <v>606.5</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1488.2</v>
+        <v>1497.5</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>999.6</v>
+        <v>994.8</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1260.1</v>
+        <v>1255.7</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10397</v>
+        <v>10262</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1744.8</v>
+        <v>1728.9</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>904.2</v>
+        <v>896.15</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2110.6</v>
+        <v>2105.1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>196.07</v>
+        <v>194.88</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>259.95</v>
+        <v>261.65</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>416.5</v>
+        <v>428.25</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>488.1</v>
+        <v>507.7</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1756.8</v>
+        <v>1789.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>391.75</v>
+        <v>403.85</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>402.45</v>
+        <v>417.6</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36510</v>
+        <v>36315</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36600</v>
+        <v>36400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>287.85</v>
+        <v>297.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5334</v>
+        <v>5336</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>130.01</v>
+        <v>129.26</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1561</v>
+        <v>1574.6</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1292.3</v>
+        <v>1327.6</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>463.05</v>
+        <v>462.25</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1320.4</v>
+        <v>1297.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2125.2</v>
+        <v>2134.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>516</v>
+        <v>519.85</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>282.05</v>
+        <v>284.8</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5160</v>
+        <v>5212</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5150</v>
+        <v>5200</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>473.25</v>
+        <v>463.1</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1848.3</v>
+        <v>1856.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6644</v>
+        <v>6796</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6600</v>
+        <v>6800</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10138</v>
+        <v>11124</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>10100</v>
+        <v>11100</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>569.2</v>
+        <v>574.15</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1270</v>
+        <v>1265.3</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7126</v>
+        <v>6971.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2960.7</v>
+        <v>2982.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>346.3</v>
+        <v>349.3</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>284.8</v>
+        <v>280.05</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>160.35</v>
+        <v>163.31</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2257.1</v>
+        <v>2277.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1030.2</v>
+        <v>1030.5</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1712.4</v>
+        <v>1730.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>729.05</v>
+        <v>728.35</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2903</v>
+        <v>2945.6</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>368.25</v>
+        <v>360.85</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4572.5</v>
+        <v>4618.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1190.9</v>
+        <v>1199.2</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1145.8</v>
+        <v>1143.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2632.8</v>
+        <v>2652.3</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>750.45</v>
+        <v>749.6</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>601.8</v>
+        <v>602.8</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5082.5</v>
+        <v>4995</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1041.4</v>
+        <v>1073.1</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1040</v>
+        <v>1070</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>564.2</v>
+        <v>595.3</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>369.9</v>
+        <v>390.1</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2262</v>
+        <v>2267.3</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>67.68000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>127.21</v>
+        <v>127.53</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>156.81</v>
+        <v>159.3</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>634.4</v>
+        <v>637.4</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2011.8</v>
+        <v>1969.2</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4201.7</v>
+        <v>4255.8</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4200</v>
+        <v>4250</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>892.85</v>
+        <v>892.5</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>400.8</v>
+        <v>413.2</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1140.3</v>
+        <v>1123.1</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>137.65</v>
+        <v>141.69</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>534</v>
+        <v>536.1</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>300.7</v>
+        <v>304.45</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1214.3</v>
+        <v>1242.9</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>517.95</v>
+        <v>509.2</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1252.3</v>
+        <v>1274.9</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>442.15</v>
+        <v>448.4</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>376</v>
+        <v>377.65</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>712.05</v>
+        <v>710.65</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1587</v>
+        <v>1575.7</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1268</v>
+        <v>1280.5</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>567.65</v>
+        <v>585.65</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3856.5</v>
+        <v>3915.8</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3850</v>
+        <v>3900</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>280.65</v>
+        <v>281.9</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3603.7</v>
+        <v>3497.9</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2245.4</v>
+        <v>2215.6</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2250</v>
+        <v>2225</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3176</v>
+        <v>3111.8</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>293.2</v>
+        <v>309.5</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>830</v>
+        <v>833.4</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13172</v>
+        <v>13103</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13200</v>
+        <v>13100</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3156.9</v>
+        <v>3204.2</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3150</v>
+        <v>3200</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>548.1</v>
+        <v>548</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1653.7</v>
+        <v>1597.9</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1064.4</v>
+        <v>1046.9</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>124.26</v>
+        <v>126.32</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2146.5</v>
+        <v>2145.2</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>126505</v>
+        <v>126480</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3353.4</v>
+        <v>3506.4</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3350</v>
+        <v>3500</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>394.05</v>
+        <v>408.25</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>930.9</v>
+        <v>927.85</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6950.5</v>
+        <v>6910.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1468.6</v>
+        <v>1468.9</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>86.62</v>
+        <v>91.11</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3611,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>392.7</v>
+        <v>390.45</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1626.7</v>
+        <v>1618.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9010.5</v>
+        <v>8928.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>294.5</v>
+        <v>297.15</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>35085</v>
+        <v>35330</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>35000</v>
+        <v>35500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4877.1</v>
+        <v>4845</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>271.15</v>
+        <v>271.35</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>440.7</v>
+        <v>446</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1453</v>
+        <v>1445.6</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2997.6</v>
+        <v>3051</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>102.78</v>
+        <v>102.77</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9021.5</v>
+        <v>8887.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>306.3</v>
+        <v>301.5</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>325.25</v>
+        <v>325.75</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>344.35</v>
+        <v>346.55</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1364</v>
+        <v>1358.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>176.09</v>
+        <v>201.31</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>625.1</v>
+        <v>634.15</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1833.9</v>
+        <v>1837.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>974.6</v>
+        <v>970.1</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24860</v>
+        <v>24995</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>930.45</v>
+        <v>920.55</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3574.4</v>
+        <v>3532.2</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2721.2</v>
+        <v>2695.2</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1845.7</v>
+        <v>1824.8</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>560.2</v>
+        <v>532.95</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>478.75</v>
+        <v>463.25</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>770.25</v>
+        <v>768.1</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1539.9</v>
+        <v>1558.8</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1253</v>
+        <v>1235</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1250</v>
+        <v>1240</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>418.4</v>
+        <v>404.45</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>212</v>
+        <v>219.62</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2300.3</v>
+        <v>2272.8</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1392.9</v>
+        <v>1375</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4055.3</v>
+        <v>4090.7</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4381.9</v>
+        <v>4295.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1597.6</v>
+        <v>1457.1</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4050.6</v>
+        <v>4084.5</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3561</v>
+        <v>3527.2</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3550</v>
+        <v>3525</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1410.5</v>
+        <v>1381.2</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11516</v>
+        <v>11573</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11500</v>
+        <v>11600</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>162.19</v>
+        <v>162.46</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>626.15</v>
+        <v>630.1</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>305.05</v>
+        <v>323.35</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1269.6</v>
+        <v>1258.9</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>189.57</v>
+        <v>187.8</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>930.65</v>
+        <v>939.25</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  13-May-2026 15:46</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  14-May-2026 15:24</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>468.55</v>
+        <v>468</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6305</v>
+        <v>6429</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6300</v>
+        <v>6450</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27280</v>
+        <v>27520</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27200</v>
+        <v>27600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>344.3</v>
+        <v>349.65</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63.59</v>
+        <v>63.48</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1366.4</v>
+        <v>1378.2</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2498</v>
+        <v>2712.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1737.8</v>
+        <v>1773.4</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5462.5</v>
+        <v>5576.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>438.4</v>
+        <v>443.9</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>298.15</v>
+        <v>303.7</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8004.5</v>
+        <v>8119</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>396.45</v>
+        <v>401.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>153.21</v>
+        <v>154.34</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2617.6</v>
+        <v>2622.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1544</v>
+        <v>1561.3</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>606.5</v>
+        <v>612.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1497.5</v>
+        <v>1510.9</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>994.8</v>
+        <v>1004.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1255.7</v>
+        <v>1254.6</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10262</v>
+        <v>10451</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10300</v>
+        <v>10500</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1728.9</v>
+        <v>1740.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>896.15</v>
+        <v>912.15</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2105.1</v>
+        <v>2191.1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>194.88</v>
+        <v>199.04</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>261.65</v>
+        <v>267.8</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>428.25</v>
+        <v>428.85</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>507.7</v>
+        <v>533.9</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1789.2</v>
+        <v>1883.5</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1800</v>
+        <v>1875</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>403.85</v>
+        <v>413.15</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>417.6</v>
+        <v>419</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36315</v>
+        <v>36945</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36400</v>
+        <v>37000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>297.1</v>
+        <v>295</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5336</v>
+        <v>5372.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>129.26</v>
+        <v>130.84</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1574.6</v>
+        <v>1567.1</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1327.6</v>
+        <v>1436.7</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1325</v>
+        <v>1425</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>462.25</v>
+        <v>454.05</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1297.1</v>
+        <v>1274.6</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2134.5</v>
+        <v>2146.6</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2125</v>
+        <v>2150</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>519.85</v>
+        <v>522.95</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>284.8</v>
+        <v>288.95</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5212</v>
+        <v>5367</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5200</v>
+        <v>5350</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>463.1</v>
+        <v>464.75</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1856.4</v>
+        <v>1840.2</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6796</v>
+        <v>6921.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6800</v>
+        <v>6900</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11124</v>
+        <v>11103</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>574.15</v>
+        <v>583.25</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1265.3</v>
+        <v>1303.6</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>6971.5</v>
+        <v>7034</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2982.7</v>
+        <v>2999.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>349.3</v>
+        <v>349.7</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>280.05</v>
+        <v>280.25</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>163.31</v>
+        <v>162.61</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2277.6</v>
+        <v>2340.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2275</v>
+        <v>2350</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1030.5</v>
+        <v>1033.3</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1730.6</v>
+        <v>1733.5</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>728.35</v>
+        <v>735.3</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2945.6</v>
+        <v>2938.7</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>360.85</v>
+        <v>362.1</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4618.5</v>
+        <v>4608</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1199.2</v>
+        <v>1210.8</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1143.2</v>
+        <v>1124</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2652.3</v>
+        <v>2691.6</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>749.6</v>
+        <v>769.55</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>602.8</v>
+        <v>612.55</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4995</v>
+        <v>5077</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1073.1</v>
+        <v>1103.3</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1070</v>
+        <v>1100</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>595.3</v>
+        <v>606.45</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>390.1</v>
+        <v>377.55</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2267.3</v>
+        <v>2248.7</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>68.3</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>127.53</v>
+        <v>128.44</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>159.3</v>
+        <v>155.71</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>637.4</v>
+        <v>650.2</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>635</v>
+        <v>650</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1969.2</v>
+        <v>1971.2</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4255.8</v>
+        <v>4280.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4250</v>
+        <v>4300</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>892.5</v>
+        <v>907.9</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>413.2</v>
+        <v>422.35</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1123.1</v>
+        <v>1095</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>141.69</v>
+        <v>140.26</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>536.1</v>
+        <v>538.85</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>304.45</v>
+        <v>307.2</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1242.9</v>
+        <v>1252.8</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>509.2</v>
+        <v>512.8</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1274.9</v>
+        <v>1296.9</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>448.4</v>
+        <v>460.45</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>377.65</v>
+        <v>383.2</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>710.65</v>
+        <v>709</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1575.7</v>
+        <v>1600.1</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1280.5</v>
+        <v>1315.5</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1280</v>
+        <v>1315</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>585.65</v>
+        <v>560.4</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3915.8</v>
+        <v>3940.4</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3900</v>
+        <v>3950</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>281.9</v>
+        <v>281.3</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3497.9</v>
+        <v>3466.6</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2215.6</v>
+        <v>2258.2</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2225</v>
+        <v>2250</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3111.8</v>
+        <v>3173.9</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>309.5</v>
+        <v>311.1</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>833.4</v>
+        <v>835</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13103</v>
+        <v>13075</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3204.2</v>
+        <v>3339.1</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3200</v>
+        <v>3350</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>548</v>
+        <v>540.7</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1597.9</v>
+        <v>1631.4</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1046.9</v>
+        <v>1067.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>126.32</v>
+        <v>126.11</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2145.2</v>
+        <v>2115.1</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>126480</v>
+        <v>126455</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3506.4</v>
+        <v>3531.1</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3500</v>
+        <v>3525</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>408.25</v>
+        <v>416.45</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>927.85</v>
+        <v>937.75</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6910.5</v>
+        <v>6892.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1468.9</v>
+        <v>1459.6</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>91.11</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3611,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>390.45</v>
+        <v>396.3</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1618.7</v>
+        <v>1637.6</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>8928.5</v>
+        <v>8904.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>297.15</v>
+        <v>300.9</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>35330</v>
+        <v>36125</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>35500</v>
+        <v>36000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4845</v>
+        <v>4628.8</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4800</v>
+        <v>4600</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>271.35</v>
+        <v>271.75</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>446</v>
+        <v>451.45</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1445.6</v>
+        <v>1483.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3051</v>
+        <v>3103.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>102.77</v>
+        <v>104.62</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8887.5</v>
+        <v>9217.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>8900</v>
+        <v>9200</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>301.5</v>
+        <v>301.75</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>325.75</v>
+        <v>337.2</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>346.55</v>
+        <v>348.3</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1358.8</v>
+        <v>1361.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>201.31</v>
+        <v>199.08</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>634.15</v>
+        <v>631.55</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1837.5</v>
+        <v>1866.7</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>970.1</v>
+        <v>979.9</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24995</v>
+        <v>25025</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>920.55</v>
+        <v>935.1</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3532.2</v>
+        <v>3693.8</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3550</v>
+        <v>3700</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2695.2</v>
+        <v>2729.4</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1824.8</v>
+        <v>1863.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1825</v>
+        <v>1875</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>532.95</v>
+        <v>523.25</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>463.25</v>
+        <v>467.95</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>768.1</v>
+        <v>757.1</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1558.8</v>
+        <v>1656.1</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1550</v>
+        <v>1650</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1235</v>
+        <v>1228.3</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>404.45</v>
+        <v>407.85</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>219.62</v>
+        <v>221.13</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2272.8</v>
+        <v>2246</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1375</v>
+        <v>1343.4</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4090.7</v>
+        <v>4135.2</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4100</v>
+        <v>4150</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4295.8</v>
+        <v>4403.9</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1457.1</v>
+        <v>1457.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4084.5</v>
+        <v>4132.4</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4100</v>
+        <v>4150</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3527.2</v>
+        <v>3460.8</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3525</v>
+        <v>3450</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1381.2</v>
+        <v>1389.2</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11573</v>
+        <v>11692</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>162.46</v>
+        <v>164.9</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>630.1</v>
+        <v>638.4</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>323.35</v>
+        <v>338.9</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1258.9</v>
+        <v>1293.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>187.8</v>
+        <v>188.3</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>939.25</v>
+        <v>991.7</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  14-May-2026 15:24</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  15-May-2026 15:21</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>468</v>
+        <v>466.25</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6429</v>
+        <v>6381</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6450</v>
+        <v>6400</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27520</v>
+        <v>27940</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27600</v>
+        <v>28000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>349.65</v>
+        <v>357.15</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63.48</v>
+        <v>62.66</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1378.2</v>
+        <v>1362.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2712.9</v>
+        <v>2716</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1773.4</v>
+        <v>1795.1</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5576.5</v>
+        <v>5486</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>443.9</v>
+        <v>433.75</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>303.7</v>
+        <v>306.85</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8119</v>
+        <v>8082.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>401.8</v>
+        <v>394.5</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>154.34</v>
+        <v>153.13</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2622.2</v>
+        <v>2605.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1561.3</v>
+        <v>1550.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>612.6</v>
+        <v>616.25</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1510.9</v>
+        <v>1511.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1004.7</v>
+        <v>990.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1254.6</v>
+        <v>1244.8</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10451</v>
+        <v>10377.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10500</v>
+        <v>10400</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1740.2</v>
+        <v>1728.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>912.15</v>
+        <v>910.45</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2191.1</v>
+        <v>2148.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>199.04</v>
+        <v>194.46</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>267.8</v>
+        <v>261.4</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>428.85</v>
+        <v>423.65</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>533.9</v>
+        <v>533.45</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1883.5</v>
+        <v>1905.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>413.15</v>
+        <v>398.3</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>419</v>
+        <v>430.1</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36945</v>
+        <v>37740</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37000</v>
+        <v>37800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>295</v>
+        <v>284.45</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5372.5</v>
+        <v>5406</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5350</v>
+        <v>5400</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>130.84</v>
+        <v>128.07</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1567.1</v>
+        <v>1546.3</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1436.7</v>
+        <v>1432.1</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>454.05</v>
+        <v>462.2</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1274.6</v>
+        <v>1282.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2146.6</v>
+        <v>2160</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>522.95</v>
+        <v>518.8</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>288.95</v>
+        <v>301.95</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5367</v>
+        <v>5392</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5350</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>464.75</v>
+        <v>467.7</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1840.2</v>
+        <v>1826.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6921.5</v>
+        <v>6760.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11103</v>
+        <v>10979</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>583.25</v>
+        <v>566.75</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1303.6</v>
+        <v>1336.7</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7034</v>
+        <v>7014.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2999.2</v>
+        <v>3000.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>349.7</v>
+        <v>349.05</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>280.25</v>
+        <v>281.3</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>162.61</v>
+        <v>162.13</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2340.6</v>
+        <v>2325.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2350</v>
+        <v>2325</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1033.3</v>
+        <v>1039.2</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1733.5</v>
+        <v>1714.1</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>735.3</v>
+        <v>736.2</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2938.7</v>
+        <v>2933.8</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2950</v>
+        <v>2925</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>362.1</v>
+        <v>369.9</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4608</v>
+        <v>4386.2</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1210.8</v>
+        <v>1209.6</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1124</v>
+        <v>1132.6</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2691.6</v>
+        <v>2703.5</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>769.55</v>
+        <v>767.5</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>612.55</v>
+        <v>608.7</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5077</v>
+        <v>5064.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1103.3</v>
+        <v>1067.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1100</v>
+        <v>1070</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>606.45</v>
+        <v>570.25</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>605</v>
+        <v>570</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>377.55</v>
+        <v>366.4</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2248.7</v>
+        <v>2272.2</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>68.54000000000001</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>128.44</v>
+        <v>125.27</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>155.71</v>
+        <v>152.12</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>650.2</v>
+        <v>656.25</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1971.2</v>
+        <v>1956.5</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4280.5</v>
+        <v>4314.9</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>907.9</v>
+        <v>886.4</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>422.35</v>
+        <v>430.15</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1095</v>
+        <v>1119</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>140.26</v>
+        <v>134.48</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>538.85</v>
+        <v>535.95</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>307.2</v>
+        <v>309.45</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1252.8</v>
+        <v>1232</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>512.8</v>
+        <v>515.05</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1296.9</v>
+        <v>1278.8</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>460.45</v>
+        <v>461.35</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>383.2</v>
+        <v>387.05</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>709</v>
+        <v>703.7</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1600.1</v>
+        <v>1602.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1315.5</v>
+        <v>1323.6</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1315</v>
+        <v>1325</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>560.4</v>
+        <v>547.05</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3940.4</v>
+        <v>3909</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3950</v>
+        <v>3900</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>281.3</v>
+        <v>280.75</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3466.6</v>
+        <v>3495.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2258.2</v>
+        <v>2276.2</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3173.9</v>
+        <v>3123.1</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>311.1</v>
+        <v>307.45</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>835</v>
+        <v>841.15</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13075</v>
+        <v>13221</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13100</v>
+        <v>13200</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3339.1</v>
+        <v>3391</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3350</v>
+        <v>3400</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>540.7</v>
+        <v>528.85</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1631.4</v>
+        <v>1604</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1067.4</v>
+        <v>1087.6</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>126.11</v>
+        <v>129.92</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2115.1</v>
+        <v>2083.2</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>126455</v>
+        <v>128640</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>126500</v>
+        <v>128500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3531.1</v>
+        <v>3311.4</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3525</v>
+        <v>3300</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>416.45</v>
+        <v>403.6</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>937.75</v>
+        <v>928.1</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6892.5</v>
+        <v>7001</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1459.6</v>
+        <v>1430.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3584,7 +3584,7 @@
         <v>100</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>93.20999999999999</v>
+        <v>91.41</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3611,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>396.3</v>
+        <v>395.25</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1637.6</v>
+        <v>1617.2</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>8904.5</v>
+        <v>9015</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>300.9</v>
+        <v>299.35</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>36125</v>
+        <v>36820</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>36000</v>
+        <v>37000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4628.8</v>
+        <v>4702.1</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>271.75</v>
+        <v>263.6</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>451.45</v>
+        <v>445.75</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1483.8</v>
+        <v>1467.7</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3103.6</v>
+        <v>3114.9</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>104.62</v>
+        <v>102.05</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9217.5</v>
+        <v>9152.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>301.75</v>
+        <v>305.85</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>337.2</v>
+        <v>338.1</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>348.3</v>
+        <v>345.85</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1361.8</v>
+        <v>1336.4</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>199.08</v>
+        <v>192.4</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>631.55</v>
+        <v>626</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1866.7</v>
+        <v>1864.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>979.9</v>
+        <v>963.2</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25025</v>
+        <v>24970</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>935.1</v>
+        <v>937.9</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3693.8</v>
+        <v>3587.9</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2729.4</v>
+        <v>2689.5</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1863.2</v>
+        <v>1878.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>523.25</v>
+        <v>535.15</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>467.95</v>
+        <v>454.05</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>757.1</v>
+        <v>748.9</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1656.1</v>
+        <v>1680</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1650</v>
+        <v>1675</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1228.3</v>
+        <v>1234</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>407.85</v>
+        <v>407</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>221.13</v>
+        <v>216.84</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2246</v>
+        <v>2264</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1343.4</v>
+        <v>1370.5</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4135.2</v>
+        <v>4169.1</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4403.9</v>
+        <v>4405.7</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1457.7</v>
+        <v>1466</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4132.4</v>
+        <v>4101.3</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4150</v>
+        <v>4100</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3460.8</v>
+        <v>3466.8</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3450</v>
+        <v>3475</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1389.2</v>
+        <v>1367.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11692</v>
+        <v>11487</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>164.9</v>
+        <v>161.94</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>638.4</v>
+        <v>632.25</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>338.9</v>
+        <v>331.05</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1293.5</v>
+        <v>1230.7</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1300</v>
+        <v>1225</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>188.3</v>
+        <v>190</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>991.7</v>
+        <v>1011.7</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  15-May-2026 15:21</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  18-May-2026 16:29</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>466.25</v>
+        <v>461.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6381</v>
+        <v>6413.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27940</v>
+        <v>27925</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>357.15</v>
+        <v>350.1</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>62.66</v>
+        <v>61.96</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1362.8</v>
+        <v>1359.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2716</v>
+        <v>2689.8</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1795.1</v>
+        <v>1787.7</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5486</v>
+        <v>5468</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>433.75</v>
+        <v>430.15</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>306.85</v>
+        <v>303.95</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8082.5</v>
+        <v>8020.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>394.5</v>
+        <v>375.15</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>153.13</v>
+        <v>151.14</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2605.6</v>
+        <v>2614</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1550.8</v>
+        <v>1545.7</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>616.25</v>
+        <v>610.1</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1511.8</v>
+        <v>1500.5</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>990.5</v>
+        <v>979</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1244.8</v>
+        <v>1237.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10377.5</v>
+        <v>10198.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10400</v>
+        <v>10200</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1728.1</v>
+        <v>1753.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>910.45</v>
+        <v>921.1</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2148.3</v>
+        <v>2117.1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>194.46</v>
+        <v>190.34</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>261.4</v>
+        <v>260.05</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>423.65</v>
+        <v>426.6</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>533.45</v>
+        <v>524.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1905.4</v>
+        <v>1938.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>398.3</v>
+        <v>395.25</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>430.1</v>
+        <v>426.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37740</v>
+        <v>37155</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37800</v>
+        <v>37200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>284.45</v>
+        <v>280.8</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5406</v>
+        <v>5380.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>128.07</v>
+        <v>124.9</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1546.3</v>
+        <v>1527.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1432.1</v>
+        <v>1426.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>462.2</v>
+        <v>462.1</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1282.1</v>
+        <v>1348.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2160</v>
+        <v>2151.2</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>518.8</v>
+        <v>501.95</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>301.95</v>
+        <v>293.3</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5392</v>
+        <v>5298.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>467.7</v>
+        <v>456.35</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1826.4</v>
+        <v>1748.5</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1850</v>
+        <v>1750</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6760.5</v>
+        <v>6835</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10979</v>
+        <v>10780</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11000</v>
+        <v>10800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>566.75</v>
+        <v>573.15</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1336.7</v>
+        <v>1331.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7014.5</v>
+        <v>6913</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3000.2</v>
+        <v>2971</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>349.05</v>
+        <v>342.85</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>281.3</v>
+        <v>283.95</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>162.13</v>
+        <v>160.22</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2325.9</v>
+        <v>2339.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1039.2</v>
+        <v>1014.4</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1714.1</v>
+        <v>1686.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>736.2</v>
+        <v>731.45</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2933.8</v>
+        <v>2943.8</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2925</v>
+        <v>2950</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>369.9</v>
+        <v>364.75</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4386.2</v>
+        <v>4326.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1209.6</v>
+        <v>1194.8</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1132.6</v>
+        <v>1146.6</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2703.5</v>
+        <v>2625.1</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>767.5</v>
+        <v>768.65</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>608.7</v>
+        <v>604.95</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5064.5</v>
+        <v>4957</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5050</v>
+        <v>4950</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1067.5</v>
+        <v>1053.1</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1070</v>
+        <v>1050</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>570.25</v>
+        <v>581.15</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>366.4</v>
+        <v>358.9</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2272.2</v>
+        <v>2254.2</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>67.65000000000001</v>
+        <v>67.59</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.27</v>
+        <v>123.5</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>152.12</v>
+        <v>151.64</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>656.25</v>
+        <v>648.55</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1956.5</v>
+        <v>1949</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4314.9</v>
+        <v>4275.7</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>886.4</v>
+        <v>892.15</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>875</v>
+        <v>900</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>430.15</v>
+        <v>430.9</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1119</v>
+        <v>1142.5</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>134.48</v>
+        <v>131.81</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>535.95</v>
+        <v>531.85</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>309.45</v>
+        <v>310.15</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1232</v>
+        <v>1231.8</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>515.05</v>
+        <v>529.05</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1278.8</v>
+        <v>1292.8</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>461.35</v>
+        <v>456.95</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>387.05</v>
+        <v>391.8</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>703.7</v>
+        <v>707.75</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1602.9</v>
+        <v>1646.3</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1323.6</v>
+        <v>1327.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>547.05</v>
+        <v>545.55</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3909</v>
+        <v>3917.8</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>280.75</v>
+        <v>278.75</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3495.1</v>
+        <v>3549.5</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2276.2</v>
+        <v>2252.4</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2275</v>
+        <v>2250</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3123.1</v>
+        <v>3083.7</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>307.45</v>
+        <v>306.1</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>841.15</v>
+        <v>833.75</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13221</v>
+        <v>13016</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13200</v>
+        <v>13000</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3391</v>
+        <v>3348.4</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3400</v>
+        <v>3350</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>528.85</v>
+        <v>507.4</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1604</v>
+        <v>1601.7</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1087.6</v>
+        <v>1058.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>129.92</v>
+        <v>128.75</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2083.2</v>
+        <v>2148.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>128640</v>
+        <v>129110</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>128500</v>
+        <v>129000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3311.4</v>
+        <v>3290.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>403.6</v>
+        <v>400.45</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>928.1</v>
+        <v>925.95</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7001</v>
+        <v>6904.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1430.5</v>
+        <v>1431.7</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>91.41</v>
+        <v>90.14</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>395.25</v>
+        <v>388.3</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1617.2</v>
+        <v>1600.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9015</v>
+        <v>9408.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9000</v>
+        <v>9400</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>299.35</v>
+        <v>297.2</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>36820</v>
+        <v>37505</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>37000</v>
+        <v>37500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4702.1</v>
+        <v>4944.1</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4700</v>
+        <v>4900</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>263.6</v>
+        <v>265.15</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>445.75</v>
+        <v>429.8</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1467.7</v>
+        <v>1450.2</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3114.9</v>
+        <v>3096.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>102.05</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9152.5</v>
+        <v>9151</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>305.85</v>
+        <v>296.55</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>338.1</v>
+        <v>325.6</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>345.85</v>
+        <v>333.7</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1336.4</v>
+        <v>1335.9</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>192.4</v>
+        <v>192.73</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1864.5</v>
+        <v>1860.4</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>963.2</v>
+        <v>939.4</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24970</v>
+        <v>24475</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25000</v>
+        <v>24500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>937.9</v>
+        <v>933.7</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3587.9</v>
+        <v>3535.1</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3600</v>
+        <v>3550</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2689.5</v>
+        <v>2639.9</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1878.2</v>
+        <v>1905.8</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>535.15</v>
+        <v>521.1</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>454.05</v>
+        <v>466.3</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>748.9</v>
+        <v>730.35</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1680</v>
+        <v>1668.4</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>407</v>
+        <v>404.35</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>216.84</v>
+        <v>209.71</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2264</v>
+        <v>2283.2</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1370.5</v>
+        <v>1430</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1375</v>
+        <v>1425</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4169.1</v>
+        <v>4169.7</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4405.7</v>
+        <v>4393.7</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1466</v>
+        <v>1523.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1475</v>
+        <v>1525</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4101.3</v>
+        <v>4032.3</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3466.8</v>
+        <v>3291</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3475</v>
+        <v>3300</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1367.8</v>
+        <v>1354.5</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11487</v>
+        <v>11561</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11500</v>
+        <v>11600</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>161.94</v>
+        <v>158.89</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>632.25</v>
+        <v>637.85</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>331.05</v>
+        <v>327</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1230.7</v>
+        <v>1252.8</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>190</v>
+        <v>192.17</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1011.7</v>
+        <v>991.1</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  18-May-2026 16:29</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  19-May-2026 16:25</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>461.2</v>
+        <v>469.25</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6413.5</v>
+        <v>6329</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6400</v>
+        <v>6350</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27925</v>
+        <v>27795</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28000</v>
+        <v>27800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>350.1</v>
+        <v>351.2</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61.96</v>
+        <v>62.46</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1359.6</v>
+        <v>1359.3</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2689.8</v>
+        <v>2725</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1787.7</v>
+        <v>1762.8</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5468</v>
+        <v>5470</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>430.15</v>
+        <v>431.7</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>303.95</v>
+        <v>328</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -857,7 +857,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8020.5</v>
+        <v>8026</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>375.15</v>
+        <v>371.9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>151.14</v>
+        <v>151.38</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2614</v>
+        <v>2600.7</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1545.7</v>
+        <v>1448.9</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1450</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>610.1</v>
+        <v>623.3</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1500.5</v>
+        <v>1512.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>979</v>
+        <v>971.9</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1237.9</v>
+        <v>1238.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10198.5</v>
+        <v>10205</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1753.1</v>
+        <v>1749.8</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>921.1</v>
+        <v>923.55</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2117.1</v>
+        <v>2128</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>190.34</v>
+        <v>191.21</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>260.05</v>
+        <v>260.6</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>426.6</v>
+        <v>422.95</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>524.6</v>
+        <v>507.7</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1938.1</v>
+        <v>1913.5</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1950</v>
+        <v>1925</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>395.25</v>
+        <v>401.1</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>426.25</v>
+        <v>428.15</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37155</v>
+        <v>37130</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>280.8</v>
+        <v>286.45</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5380.5</v>
+        <v>5416.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124.9</v>
+        <v>126.15</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1527.9</v>
+        <v>1511.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1426.2</v>
+        <v>1409.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>462.1</v>
+        <v>456.95</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1348.1</v>
+        <v>1412</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2151.2</v>
+        <v>2188.3</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>501.95</v>
+        <v>505.6</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>293.3</v>
+        <v>293.6</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5298.5</v>
+        <v>5254</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>456.35</v>
+        <v>452.8</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1748.5</v>
+        <v>1805.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6835</v>
+        <v>6912</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6800</v>
+        <v>6900</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10780</v>
+        <v>11048</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>10800</v>
+        <v>11000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>573.15</v>
+        <v>577.4</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1331.2</v>
+        <v>1335.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>6913</v>
+        <v>6882.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2971</v>
+        <v>2890.8</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>342.85</v>
+        <v>344.65</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>283.95</v>
+        <v>286.6</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>160.22</v>
+        <v>156.12</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2339.9</v>
+        <v>2405.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1014.4</v>
+        <v>1022</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1686.3</v>
+        <v>1715.4</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>731.45</v>
+        <v>766.45</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>730</v>
+        <v>765</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2943.8</v>
+        <v>2935.2</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2950</v>
+        <v>2925</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>364.75</v>
+        <v>376.55</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4326.5</v>
+        <v>4333.2</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1194.8</v>
+        <v>1207.2</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1146.6</v>
+        <v>1179.4</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2625.1</v>
+        <v>2653.6</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>768.65</v>
+        <v>762.45</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>604.95</v>
+        <v>610.4</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4957</v>
+        <v>5007.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1053.1</v>
+        <v>1048.3</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>581.15</v>
+        <v>569.5</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>358.9</v>
+        <v>371</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2254.2</v>
+        <v>2232.9</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>67.59</v>
+        <v>67.81</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123.5</v>
+        <v>125.48</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>151.64</v>
+        <v>157.35</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>648.55</v>
+        <v>652.75</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1949</v>
+        <v>1982.6</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4275.7</v>
+        <v>4230.3</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4300</v>
+        <v>4250</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>892.15</v>
+        <v>895.25</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>430.9</v>
+        <v>430.7</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1142.5</v>
+        <v>1196.9</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>131.81</v>
+        <v>135</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>531.85</v>
+        <v>529.8</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>310.15</v>
+        <v>310.3</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1231.8</v>
+        <v>1226.3</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>529.05</v>
+        <v>533.15</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1292.8</v>
+        <v>1285.2</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>456.95</v>
+        <v>473</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>391.8</v>
+        <v>381.95</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>707.75</v>
+        <v>743.7</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1646.3</v>
+        <v>1703.7</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1327.3</v>
+        <v>1344.9</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1325</v>
+        <v>1345</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>545.55</v>
+        <v>543</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3917.8</v>
+        <v>3921</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>278.75</v>
+        <v>277.95</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3549.5</v>
+        <v>3554.6</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2252.4</v>
+        <v>2287.4</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3083.7</v>
+        <v>3092.3</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>306.1</v>
+        <v>315.3</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>833.75</v>
+        <v>831.45</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13016</v>
+        <v>12956</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3348.4</v>
+        <v>3414.7</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3350</v>
+        <v>3425</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>507.4</v>
+        <v>508.4</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1601.7</v>
+        <v>1617.9</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1058.7</v>
+        <v>1059.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>128.75</v>
+        <v>131.49</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2148.5</v>
+        <v>2220.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>129110</v>
+        <v>126730</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>129000</v>
+        <v>126500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3290.9</v>
+        <v>3303.6</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>400.45</v>
+        <v>398.95</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>925.95</v>
+        <v>933.65</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6904.5</v>
+        <v>7075.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>6900</v>
+        <v>7100</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1431.7</v>
+        <v>1431.4</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>90.14</v>
+        <v>89.02</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>388.3</v>
+        <v>389.4</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1600.7</v>
+        <v>1622</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9408.5</v>
+        <v>9646</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>297.2</v>
+        <v>296.5</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37505</v>
+        <v>38700</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>37500</v>
+        <v>38500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4944.1</v>
+        <v>5066.3</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>429.8</v>
+        <v>431.6</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1450.2</v>
+        <v>1455.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3096.3</v>
+        <v>3124.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>99.48999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9151</v>
+        <v>9162.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>296.55</v>
+        <v>298.6</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>325.6</v>
+        <v>323.65</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>333.7</v>
+        <v>334.25</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1335.9</v>
+        <v>1322.7</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>192.73</v>
+        <v>199.05</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>624</v>
+        <v>623.8</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1860.4</v>
+        <v>1881.4</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>939.4</v>
+        <v>948.8</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24475</v>
+        <v>24425</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>933.7</v>
+        <v>927.35</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3535.1</v>
+        <v>3550.9</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2639.9</v>
+        <v>2637.2</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1905.8</v>
+        <v>1882.3</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>521.1</v>
+        <v>525.15</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>466.3</v>
+        <v>471.35</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>730.35</v>
+        <v>736.2</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1668.4</v>
+        <v>1646.6</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1231</v>
+        <v>1210.9</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1230</v>
+        <v>1210</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>404.35</v>
+        <v>415</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>209.71</v>
+        <v>209.29</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2283.2</v>
+        <v>2327.1</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1430</v>
+        <v>1467.1</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1425</v>
+        <v>1475</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4169.7</v>
+        <v>4102</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4150</v>
+        <v>4100</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4393.7</v>
+        <v>4460.1</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4400</v>
+        <v>4450</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1523.5</v>
+        <v>1480.3</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1525</v>
+        <v>1475</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4032.3</v>
+        <v>4069.6</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3291</v>
+        <v>3283.4</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3300</v>
+        <v>3275</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1354.5</v>
+        <v>1348.3</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11561</v>
+        <v>11368</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11600</v>
+        <v>11400</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>158.89</v>
+        <v>158.96</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>637.85</v>
+        <v>633.3</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>327</v>
+        <v>337.65</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1252.8</v>
+        <v>1302.6</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>192.17</v>
+        <v>195.17</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>991.1</v>
+        <v>1018.9</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  19-May-2026 16:25</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  20-May-2026 16:29</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>469.25</v>
+        <v>463.35</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6329</v>
+        <v>6605</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6350</v>
+        <v>6600</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27795</v>
+        <v>27445</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27800</v>
+        <v>27400</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>351.2</v>
+        <v>353.1</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>62.46</v>
+        <v>62.53</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1359.3</v>
+        <v>1351.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2725</v>
+        <v>2704.8</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1762.8</v>
+        <v>1772.6</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5470</v>
+        <v>5436.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>431.7</v>
+        <v>430.25</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -857,7 +857,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8026</v>
+        <v>8078.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>371.9</v>
+        <v>375.9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>151.38</v>
+        <v>153.61</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2600.7</v>
+        <v>2598.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1448.9</v>
+        <v>1443.7</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>623.3</v>
+        <v>610.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1512.8</v>
+        <v>1517.5</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>971.9</v>
+        <v>974</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1238.3</v>
+        <v>1249.8</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10205</v>
+        <v>10462.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10200</v>
+        <v>10500</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1749.8</v>
+        <v>1772</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>923.55</v>
+        <v>923.1</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2128</v>
+        <v>2155</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>191.21</v>
+        <v>192.15</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>260.6</v>
+        <v>263.55</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>422.95</v>
+        <v>413.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>507.7</v>
+        <v>508.45</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1913.5</v>
+        <v>1904.9</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1925</v>
+        <v>1900</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>401.1</v>
+        <v>408.4</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>428.15</v>
+        <v>432.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37130</v>
+        <v>36830</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37200</v>
+        <v>36800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>286.45</v>
+        <v>293.75</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5416.5</v>
+        <v>5344.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5400</v>
+        <v>5350</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>126.15</v>
+        <v>127.66</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1511.4</v>
+        <v>1518.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1409.8</v>
+        <v>1399.5</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>456.95</v>
+        <v>458.7</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1412</v>
+        <v>1402.3</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2188.3</v>
+        <v>2185.4</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2200</v>
+        <v>2175</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>505.6</v>
+        <v>504.15</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>293.6</v>
+        <v>290.6</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5254</v>
+        <v>5399.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5250</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>452.8</v>
+        <v>450.9</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1805.8</v>
+        <v>1824</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6912</v>
+        <v>6893</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11048</v>
+        <v>10997</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>577.4</v>
+        <v>583.3</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1335.2</v>
+        <v>1321.9</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>6882.5</v>
+        <v>6849.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2890.8</v>
+        <v>2895.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>344.65</v>
+        <v>339.55</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>286.6</v>
+        <v>289.9</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>156.12</v>
+        <v>155.64</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2405.9</v>
+        <v>2379</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2400</v>
+        <v>2375</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1022</v>
+        <v>1022.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1715.4</v>
+        <v>1719.4</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>766.45</v>
+        <v>758.65</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2935.2</v>
+        <v>2971.1</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2925</v>
+        <v>2975</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>376.55</v>
+        <v>372.6</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4333.2</v>
+        <v>4326.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1207.2</v>
+        <v>1207.8</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1179.4</v>
+        <v>1169.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2653.6</v>
+        <v>2685.3</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>762.45</v>
+        <v>759.5</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>610.4</v>
+        <v>605.1</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5007.5</v>
+        <v>4968</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1048.3</v>
+        <v>1085.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1050</v>
+        <v>1090</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>569.5</v>
+        <v>554.6</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>371</v>
+        <v>382.75</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2232.9</v>
+        <v>2209.3</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>67.81</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.48</v>
+        <v>125.62</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>157.35</v>
+        <v>154.8</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>652.75</v>
+        <v>659.6</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1982.6</v>
+        <v>1998</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4230.3</v>
+        <v>4264.6</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>895.25</v>
+        <v>897.15</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>430.7</v>
+        <v>427.85</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1196.9</v>
+        <v>1193.7</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>135</v>
+        <v>138.04</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>529.8</v>
+        <v>527.85</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>310.3</v>
+        <v>307.55</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1226.3</v>
+        <v>1223.1</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>533.15</v>
+        <v>537.1</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1285.2</v>
+        <v>1283.2</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>473</v>
+        <v>472.55</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>381.95</v>
+        <v>383.2</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>743.7</v>
+        <v>750.8</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1703.7</v>
+        <v>1668.6</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1344.9</v>
+        <v>1361.1</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1345</v>
+        <v>1360</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>543</v>
+        <v>546.8</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3921</v>
+        <v>3910.7</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>277.95</v>
+        <v>275.65</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3554.6</v>
+        <v>3580.6</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2287.4</v>
+        <v>2285.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3092.3</v>
+        <v>3122.2</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>315.3</v>
+        <v>319.15</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>831.45</v>
+        <v>838.45</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>12956</v>
+        <v>13003</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3414.7</v>
+        <v>3441.7</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3425</v>
+        <v>3450</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>508.4</v>
+        <v>518.3</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1617.9</v>
+        <v>1625.4</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1059.4</v>
+        <v>1075.6</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>131.49</v>
+        <v>132.17</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2220.5</v>
+        <v>2228</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>126730</v>
+        <v>127125</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>126500</v>
+        <v>127000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3303.6</v>
+        <v>3309.3</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>398.95</v>
+        <v>402.4</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>933.65</v>
+        <v>942.25</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7075.5</v>
+        <v>7046.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1431.4</v>
+        <v>1420.1</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>89.02</v>
+        <v>88.48</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>389.4</v>
+        <v>392.45</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1622</v>
+        <v>1626.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9646</v>
+        <v>9703.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>296.5</v>
+        <v>298.3</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38700</v>
+        <v>38285</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5066.3</v>
+        <v>5084.1</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>265.15</v>
+        <v>264.65</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>431.6</v>
+        <v>429.35</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1455.8</v>
+        <v>1455.6</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>3124.6</v>
+        <v>2901.2</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>101.3</v>
+        <v>102.22</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9162.5</v>
+        <v>9199</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>298.6</v>
+        <v>299.9</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>323.65</v>
+        <v>328.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>334.25</v>
+        <v>333</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1322.7</v>
+        <v>1359.7</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>199.05</v>
+        <v>199.04</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>623.8</v>
+        <v>624.35</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1881.4</v>
+        <v>1864.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>948.8</v>
+        <v>950.9</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24425</v>
+        <v>24420</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>927.35</v>
+        <v>923.45</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3550.9</v>
+        <v>3696.4</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3550</v>
+        <v>3700</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2637.2</v>
+        <v>2613.3</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2650</v>
+        <v>2600</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1882.3</v>
+        <v>1880.3</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>525.15</v>
+        <v>517.45</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>471.35</v>
+        <v>466.05</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>736.2</v>
+        <v>729.95</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1646.6</v>
+        <v>1775.6</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1650</v>
+        <v>1775</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1210.9</v>
+        <v>1208.7</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>415</v>
+        <v>413.5</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>209.29</v>
+        <v>207.01</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2327.1</v>
+        <v>2327.4</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1467.1</v>
+        <v>1439</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4102</v>
+        <v>4106.4</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4460.1</v>
+        <v>4429.2</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1480.3</v>
+        <v>1512.6</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1475</v>
+        <v>1525</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4069.6</v>
+        <v>4099.9</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3283.4</v>
+        <v>3361.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3275</v>
+        <v>3350</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1348.3</v>
+        <v>1348.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11368</v>
+        <v>11409</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>158.96</v>
+        <v>159</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>633.3</v>
+        <v>634.35</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>337.65</v>
+        <v>333.75</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1302.6</v>
+        <v>1295.8</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>195.17</v>
+        <v>197.12</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1018.9</v>
+        <v>1040.85</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  20-May-2026 16:29</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  21-May-2026 16:18</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>463.35</v>
+        <v>482.75</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6605</v>
+        <v>6598</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27445</v>
+        <v>27715</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27400</v>
+        <v>27800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>353.1</v>
+        <v>349.4</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>62.53</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1351.6</v>
+        <v>1360.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2704.8</v>
+        <v>2697.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1772.6</v>
+        <v>1793.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5436.5</v>
+        <v>5501.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>430.25</v>
+        <v>436.45</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>325</v>
+        <v>339.65</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -857,7 +857,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8078.5</v>
+        <v>8308.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>375.9</v>
+        <v>371.9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>153.61</v>
+        <v>154.48</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2598.6</v>
+        <v>2598.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1443.7</v>
+        <v>1480</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>610.6</v>
+        <v>638.1</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1517.5</v>
+        <v>1546.7</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>974</v>
+        <v>958.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1249.8</v>
+        <v>1253.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10462.5</v>
+        <v>10667</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10500</v>
+        <v>10700</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1772</v>
+        <v>1752.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>923.1</v>
+        <v>907.65</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2155</v>
+        <v>2205.4</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>192.15</v>
+        <v>191.08</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>263.55</v>
+        <v>263.1</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>413.3</v>
+        <v>420.4</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>508.45</v>
+        <v>499.35</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1904.9</v>
+        <v>1885.3</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>408.4</v>
+        <v>408.15</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>432.7</v>
+        <v>430.85</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36830</v>
+        <v>35210</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36800</v>
+        <v>35200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>293.75</v>
+        <v>296.4</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5344.5</v>
+        <v>5333</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>127.66</v>
+        <v>127.97</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1518.9</v>
+        <v>1504</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1399.5</v>
+        <v>1401.9</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>458.7</v>
+        <v>460.2</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1402.3</v>
+        <v>1377</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2185.4</v>
+        <v>2164.9</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>504.15</v>
+        <v>505.9</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>290.6</v>
+        <v>291.85</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5399.5</v>
+        <v>5390</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>450.9</v>
+        <v>446.85</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1824</v>
+        <v>1785.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6893</v>
+        <v>6858</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>10997</v>
+        <v>11258</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11000</v>
+        <v>11300</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>583.3</v>
+        <v>587.95</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1321.9</v>
+        <v>1318.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>6849.5</v>
+        <v>6892</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>6800</v>
+        <v>6900</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2895.6</v>
+        <v>2904.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>339.55</v>
+        <v>340.8</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>289.9</v>
+        <v>283.75</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>155.64</v>
+        <v>155.9</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2379</v>
+        <v>2393</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1022.9</v>
+        <v>1017.3</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1719.4</v>
+        <v>1736.9</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>758.65</v>
+        <v>764.2</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2971.1</v>
+        <v>3154.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2975</v>
+        <v>3150</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>372.6</v>
+        <v>374</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4326.5</v>
+        <v>4370.4</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1207.8</v>
+        <v>1209.7</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1169.8</v>
+        <v>1168.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2685.3</v>
+        <v>2727.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>759.5</v>
+        <v>759.15</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>605.1</v>
+        <v>614.35</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4968</v>
+        <v>4969.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1085.5</v>
+        <v>1099.3</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1090</v>
+        <v>1100</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>554.6</v>
+        <v>552.15</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>382.75</v>
+        <v>388.8</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2209.3</v>
+        <v>2179</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>68.20999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.62</v>
+        <v>127.05</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>154.8</v>
+        <v>154.81</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>659.6</v>
+        <v>657.4</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1998</v>
+        <v>2030.2</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4264.6</v>
+        <v>4403</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4250</v>
+        <v>4400</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>897.15</v>
+        <v>899.95</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>427.85</v>
+        <v>431.8</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1193.7</v>
+        <v>1181.2</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>138.04</v>
+        <v>140.53</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>527.85</v>
+        <v>527.15</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>307.55</v>
+        <v>308.05</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1223.1</v>
+        <v>1196.8</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>537.1</v>
+        <v>548.45</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1283.2</v>
+        <v>1281.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>472.55</v>
+        <v>435.65</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>383.2</v>
+        <v>380.85</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>750.8</v>
+        <v>750.9</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1668.6</v>
+        <v>1680.8</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1361.1</v>
+        <v>1351</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1360</v>
+        <v>1350</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>546.8</v>
+        <v>537.95</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3910.7</v>
+        <v>3928.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3900</v>
+        <v>3950</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>275.65</v>
+        <v>269.85</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3580.6</v>
+        <v>3587.3</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2285.5</v>
+        <v>2284.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3122.2</v>
+        <v>3099</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>319.15</v>
+        <v>322.4</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>838.45</v>
+        <v>831.85</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13003</v>
+        <v>13010</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3441.7</v>
+        <v>3322.8</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3450</v>
+        <v>3325</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>518.3</v>
+        <v>528.8</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1625.4</v>
+        <v>1626</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1075.6</v>
+        <v>1053.8</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>132.17</v>
+        <v>137</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2228</v>
+        <v>2227.6</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>127125</v>
+        <v>126070</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>127000</v>
+        <v>126000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3309.3</v>
+        <v>3272.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3300</v>
+        <v>3275</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>402.4</v>
+        <v>406.4</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>942.25</v>
+        <v>926.25</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7046.5</v>
+        <v>7118.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1420.1</v>
+        <v>1406.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.48</v>
+        <v>88.16</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>392.45</v>
+        <v>388.8</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1626.7</v>
+        <v>1654.4</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9703.5</v>
+        <v>9730.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>298.3</v>
+        <v>295.85</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38285</v>
+        <v>38380</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5084.1</v>
+        <v>5019</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>264.65</v>
+        <v>269.9</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>429.35</v>
+        <v>431</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1455.6</v>
+        <v>1472.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2901.2</v>
+        <v>2740.5</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2900</v>
+        <v>2750</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>102.22</v>
+        <v>101.92</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9199</v>
+        <v>9193.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>299.9</v>
+        <v>299.55</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>328.5</v>
+        <v>328.75</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>333</v>
+        <v>333.7</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1359.7</v>
+        <v>1349.6</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>199.04</v>
+        <v>196.53</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>624.35</v>
+        <v>620.2</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1864.2</v>
+        <v>1859.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24420</v>
+        <v>24605</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>923.45</v>
+        <v>914.75</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3696.4</v>
+        <v>3720.6</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2613.3</v>
+        <v>2620.4</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1880.3</v>
+        <v>1891.3</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>517.45</v>
+        <v>518.75</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>466.05</v>
+        <v>470.2</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>729.95</v>
+        <v>755.1</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1775.6</v>
+        <v>1896.3</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1775</v>
+        <v>1900</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1208.7</v>
+        <v>1194.9</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1210</v>
+        <v>1190</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>413.5</v>
+        <v>410.5</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>207.01</v>
+        <v>208.58</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2327.4</v>
+        <v>2327.2</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1439</v>
+        <v>1420</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4106.4</v>
+        <v>4083.1</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4429.2</v>
+        <v>4469.2</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1512.6</v>
+        <v>1491.4</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4099.9</v>
+        <v>4170.4</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4100</v>
+        <v>4150</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3361.9</v>
+        <v>3380.7</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3350</v>
+        <v>3375</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1348.8</v>
+        <v>1331</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11409</v>
+        <v>11474</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>159</v>
+        <v>160.12</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>634.35</v>
+        <v>629</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>333.75</v>
+        <v>329.75</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1295.8</v>
+        <v>1273.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>197.12</v>
+        <v>199.74</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1040.85</v>
+        <v>1036.45</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  21-May-2026 16:18</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  22-May-2026 15:51</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>482.75</v>
+        <v>476.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6598</v>
+        <v>6689.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27715</v>
+        <v>27830</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>349.4</v>
+        <v>357.3</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>66.76000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1360.8</v>
+        <v>1360</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2697.6</v>
+        <v>2717.3</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1793.3</v>
+        <v>1786.9</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5501.5</v>
+        <v>5404.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>436.45</v>
+        <v>436.35</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>339.65</v>
+        <v>339.35</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8308.5</v>
+        <v>8362.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>371.9</v>
+        <v>371.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>154.48</v>
+        <v>158.21</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2598.8</v>
+        <v>2639.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2600</v>
+        <v>2650</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1480</v>
+        <v>1541.7</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1475</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>638.1</v>
+        <v>652.8</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1546.7</v>
+        <v>1463.5</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1550</v>
+        <v>1475</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>958.7</v>
+        <v>977.9</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1253.3</v>
+        <v>1285.4</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10667</v>
+        <v>10549.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10700</v>
+        <v>10500</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1752.2</v>
+        <v>1766</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>907.65</v>
+        <v>916.55</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2205.4</v>
+        <v>2208.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>191.08</v>
+        <v>194.61</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>263.1</v>
+        <v>265.4</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>420.4</v>
+        <v>416.55</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>499.35</v>
+        <v>501.15</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1885.3</v>
+        <v>1871.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>408.15</v>
+        <v>408.55</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>430.85</v>
+        <v>430.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>35210</v>
+        <v>36065</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>35200</v>
+        <v>36000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>296.4</v>
+        <v>295.6</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5333</v>
+        <v>5331.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>127.97</v>
+        <v>128.23</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1504</v>
+        <v>1539.8</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1401.9</v>
+        <v>1399.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>460.2</v>
+        <v>456.55</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1377</v>
+        <v>1387.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2164.9</v>
+        <v>2156.9</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2175</v>
+        <v>2150</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>291.85</v>
+        <v>294.75</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5390</v>
+        <v>5353</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5400</v>
+        <v>5350</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>446.85</v>
+        <v>451.05</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1785.3</v>
+        <v>1739.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6858</v>
+        <v>6887</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11258</v>
+        <v>11722</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11300</v>
+        <v>11700</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>587.95</v>
+        <v>586.7</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1318.5</v>
+        <v>1307.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>6892</v>
+        <v>6981.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2904.1</v>
+        <v>2931.4</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>340.8</v>
+        <v>339.75</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>283.75</v>
+        <v>287.2</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>155.9</v>
+        <v>160.77</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2393</v>
+        <v>2259.1</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2400</v>
+        <v>2250</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1017.3</v>
+        <v>1027.5</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1736.9</v>
+        <v>1732.9</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>764.2</v>
+        <v>751.95</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3154.5</v>
+        <v>3155.3</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4370.4</v>
+        <v>4368.4</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1209.7</v>
+        <v>1200.9</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1168.2</v>
+        <v>1164</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2727.9</v>
+        <v>2738.7</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>759.15</v>
+        <v>766.8</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>614.35</v>
+        <v>616.6</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4969.5</v>
+        <v>4966</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1099.3</v>
+        <v>1109.2</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>552.15</v>
+        <v>545.75</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>388.8</v>
+        <v>389.65</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2179</v>
+        <v>2203.6</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>68.3</v>
+        <v>68.88</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>127.05</v>
+        <v>127.07</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>154.81</v>
+        <v>155.51</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>657.4</v>
+        <v>650.25</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2030.2</v>
+        <v>2030</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4403</v>
+        <v>4438.6</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4400</v>
+        <v>4450</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>899.95</v>
+        <v>910.15</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>431.8</v>
+        <v>432.05</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1181.2</v>
+        <v>1174.5</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>140.53</v>
+        <v>139.47</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>527.15</v>
+        <v>530.25</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>308.05</v>
+        <v>301.7</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1196.8</v>
+        <v>1209.9</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>548.45</v>
+        <v>551.25</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1281.3</v>
+        <v>1285.5</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>435.65</v>
+        <v>436.65</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>380.85</v>
+        <v>384.15</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>750.9</v>
+        <v>751.05</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1680.8</v>
+        <v>1630.1</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1351</v>
+        <v>1343.5</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>537.95</v>
+        <v>539.2</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3928.5</v>
+        <v>3926.6</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>269.85</v>
+        <v>270.15</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3587.3</v>
+        <v>3419.3</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3600</v>
+        <v>3400</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2284.5</v>
+        <v>2281.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3099</v>
+        <v>3081.3</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>322.4</v>
+        <v>324.1</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>831.85</v>
+        <v>824.45</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13010</v>
+        <v>12987</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3322.8</v>
+        <v>3269.9</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3325</v>
+        <v>3275</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>528.8</v>
+        <v>518.95</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1626</v>
+        <v>1680</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1625</v>
+        <v>1675</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1053.8</v>
+        <v>1054.8</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>137</v>
+        <v>136.18</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2227.6</v>
+        <v>2222.4</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>126070</v>
+        <v>126785</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>126000</v>
+        <v>127000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3272.7</v>
+        <v>3296.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3275</v>
+        <v>3300</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>406.4</v>
+        <v>409.25</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>926.25</v>
+        <v>960.95</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7118.5</v>
+        <v>7125</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1406.5</v>
+        <v>1423.1</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.16</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>388.8</v>
+        <v>388.65</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1654.4</v>
+        <v>1659.6</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9730.5</v>
+        <v>9525</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>295.85</v>
+        <v>290</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38380</v>
+        <v>39455</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>38500</v>
+        <v>39500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5019</v>
+        <v>4970.3</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>269.9</v>
+        <v>272.35</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>431</v>
+        <v>430.55</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1472.8</v>
+        <v>1478.4</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2740.5</v>
+        <v>2781</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>101.92</v>
+        <v>102.66</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9193.5</v>
+        <v>9263.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>299.55</v>
+        <v>294.3</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>328.75</v>
+        <v>334.35</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>333.7</v>
+        <v>336.95</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1349.6</v>
+        <v>1354.5</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>196.53</v>
+        <v>201.21</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1859.9</v>
+        <v>1870.7</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>950.9</v>
+        <v>949.2</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24605</v>
+        <v>24785</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24500</v>
+        <v>25000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>914.75</v>
+        <v>941</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3720.6</v>
+        <v>3811.7</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2620.4</v>
+        <v>2639.4</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2600</v>
+        <v>2650</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1891.3</v>
+        <v>1844.6</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1900</v>
+        <v>1850</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>518.75</v>
+        <v>486.7</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>470.2</v>
+        <v>461.85</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>755.1</v>
+        <v>750.2</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1896.3</v>
+        <v>1964</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1900</v>
+        <v>1975</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1194.9</v>
+        <v>1191.8</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>410.5</v>
+        <v>408.9</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>208.58</v>
+        <v>209.19</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2327.2</v>
+        <v>2317.3</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1420</v>
+        <v>1422.2</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4083.1</v>
+        <v>4079.8</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4469.2</v>
+        <v>4486.2</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4450</v>
+        <v>4500</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1491.4</v>
+        <v>1498.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4170.4</v>
+        <v>4296.5</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4150</v>
+        <v>4300</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3380.7</v>
+        <v>3417.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3375</v>
+        <v>3425</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1331</v>
+        <v>1315.2</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11474</v>
+        <v>11569</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11500</v>
+        <v>11600</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>160.12</v>
+        <v>160.72</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>329.75</v>
+        <v>329.95</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1273.5</v>
+        <v>1268.1</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>199.74</v>
+        <v>203.11</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1036.45</v>
+        <v>1038.95</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  22-May-2026 15:51</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  25-May-2026 15:54</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>476.2</v>
+        <v>482.6</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6689.5</v>
+        <v>6755</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6700</v>
+        <v>6750</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27830</v>
+        <v>27705</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>357.3</v>
+        <v>363.65</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>67.34999999999999</v>
+        <v>67.36</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1360</v>
+        <v>1382.3</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2717.3</v>
+        <v>2849.7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2700</v>
+        <v>2850</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1786.9</v>
+        <v>1802.9</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5404.5</v>
+        <v>5400.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>436.35</v>
+        <v>441.95</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>339.35</v>
+        <v>346.45</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8362.5</v>
+        <v>8404</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>371.8</v>
+        <v>388.35</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>158.21</v>
+        <v>164.08</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2639.8</v>
+        <v>2657.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1541.7</v>
+        <v>1552.3</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>652.8</v>
+        <v>659.15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1463.5</v>
+        <v>1454.6</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>977.9</v>
+        <v>999.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>975</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1285.4</v>
+        <v>1311.2</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10549.5</v>
+        <v>10491</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1766</v>
+        <v>1807.4</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>916.55</v>
+        <v>941.9</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2208.3</v>
+        <v>2219.1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>194.61</v>
+        <v>196.97</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>265.4</v>
+        <v>272.25</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>416.55</v>
+        <v>421.85</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>501.15</v>
+        <v>504.85</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1871.4</v>
+        <v>1874.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>408.55</v>
+        <v>419.4</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>430.25</v>
+        <v>430.05</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36065</v>
+        <v>36310</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36000</v>
+        <v>36400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>295.6</v>
+        <v>308.25</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5331.5</v>
+        <v>5327</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>128.23</v>
+        <v>133.7</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1539.8</v>
+        <v>1591</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1399.2</v>
+        <v>1413.9</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1400</v>
+        <v>1425</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>456.55</v>
+        <v>458</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1387.1</v>
+        <v>1398</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2156.9</v>
+        <v>2097</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>505.9</v>
+        <v>512.05</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>294.75</v>
+        <v>293.5</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5353</v>
+        <v>5382</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5350</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>451.05</v>
+        <v>447.2</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1739.8</v>
+        <v>1745.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6887</v>
+        <v>6756.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11722</v>
+        <v>11824</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>586.7</v>
+        <v>592.3</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1307.2</v>
+        <v>1331.4</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>6981.5</v>
+        <v>7414</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7000</v>
+        <v>7400</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2931.4</v>
+        <v>2976.5</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>339.75</v>
+        <v>346.25</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>287.2</v>
+        <v>289.25</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>160.77</v>
+        <v>168.67</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2259.1</v>
+        <v>2337</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2250</v>
+        <v>2325</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1027.5</v>
+        <v>1020.4</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1732.9</v>
+        <v>1767.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>751.95</v>
+        <v>758.4</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3155.3</v>
+        <v>3171.6</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3150</v>
+        <v>3175</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>373</v>
+        <v>377.5</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4368.4</v>
+        <v>4425.9</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1200.9</v>
+        <v>1203.8</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1164</v>
+        <v>1165.7</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2738.7</v>
+        <v>2758.1</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>766.8</v>
+        <v>786.85</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>616.6</v>
+        <v>620</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4966</v>
+        <v>4979</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1109.2</v>
+        <v>1099.6</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>545.75</v>
+        <v>545.55</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>389.65</v>
+        <v>403.35</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2203.6</v>
+        <v>2196.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>68.88</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>127.07</v>
+        <v>127.58</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>155.51</v>
+        <v>160.48</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>650.25</v>
+        <v>663.55</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2030</v>
+        <v>2029.3</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4438.6</v>
+        <v>4501.9</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4450</v>
+        <v>4500</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>910.15</v>
+        <v>926.1</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>432.05</v>
+        <v>438.85</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1174.5</v>
+        <v>1168.5</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>139.47</v>
+        <v>143.95</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>530.25</v>
+        <v>537.85</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>301.7</v>
+        <v>303.95</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1209.9</v>
+        <v>1212.3</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>551.25</v>
+        <v>557.05</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1285.5</v>
+        <v>1289.4</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>436.65</v>
+        <v>438.75</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>384.15</v>
+        <v>392.85</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>751.05</v>
+        <v>756.6</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1630.1</v>
+        <v>1614.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1343.5</v>
+        <v>1356.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>539.2</v>
+        <v>543.45</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3926.6</v>
+        <v>4033.4</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3950</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>270.15</v>
+        <v>279.35</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3419.3</v>
+        <v>3546.2</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2281.8</v>
+        <v>2287.2</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3081.3</v>
+        <v>3139</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>324.1</v>
+        <v>325.65</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>824.45</v>
+        <v>823.35</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>12987</v>
+        <v>13170</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13000</v>
+        <v>13200</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3269.9</v>
+        <v>3313.9</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3275</v>
+        <v>3325</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>518.95</v>
+        <v>524.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1680</v>
+        <v>1726.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1675</v>
+        <v>1725</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1054.8</v>
+        <v>1074.9</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>136.18</v>
+        <v>135.91</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2222.4</v>
+        <v>2244</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>126785</v>
+        <v>128655</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>127000</v>
+        <v>128500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3296.7</v>
+        <v>3354.4</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3300</v>
+        <v>3350</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>409.25</v>
+        <v>403</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>960.95</v>
+        <v>938.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7125</v>
+        <v>7445.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7100</v>
+        <v>7400</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1423.1</v>
+        <v>1413.6</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>87.84999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>388.65</v>
+        <v>390.05</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1659.6</v>
+        <v>1712.4</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9525</v>
+        <v>9703</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>290</v>
+        <v>284.95</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>39455</v>
+        <v>38545</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>39500</v>
+        <v>38500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4970.3</v>
+        <v>5038</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>272.35</v>
+        <v>282.25</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>430.55</v>
+        <v>438.9</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1478.4</v>
+        <v>1477.2</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2781</v>
+        <v>2849</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>102.66</v>
+        <v>106.26</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9263.5</v>
+        <v>9398.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>294.3</v>
+        <v>295.35</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>334.35</v>
+        <v>343.35</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>336.95</v>
+        <v>342.2</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1354.5</v>
+        <v>1367</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>201.21</v>
+        <v>198.32</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>620.2</v>
+        <v>630.3</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1870.7</v>
+        <v>1901.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>949.2</v>
+        <v>969.6</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24785</v>
+        <v>25355</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>941</v>
+        <v>961.95</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3811.7</v>
+        <v>3667.5</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3800</v>
+        <v>3650</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2639.4</v>
+        <v>2711</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2650</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1844.6</v>
+        <v>1840.6</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>486.7</v>
+        <v>494.3</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>461.85</v>
+        <v>462.4</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>750.2</v>
+        <v>765.95</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1964</v>
+        <v>1936</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1975</v>
+        <v>1925</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1191.8</v>
+        <v>1187.2</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>408.9</v>
+        <v>413.55</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>209.19</v>
+        <v>210.22</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2317.3</v>
+        <v>2308.2</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1422.2</v>
+        <v>1435.5</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4079.8</v>
+        <v>4159.2</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4100</v>
+        <v>4150</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4486.2</v>
+        <v>4572.6</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4500</v>
+        <v>4550</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1498.5</v>
+        <v>1474.6</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1500</v>
+        <v>1475</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4296.5</v>
+        <v>4300</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3417.5</v>
+        <v>3469.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3425</v>
+        <v>3475</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1315.2</v>
+        <v>1323.5</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11569</v>
+        <v>11726</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>160.72</v>
+        <v>168.87</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>632</v>
+        <v>652.3</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>329.95</v>
+        <v>332.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1268.1</v>
+        <v>1284</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>203.11</v>
+        <v>206.84</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1038.95</v>
+        <v>1072.95</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  25-May-2026 15:54</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  26-May-2026 16:45</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>482.6</v>
+        <v>491</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6755</v>
+        <v>6804</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6750</v>
+        <v>6800</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27705</v>
+        <v>27610</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27800</v>
+        <v>27600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>363.65</v>
+        <v>363.05</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>67.36</v>
+        <v>64.87</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1382.3</v>
+        <v>1412.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1375</v>
+        <v>1425</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2849.7</v>
+        <v>2969.3</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2850</v>
+        <v>2950</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1802.9</v>
+        <v>1811.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5400.5</v>
+        <v>5380</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>441.95</v>
+        <v>449.7</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>346.45</v>
+        <v>344.45</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8404</v>
+        <v>8258.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>388.35</v>
+        <v>393.25</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>164.08</v>
+        <v>160.54</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2657.8</v>
+        <v>2647</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1552.3</v>
+        <v>1578.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>659.15</v>
+        <v>713.1</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>650</v>
+        <v>725</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1454.6</v>
+        <v>1461.2</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>999.3</v>
+        <v>1011.8</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1311.2</v>
+        <v>1299.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10491</v>
+        <v>10593</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10500</v>
+        <v>10600</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1807.4</v>
+        <v>1800.7</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>941.9</v>
+        <v>930.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2219.1</v>
+        <v>2202.7</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>196.97</v>
+        <v>200.4</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>272.25</v>
+        <v>270.55</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>421.85</v>
+        <v>420.1</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>504.85</v>
+        <v>515.55</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1874.8</v>
+        <v>1846.9</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>419.4</v>
+        <v>417.75</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>430.05</v>
+        <v>436.15</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36310</v>
+        <v>35835</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36400</v>
+        <v>35800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>308.25</v>
+        <v>304.6</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5327</v>
+        <v>5338</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>133.7</v>
+        <v>133.15</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1591</v>
+        <v>1567.3</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1413.9</v>
+        <v>1417.5</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>458</v>
+        <v>458.15</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1398</v>
+        <v>1422.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2097</v>
+        <v>2077.1</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2100</v>
+        <v>2075</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>512.05</v>
+        <v>475.9</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>293.5</v>
+        <v>289.05</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5382</v>
+        <v>5418.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>447.2</v>
+        <v>447.6</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1745.9</v>
+        <v>1727.1</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6756.5</v>
+        <v>6753</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11824</v>
+        <v>11673</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11800</v>
+        <v>11700</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>592.3</v>
+        <v>589.8</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1331.4</v>
+        <v>1327.9</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7414</v>
+        <v>7376</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2976.5</v>
+        <v>2939.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>346.25</v>
+        <v>366.25</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>289.25</v>
+        <v>290.2</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>168.67</v>
+        <v>167.63</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2337</v>
+        <v>2351.4</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1020.4</v>
+        <v>1031.8</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1767.3</v>
+        <v>1760.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>758.4</v>
+        <v>756.5</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3171.6</v>
+        <v>3165</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>377.5</v>
+        <v>371.5</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4425.9</v>
+        <v>4427.7</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1203.8</v>
+        <v>1201</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1165.7</v>
+        <v>1161.9</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2758.1</v>
+        <v>2739.8</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>786.85</v>
+        <v>778.9</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>620</v>
+        <v>618.85</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4979</v>
+        <v>4983</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1099.6</v>
+        <v>1103.8</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>545.55</v>
+        <v>556</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>403.35</v>
+        <v>398</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2196.5</v>
+        <v>2209.4</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>69.45999999999999</v>
+        <v>70.22</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>127.58</v>
+        <v>127.47</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>160.48</v>
+        <v>166.01</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>663.55</v>
+        <v>657.15</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2029.3</v>
+        <v>2037.9</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4501.9</v>
+        <v>4480.8</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>926.1</v>
+        <v>932.3</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>438.85</v>
+        <v>433.25</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1168.5</v>
+        <v>1167.7</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>143.95</v>
+        <v>142.38</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>537.85</v>
+        <v>537.2</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>303.95</v>
+        <v>301.65</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1212.3</v>
+        <v>1222.9</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1200</v>
+        <v>1225</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>557.05</v>
+        <v>576</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1289.4</v>
+        <v>1293.6</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>438.75</v>
+        <v>430.05</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>392.85</v>
+        <v>388.65</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>756.6</v>
+        <v>784.7</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1614.9</v>
+        <v>1604</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1356.3</v>
+        <v>1373.9</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1355</v>
+        <v>1375</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>543.45</v>
+        <v>544.15</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4033.4</v>
+        <v>4037.8</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>279.35</v>
+        <v>282.7</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3546.2</v>
+        <v>3540.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2287.2</v>
+        <v>2266</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3139</v>
+        <v>3107.3</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>325.65</v>
+        <v>330.25</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>823.35</v>
+        <v>830</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13170</v>
+        <v>13208</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3313.9</v>
+        <v>3307.3</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3325</v>
+        <v>3300</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>524.5</v>
+        <v>540.85</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1726.8</v>
+        <v>1725.6</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1074.9</v>
+        <v>1096</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>135.91</v>
+        <v>135.82</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2244</v>
+        <v>2265.3</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>128655</v>
+        <v>127160</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>128500</v>
+        <v>127000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3354.4</v>
+        <v>3331.5</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3350</v>
+        <v>3325</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>403</v>
+        <v>416.2</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>938.5</v>
+        <v>980.7</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7445.5</v>
+        <v>7396</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1413.6</v>
+        <v>1428.6</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>90.19</v>
+        <v>90.67</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>390.05</v>
+        <v>389.7</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1712.4</v>
+        <v>1693.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9703</v>
+        <v>9882</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9700</v>
+        <v>9900</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>284.95</v>
+        <v>287.5</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38545</v>
+        <v>38305</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5038</v>
+        <v>5105.8</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>282.25</v>
+        <v>280.2</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>438.9</v>
+        <v>433.7</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1477.2</v>
+        <v>1478.5</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2849</v>
+        <v>2837.9</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>106.26</v>
+        <v>105.91</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9398.5</v>
+        <v>9613.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>295.35</v>
+        <v>292.55</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>343.35</v>
+        <v>344.25</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>342.2</v>
+        <v>337.6</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1367</v>
+        <v>1356.3</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>198.32</v>
+        <v>203.84</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>630.3</v>
+        <v>628.7</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1901.9</v>
+        <v>1883.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>969.6</v>
+        <v>968.5</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25355</v>
+        <v>25180</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25500</v>
+        <v>25000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>961.95</v>
+        <v>952.15</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3667.5</v>
+        <v>3677.2</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3650</v>
+        <v>3700</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2711</v>
+        <v>2749.7</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1840.6</v>
+        <v>1840.8</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>494.3</v>
+        <v>493.2</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>462.4</v>
+        <v>465.25</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>765.95</v>
+        <v>783.9</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1936</v>
+        <v>2009.1</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1925</v>
+        <v>2000</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1187.2</v>
+        <v>1187.6</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>413.55</v>
+        <v>420.95</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>210.22</v>
+        <v>210.47</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2308.2</v>
+        <v>2276.2</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1435.5</v>
+        <v>1458.7</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4159.2</v>
+        <v>4105.9</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4150</v>
+        <v>4100</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4572.6</v>
+        <v>4452.1</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4550</v>
+        <v>4450</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1474.6</v>
+        <v>1468.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4300</v>
+        <v>4239.6</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4300</v>
+        <v>4250</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3469.5</v>
+        <v>3454.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3475</v>
+        <v>3450</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1323.5</v>
+        <v>1343.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11726</v>
+        <v>11623</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11700</v>
+        <v>11600</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>168.87</v>
+        <v>167.56</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>652.3</v>
+        <v>655</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>332.5</v>
+        <v>344.9</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1284</v>
+        <v>1271.4</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>206.84</v>
+        <v>203.73</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1072.95</v>
+        <v>1079.05</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  26-May-2026 16:45</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  27-May-2026 16:41</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>491</v>
+        <v>500.75</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6804</v>
+        <v>7219</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6800</v>
+        <v>7200</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27610</v>
+        <v>27735</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27600</v>
+        <v>27800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>363.05</v>
+        <v>364.9</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>64.87</v>
+        <v>64.06</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1412.6</v>
+        <v>1426.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2969.3</v>
+        <v>2973.1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1811.2</v>
+        <v>1824.5</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5380</v>
+        <v>5451.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>449.7</v>
+        <v>459.75</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>344.45</v>
+        <v>336.95</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8258.5</v>
+        <v>8272.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>393.25</v>
+        <v>399.75</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>160.54</v>
+        <v>163.62</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2647</v>
+        <v>2671.9</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1578.8</v>
+        <v>1598.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>713.1</v>
+        <v>808.55</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>725</v>
+        <v>800</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1461.2</v>
+        <v>1435.9</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1011.8</v>
+        <v>1005</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1299.3</v>
+        <v>1304.1</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10593</v>
+        <v>10808.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10600</v>
+        <v>10800</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1800.7</v>
+        <v>1809.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>930.2</v>
+        <v>931.15</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2202.7</v>
+        <v>2194.7</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>200.4</v>
+        <v>205.83</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>270.55</v>
+        <v>270.95</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>420.1</v>
+        <v>419.1</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>515.55</v>
+        <v>526.95</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1846.9</v>
+        <v>1852.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>417.75</v>
+        <v>422.35</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>436.15</v>
+        <v>432.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>35835</v>
+        <v>36035</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>35800</v>
+        <v>36000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>304.6</v>
+        <v>307.15</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5338</v>
+        <v>5335.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>133.15</v>
+        <v>134.16</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1567.3</v>
+        <v>1579.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1417.5</v>
+        <v>1418.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>458.15</v>
+        <v>463.05</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1422.8</v>
+        <v>1388.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2077.1</v>
+        <v>2087.4</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>475.9</v>
+        <v>472.3</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>289.05</v>
+        <v>288.25</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5418.5</v>
+        <v>6027.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5400</v>
+        <v>6050</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>447.6</v>
+        <v>445.45</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1727.1</v>
+        <v>1714.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6753</v>
+        <v>6797.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11673</v>
+        <v>11756</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>589.8</v>
+        <v>593.9</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1327.9</v>
+        <v>1319</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7376</v>
+        <v>7419</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2939.6</v>
+        <v>2880.4</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>366.25</v>
+        <v>394.15</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>290.2</v>
+        <v>288.9</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>167.63</v>
+        <v>169</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2351.4</v>
+        <v>2384.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2350</v>
+        <v>2375</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1031.8</v>
+        <v>1044.4</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1760.2</v>
+        <v>1788.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>756.5</v>
+        <v>782.6</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>755</v>
+        <v>785</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3165</v>
+        <v>3170</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>371.5</v>
+        <v>369.8</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4427.7</v>
+        <v>4413</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1201</v>
+        <v>1211</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1161.9</v>
+        <v>1165.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2739.8</v>
+        <v>2716.3</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>778.9</v>
+        <v>758.65</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>618.85</v>
+        <v>609.6</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4983</v>
+        <v>5075</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1103.8</v>
+        <v>1149.7</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>556</v>
+        <v>555.35</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>398</v>
+        <v>402.9</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2209.4</v>
+        <v>2198.4</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>70.22</v>
+        <v>71.48</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>127.47</v>
+        <v>126.59</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>166.01</v>
+        <v>164.61</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>657.15</v>
+        <v>667.7</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2037.9</v>
+        <v>2020.1</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4480.8</v>
+        <v>4570</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4500</v>
+        <v>4550</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>433.25</v>
+        <v>436.25</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1167.7</v>
+        <v>1159.9</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>142.38</v>
+        <v>143.94</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>537.2</v>
+        <v>523.2</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>301.65</v>
+        <v>291.95</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1222.9</v>
+        <v>1220.6</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>576</v>
+        <v>602.05</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1293.6</v>
+        <v>1309.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>430.05</v>
+        <v>427.3</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>388.65</v>
+        <v>388.7</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>784.7</v>
+        <v>771.8</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1604</v>
+        <v>1617.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1373.9</v>
+        <v>1381.7</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>544.15</v>
+        <v>556.45</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4037.8</v>
+        <v>4047.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>282.7</v>
+        <v>281.7</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3540.7</v>
+        <v>3491.6</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2266</v>
+        <v>2276.4</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3107.3</v>
+        <v>3121.6</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>330.25</v>
+        <v>328.75</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>830</v>
+        <v>833.8</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13208</v>
+        <v>13364</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13200</v>
+        <v>13400</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3307.3</v>
+        <v>3158.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3300</v>
+        <v>3150</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>540.85</v>
+        <v>536.15</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1725.6</v>
+        <v>1682.3</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1725</v>
+        <v>1675</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1096</v>
+        <v>1103.2</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>135.82</v>
+        <v>142.41</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2265.3</v>
+        <v>2232.9</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>127160</v>
+        <v>127040</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3331.5</v>
+        <v>3306.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3325</v>
+        <v>3300</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>416.2</v>
+        <v>433.05</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>980.7</v>
+        <v>1005.65</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7396</v>
+        <v>7244.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7400</v>
+        <v>7200</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1428.6</v>
+        <v>1427.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>90.67</v>
+        <v>92.28</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>389.7</v>
+        <v>398.15</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1693.7</v>
+        <v>1692.6</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9882</v>
+        <v>10299.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9900</v>
+        <v>10300</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>287.5</v>
+        <v>274.05</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38305</v>
+        <v>38145</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>38500</v>
+        <v>38000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5105.8</v>
+        <v>5098.4</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>280.2</v>
+        <v>278.8</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>433.7</v>
+        <v>433.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1478.5</v>
+        <v>1480.7</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2837.9</v>
+        <v>2847.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>105.91</v>
+        <v>106.67</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9613.5</v>
+        <v>9664</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>292.55</v>
+        <v>300.15</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>344.25</v>
+        <v>348.25</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>337.6</v>
+        <v>339.7</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1356.3</v>
+        <v>1350.5</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>203.84</v>
+        <v>206.06</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>628.7</v>
+        <v>625.25</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1883.2</v>
+        <v>1864.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>968.5</v>
+        <v>967.8</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25180</v>
+        <v>25400</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>952.15</v>
+        <v>963.2</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3677.2</v>
+        <v>3878.7</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2749.7</v>
+        <v>2736.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1840.8</v>
+        <v>1844.3</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>493.2</v>
+        <v>512.9</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>465.25</v>
+        <v>460.4</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>783.9</v>
+        <v>774.55</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>2009.1</v>
+        <v>1966.6</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>2000</v>
+        <v>1975</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1187.6</v>
+        <v>1204.6</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>420.95</v>
+        <v>425.8</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>210.47</v>
+        <v>214.7</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2276.2</v>
+        <v>2284.2</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1458.7</v>
+        <v>1455.6</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4105.9</v>
+        <v>4137.9</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4100</v>
+        <v>4150</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4452.1</v>
+        <v>4537.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4450</v>
+        <v>4550</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1468.5</v>
+        <v>1440.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4239.6</v>
+        <v>4248.6</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3454.9</v>
+        <v>3384.6</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3450</v>
+        <v>3375</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1343.7</v>
+        <v>1339.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11623</v>
+        <v>11689</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>167.56</v>
+        <v>168.72</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>655</v>
+        <v>656.15</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>344.9</v>
+        <v>354.7</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1271.4</v>
+        <v>1261.8</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>203.73</v>
+        <v>201.58</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1079.05</v>
+        <v>1085.8</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  27-May-2026 16:41</t>
+          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  28-May-2026 16:57</t>
         </is>
       </c>
     </row>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:28-May-2026  NM:25-Jun-2026  |  28-May-2026 16:57</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  29-May-2026 16:44</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>500.75</v>
+        <v>475</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7219</v>
+        <v>7253</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7200</v>
+        <v>7250</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27735</v>
+        <v>26855</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27800</v>
+        <v>26800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>364.9</v>
+        <v>363.3</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>64.06</v>
+        <v>64.61</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1426.6</v>
+        <v>1399.3</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2973.1</v>
+        <v>2937.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1824.5</v>
+        <v>1804.6</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5451.5</v>
+        <v>5498</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>459.75</v>
+        <v>447.85</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>336.95</v>
+        <v>337.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8272.5</v>
+        <v>8176.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>399.75</v>
+        <v>394.5</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>163.62</v>
+        <v>155.44</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2671.9</v>
+        <v>2671.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1598.6</v>
+        <v>1578.2</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>808.55</v>
+        <v>773.3</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1435.9</v>
+        <v>1426.4</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1005</v>
+        <v>984.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1304.1</v>
+        <v>1286.6</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10808.5</v>
+        <v>10460</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10800</v>
+        <v>10500</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1809.1</v>
+        <v>1783.6</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>931.15</v>
+        <v>908.25</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2194.7</v>
+        <v>2205.5</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>205.83</v>
+        <v>208.3</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>270.95</v>
+        <v>268.5</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>419.1</v>
+        <v>410.75</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>526.95</v>
+        <v>500.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1852.2</v>
+        <v>1829</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>422.35</v>
+        <v>416.75</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>432.2</v>
+        <v>428.65</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36035</v>
+        <v>36625</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36000</v>
+        <v>36600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>307.15</v>
+        <v>298.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5335.5</v>
+        <v>5204.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5350</v>
+        <v>5200</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>134.16</v>
+        <v>130.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1579.2</v>
+        <v>1537.7</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1418.2</v>
+        <v>1401</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>463.05</v>
+        <v>457.9</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1388.4</v>
+        <v>1421.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2087.4</v>
+        <v>2059.9</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>472.3</v>
+        <v>463.65</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>288.25</v>
+        <v>281.15</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>6027.5</v>
+        <v>5881</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>6050</v>
+        <v>5900</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>445.45</v>
+        <v>443.4</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1714.8</v>
+        <v>1682</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6797.5</v>
+        <v>6667</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11756</v>
+        <v>11524</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11800</v>
+        <v>11500</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>593.9</v>
+        <v>590.6</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1319</v>
+        <v>1303.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7419</v>
+        <v>7177</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7400</v>
+        <v>7200</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2880.4</v>
+        <v>2859.8</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2900</v>
+        <v>2850</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>394.15</v>
+        <v>386.5</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>288.9</v>
+        <v>288.95</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>169</v>
+        <v>164.51</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2384.9</v>
+        <v>2274.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2375</v>
+        <v>2275</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1044.4</v>
+        <v>1029.3</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1788.6</v>
+        <v>1762.7</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>782.6</v>
+        <v>773.85</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3170</v>
+        <v>3122.4</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3175</v>
+        <v>3125</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>369.8</v>
+        <v>401.15</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4413</v>
+        <v>4303.8</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1211</v>
+        <v>1176.8</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1165.2</v>
+        <v>1183.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2716.3</v>
+        <v>2674.3</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>758.65</v>
+        <v>744.55</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>609.6</v>
+        <v>594.8</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5075</v>
+        <v>4903</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5100</v>
+        <v>4900</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1149.7</v>
+        <v>1126.7</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>555.35</v>
+        <v>538.7</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>402.9</v>
+        <v>393.85</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2198.4</v>
+        <v>2153.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>71.48</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>126.59</v>
+        <v>128.31</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>164.61</v>
+        <v>160.47</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>667.7</v>
+        <v>654.25</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2020.1</v>
+        <v>2015.7</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4570</v>
+        <v>4405</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4550</v>
+        <v>4400</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>932.3</v>
+        <v>914.35</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>436.25</v>
+        <v>442.05</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1159.9</v>
+        <v>1160.9</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>143.94</v>
+        <v>140.24</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>523.2</v>
+        <v>509.85</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>291.95</v>
+        <v>286.9</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1220.6</v>
+        <v>1207.2</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>602.05</v>
+        <v>595.05</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1309.3</v>
+        <v>1278</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>427.3</v>
+        <v>427.5</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>388.7</v>
+        <v>384.2</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>771.8</v>
+        <v>771.95</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1617.2</v>
+        <v>1607.4</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1381.7</v>
+        <v>1362</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>556.45</v>
+        <v>533.15</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4047.5</v>
+        <v>4076.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>281.7</v>
+        <v>286.6</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3491.6</v>
+        <v>3432.4</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2276.4</v>
+        <v>2267.7</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3121.6</v>
+        <v>3045.6</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>328.75</v>
+        <v>325.4</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>833.8</v>
+        <v>821.7</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13364</v>
+        <v>13127</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13400</v>
+        <v>13100</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3158.5</v>
+        <v>2954.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3150</v>
+        <v>2950</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>536.15</v>
+        <v>555.35</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1682.3</v>
+        <v>1674</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1103.2</v>
+        <v>1095</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>142.41</v>
+        <v>145.74</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2232.9</v>
+        <v>2271.4</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>127040</v>
+        <v>123420</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>127000</v>
+        <v>123500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3306.9</v>
+        <v>3342.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3300</v>
+        <v>3350</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>433.05</v>
+        <v>424.45</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1005.65</v>
+        <v>995</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7244.5</v>
+        <v>7129</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1427.5</v>
+        <v>1421.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>92.28</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>398.15</v>
+        <v>386.9</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1692.6</v>
+        <v>1707.1</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>10299.5</v>
+        <v>9964</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>10300</v>
+        <v>10000</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>274.05</v>
+        <v>265.4</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38145</v>
+        <v>38195</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5098.4</v>
+        <v>5194.3</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>278.8</v>
+        <v>271.05</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>433.5</v>
+        <v>428.6</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1480.7</v>
+        <v>1482.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2847.3</v>
+        <v>2775</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>106.67</v>
+        <v>106.05</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9664</v>
+        <v>9477.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>300.15</v>
+        <v>290.55</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>348.25</v>
+        <v>345</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>339.7</v>
+        <v>337.65</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1350.5</v>
+        <v>1321.2</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>206.06</v>
+        <v>204.37</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>625.25</v>
+        <v>624.4</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1864.5</v>
+        <v>1830.1</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1875</v>
+        <v>1825</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>967.8</v>
+        <v>964.4</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25400</v>
+        <v>25275</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>963.2</v>
+        <v>947.15</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3878.7</v>
+        <v>3844</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3900</v>
+        <v>3850</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2736.8</v>
+        <v>2715.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1844.3</v>
+        <v>1799.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>512.9</v>
+        <v>502.15</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>460.4</v>
+        <v>442</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>774.55</v>
+        <v>758</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1966.6</v>
+        <v>1965</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1204.6</v>
+        <v>1178.4</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>425.8</v>
+        <v>420.75</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>214.7</v>
+        <v>208.02</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2284.2</v>
+        <v>2258.9</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1455.6</v>
+        <v>1483.9</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4137.9</v>
+        <v>4074.9</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4150</v>
+        <v>4050</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4537.8</v>
+        <v>4410.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4550</v>
+        <v>4400</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1440.5</v>
+        <v>1420.3</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4248.6</v>
+        <v>4224</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4250</v>
+        <v>4200</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3384.6</v>
+        <v>3355.7</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3375</v>
+        <v>3350</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1339.8</v>
+        <v>1320</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11689</v>
+        <v>11482</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>168.72</v>
+        <v>167.88</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>656.15</v>
+        <v>644.8</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>354.7</v>
+        <v>352.6</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1261.8</v>
+        <v>1245.7</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>201.58</v>
+        <v>204.25</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1085.8</v>
+        <v>1077.7</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -42,9 +42,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -53,10 +51,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,11 +118,35 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -498,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  01-Jun-2026 18:43</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  02-Jun-2026 17:27</t>
         </is>
       </c>
     </row>
@@ -536,6 +565,4326 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>469.75</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>AARTIIND_CM | AARTIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>7146</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>7150</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>ABB_CM | ABB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>26295</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>26200</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA_CM | ABBOTINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>ABCAPITAL_CM | ABCAPITAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>ABFRL_CM | ABFRL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1369.9</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1375</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>ACC_CM | ACC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2968.1</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>ADANIENT_CM | ADANIENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1814.5</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1825</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>ADANIPORTS_CM | ADANIPORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5239</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ALKEM_CM | ALKEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>439.35</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>440</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>AMBUJACEM_CM | AMBUJACEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE_CM | ANGELONE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>8089.5</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>8100</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP_CM | APOLLOHOSP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>390</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE_CM | APOLLOTYRE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>149.05</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>ASHOKLEY_CM | ASHOKLEY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2660.7</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ASIANPAINT_CM | ASIANPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1526.7</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1525</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>ASTRAL_CM | ASTRAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>738.15</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>750</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ATGL_CM | ATGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1429.2</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>AUROPHARMA_CM | AUROPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>976.45</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>975</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>AUBANK_CM | AUBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>1251.1</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>625</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>AXISBANK_CM | AXISBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>10281</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO_CM | BAJAJ-AUTO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1741.4</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV_CM | BAJAJFINSV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>882</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>BAJFINANCE_CM | BAJFINANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>BALKRISIND</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2150.3</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>BALKRISIND_CM | BALKRISIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>206.33</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>BANDHANBNK_CM | BANDHANBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>5850</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>265</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>BANKBARODA_CM | BANKBARODA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>407.85</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>BEL_CM | BEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>508.25</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>BERGEPAINT_CM | BERGEPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1814.2</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1825</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>BHARTIARTL_CM | BHARTIARTL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>410.75</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>410</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>BHEL_CM | BHEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>416.8</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>415</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>BIOCON_CM | BIOCON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>37220</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>37200</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>BOSCHLTD_CM | BOSCHLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>BPCL_CM | BPCL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>5117</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>BRITANNIA_CM | BRITANNIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>129.08</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>4350</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>CANBK_CM | CANBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>1482.8</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>1475</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>CHOLAFIN_CM | CHOLAFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1379.3</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>CIPLA_CM | CIPLA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>472.15</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>470</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>COALINDIA_CM | COALINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1519.5</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE_CM | COFORGE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>1998.8</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>COLPAL_CM | COLPAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>459.45</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>CONCOR_CM | CONCOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>273.45</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>275</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>CROMPTON_CM | CROMPTON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>5708</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>CUMMINSIND_CM | CUMMINSIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>425.5</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>425</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>DABUR_CM | DABUR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1686.5</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR_CM | DEEPAKNTR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>6533</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>DIVISLAB_CM | DIVISLAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>11604</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>11600</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>DIXON_CM | DIXON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>591.85</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>590</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>DLF_CM | DLF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>DRREDDY_CM | DRREDDY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>7141.5</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>EICHERMOT_CM | EICHERMOT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>2750.3</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>ESCORTS_CM | ESCORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>406.25</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>405</v>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>EXIDEIND_CM | EXIDEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>295</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK_CM | FEDERALBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>164.83</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>6400</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>GAIL_CM | GAIL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2184.6</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>2175</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK_CM | GLENMARK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>999.1</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>GODREJCP_CM | GODREJCP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1720.5</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>GODREJPROP_CM | GODREJPROP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>777.55</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>780</v>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>GRANULES_CM | GRANULES_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>3097.6</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>475</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM_CM | GRASIM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>GUJGASLTD</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>396.95</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>GUJGASLTD_CM | GUJGASLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4278.5</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>4300</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>HAL_CM | HAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>1174.6</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>1175</v>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>HAVELLS_CM | HAVELLS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1243.5</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>HCLTECH_CM | HCLTECH_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>2583.5</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>HDFCAMC_CM | HDFCAMC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>748.25</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>750</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>HDFCBANK_CM | HDFCBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>579.9</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>580</v>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>HDFCLIFE_CM | HDFCLIFE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>4875</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO_CM | HEROMOTOCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>1146.3</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>HINDALCO_CM | HINDALCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>546.2</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>3650</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>545</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>HINDCOPPER_CM | HINDCOPPER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>385</v>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>HINDPETRO_CM | HINDPETRO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>2093.7</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>HINDUNILVR_CM | HINDUNILVR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB_CM | IDFCFIRSTB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>IEX_CM | IEX_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>160.85</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>1375</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>IGL_CM | IGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>661.65</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>660</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL_CM | INDHOTEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>INDIAMART</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>1971.4</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>INDIAMART_CM | INDIAMART_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>4466.1</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>4450</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>INDIGO_CM | INDIGO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>912.5</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>900</v>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>INDUSINDBK_CM | INDUSINDBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>429.15</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>INDUSTOWER_CM | INDUSTOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>1270.8</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>INFY_CM | INFY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>138.83</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>IOC_CM | IOC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>516.9</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>875</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>525</v>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>IRCTC_CM | IRCTC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>283.25</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>ITC_CM | ITC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>1203.4</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>JINDALSTEL_CM | JINDALSTEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>588.55</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>590</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>JSWENERGY_CM | JSWENERGY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n">
+        <v>1310.8</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>JSWSTEEL_CM | JSWSTEEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>430.7</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>625</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>425</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>JUBLFOOD_CM | JUBLFOOD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n">
+        <v>379.05</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>375</v>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_CM | KOTAKBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>809.25</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>800</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>KPITTECH_CM | KPITTECH_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n">
+        <v>1561</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>LALPATHLAB_CM | LALPATHLAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>1382.6</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>1385</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS_CM | LAURUSLABS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>535</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>540</v>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>LICHSGFIN_CM | LICHSGFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>4000.9</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>LT_CM | LT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>270.7</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>LTF_CM | LTF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>3508.3</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>LTTS_CM | LTTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>2249.8</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>LUPIN_CM | LUPIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>2998.3</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>M&amp;M_CM | M&amp;M_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>313.55</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>315</v>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>MANAPPURAM_CM | MANAPPURAM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>810.95</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>810</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>MARICO_CM | MARICO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>13022</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>MARUTI_CM | MARUTI_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>2878.7</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>2875</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>MCX_CM | MCX_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>METROPOLIS</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>541.5</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>550</v>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>METROPOLIS_CM | METROPOLIS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>1595.4</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>MFSL_CM | MFSL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>1092.2</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>550</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>MGL_CM | MGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>144.89</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON_CM | MOTHERSON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>2387.7</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>MPHASIS_CM | MPHASIS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>124695</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>124500</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>MRF_CM | MRF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>3262.1</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN_CM | MUTHOOTFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>434.4</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>435</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>NATIONALUM_CM | NATIONALUM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>1015.7</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>NAUKRI_CM | NAUKRI_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>7052</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR_CM | NAVINFLUOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>1398.7</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>NESTLEIND_CM | NESTLEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>NMDC_CM | NMDC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>370</v>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>NTPC_CM | NTPC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>1674.7</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY_CM | OBEROIRLTY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>10344.5</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>OFSS_CM | OFSS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>265.05</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>ONGC_CM | ONGC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>37365</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>37500</v>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>PAGEIND_CM | PAGEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>5470.5</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT_CM | PERSISTENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>269</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>PETRONET_CM | PETRONET_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>413.05</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>415</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>PFC_CM | PFC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>PIDILITIND_CM | PIDILITIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>2739.8</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>PIIND_CM | PIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="n">
+        <v>104.09</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>PNB_CM | PNB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>9531.5</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>POLYCAB_CM | POLYCAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>282.15</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>280</v>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>POWERGRID_CM | POWERGRID_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>344.15</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>345</v>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK_CM | RBLBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>325</v>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>RECLTD_CM | RECLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>1314.6</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>RELIANCE_CM | RELIANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="n">
+        <v>205.85</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E132" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>205</v>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>SAIL_CM | SAIL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>605.5</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>SBICARD_CM | SBICARD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>1801.7</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="E134" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>SBILIFE_CM | SBILIFE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>956.65</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>960</v>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>SBIN_CM | SBIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>24995</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E136" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F136" s="10" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>SHREECEM_CM | SHREECEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>911.7</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN_CM | SHRIRAMFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>3729.7</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>275</v>
+      </c>
+      <c r="E138" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F138" s="10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>SIEMENS_CM | SIEMENS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>2745.3</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>SRF_CM | SRF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>1789.9</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E140" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_CM | SUNPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>517.9</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v>520</v>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>SUNTV_CM | SUNTV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="n">
+        <v>440.85</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E142" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>440</v>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>SYNGENE_CM | SYNGENE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>738.1</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>750</v>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>TATACHEM_CM | TATACHEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>1906.2</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E144" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>1900</v>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>TATACOMM_CM | TATACOMM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>1154.7</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>TATACONSUM_CM | TATACONSUM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>3375</v>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>415</v>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>TATAPOWER_CM | TATAPOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F147" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>TATASTEEL_CM | TATASTEEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>2446.9</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E148" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F148" s="10" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>TCS_CM | TCS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>1571.4</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>1575</v>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>TECHM_CM | TECHM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>4078.1</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>TITAN_CM | TITAN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>4317.9</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>4300</v>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>TORNTPHARM_CM | TORNTPHARM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="n">
+        <v>1423.9</v>
+      </c>
+      <c r="D152" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E152" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>TORNTPOWER_CM | TORNTPOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>4210.4</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>TRENT_CM | TRENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="n">
+        <v>3366.9</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F154" s="10" t="n">
+        <v>3375</v>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>TVSMOTOR_CM | TVSMOTOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>1318.8</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>UBL_CM | UBL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="n">
+        <v>11165</v>
+      </c>
+      <c r="D156" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>11200</v>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO_CM | ULTRACEMCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>162.68</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>UNIONBANK_CM | UNIONBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="n">
+        <v>641.65</v>
+      </c>
+      <c r="D158" s="7" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>650</v>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>UPL_CM | UPL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>333.55</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>VEDL_CM | VEDL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="n">
+        <v>1240.4</v>
+      </c>
+      <c r="D160" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E160" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F160" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>VOLTAS_CM | VOLTAS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>209.84</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>WIPRO_CM | WIPRO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="n">
+        <v>1078.3</v>
+      </c>
+      <c r="D162" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F162" s="10" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE_CM | ZYDUSLIFE_NM</t>
         </is>
       </c>
     </row>
@@ -562,151 +4911,151 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Legend &amp; Column Guide</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Sheet Naming</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SYMBOL_CM = Current Month | SYMBOL_NM = Next Month</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Monthly Expiry</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Last Thursday of each month (NSE standard for stock F&amp;O)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>ATM Row</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Yellow = At-The-Money strike (nearest to spot price)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>CALL (CE)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Blue — buyer profits when stock RISES above strike</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>PUT (PE)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Red — buyer profits when stock FALLS below strike</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Last traded price of the option contract</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Open Interest — total outstanding contracts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Contracts traded in current session</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>IV (%)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Implied Volatility (%) from Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Open / Chg OI</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>0 = not available via Yahoo Finance option chain</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Data Source</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Yahoo Finance (yfinance) — NSE option chain</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>GitHub Actions — Every weekday Mon–Fri at 6:30 PM IST</t>
         </is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  02-Jun-2026 17:27</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  03-Jun-2026 18:02</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>469.75</v>
+        <v>463.8</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7146</v>
+        <v>7196</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7150</v>
+        <v>7200</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26295</v>
+        <v>26290</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>351.3</v>
+        <v>348.75</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61.9</v>
+        <v>60.54</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1369.9</v>
+        <v>1350.9</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2968.1</v>
+        <v>2925.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1814.5</v>
+        <v>1803.8</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5239</v>
+        <v>5274</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>439.35</v>
+        <v>426.95</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>342.65</v>
+        <v>334.75</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8089.5</v>
+        <v>8290.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>391.75</v>
+        <v>391.15</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>149.05</v>
+        <v>145.84</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2660.7</v>
+        <v>2662.4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1526.7</v>
+        <v>1536.9</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>738.15</v>
+        <v>717.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1429.2</v>
+        <v>1440.4</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>976.45</v>
+        <v>970.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1251.1</v>
+        <v>1255.2</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10281</v>
+        <v>10259</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1741.4</v>
+        <v>1734.4</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>882</v>
+        <v>876.8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2150.3</v>
+        <v>2200.4</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>206.33</v>
+        <v>207.62</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>265.8</v>
+        <v>268.85</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>407.85</v>
+        <v>406.6</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>508.25</v>
+        <v>496.05</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1814.2</v>
+        <v>1824.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>410.75</v>
+        <v>406.3</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>416.8</v>
+        <v>412.45</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37220</v>
+        <v>37760</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37200</v>
+        <v>37800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>294.4</v>
+        <v>292.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5117</v>
+        <v>5064</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>129.08</v>
+        <v>131.85</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1482.8</v>
+        <v>1470.6</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1379.3</v>
+        <v>1375.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>472.15</v>
+        <v>472.3</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1519.5</v>
+        <v>1420.9</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1998.8</v>
+        <v>2018.6</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>459.45</v>
+        <v>451.9</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>273.45</v>
+        <v>272.65</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5708</v>
+        <v>5692.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>425.5</v>
+        <v>417.85</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1686.5</v>
+        <v>1698.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6533</v>
+        <v>6576.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11604</v>
+        <v>11227</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11600</v>
+        <v>11200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>591.85</v>
+        <v>581.55</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1274</v>
+        <v>1263.3</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7141.5</v>
+        <v>7130</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2750.3</v>
+        <v>2765</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>406.25</v>
+        <v>398.95</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>293.05</v>
+        <v>301.05</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>164.83</v>
+        <v>163.86</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2184.6</v>
+        <v>2174</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>999.1</v>
+        <v>986.5</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1720.5</v>
+        <v>1704.8</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>777.55</v>
+        <v>793.8</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3097.6</v>
+        <v>3101.6</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>396.95</v>
+        <v>397.75</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4278.5</v>
+        <v>4264.1</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1174.6</v>
+        <v>1156.4</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1243.5</v>
+        <v>1179</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1250</v>
+        <v>1175</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2583.5</v>
+        <v>2510</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>748.25</v>
+        <v>753.65</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>579.9</v>
+        <v>574.4</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4875</v>
+        <v>4840.9</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1146.3</v>
+        <v>1138.9</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>546.2</v>
+        <v>545.4</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>383.75</v>
+        <v>384.1</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2093.7</v>
+        <v>2090.6</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>71.59</v>
+        <v>71.78</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.25</v>
+        <v>123.28</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>160.85</v>
+        <v>161.48</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>661.65</v>
+        <v>656.3</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1971.4</v>
+        <v>1980</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4466.1</v>
+        <v>4512.1</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4450</v>
+        <v>4500</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>912.5</v>
+        <v>899.95</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>429.15</v>
+        <v>429.2</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1270.8</v>
+        <v>1222.6</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1275</v>
+        <v>1225</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>138.83</v>
+        <v>137.38</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>516.9</v>
+        <v>510.8</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>283.25</v>
+        <v>277</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1203.4</v>
+        <v>1211.3</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>588.55</v>
+        <v>580.2</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1310.8</v>
+        <v>1312.9</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>430.7</v>
+        <v>432.3</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>379.05</v>
+        <v>381</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>809.25</v>
+        <v>774.25</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1561</v>
+        <v>1569.6</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1382.6</v>
+        <v>1394.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>535</v>
+        <v>541.25</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4000.9</v>
+        <v>3953.2</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>270.7</v>
+        <v>267.85</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3508.3</v>
+        <v>3299.2</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2249.8</v>
+        <v>2261.2</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2998.3</v>
+        <v>3011.1</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>313.55</v>
+        <v>311.95</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>810.95</v>
+        <v>811.25</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13022</v>
+        <v>13044</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2878.7</v>
+        <v>2833.6</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2875</v>
+        <v>2825</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>541.5</v>
+        <v>536.15</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1595.4</v>
+        <v>1559.6</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1092.2</v>
+        <v>1080.8</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>144.89</v>
+        <v>145.61</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2387.7</v>
+        <v>2288.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>124695</v>
+        <v>124790</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>124500</v>
+        <v>125000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3262.1</v>
+        <v>3218.3</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3250</v>
+        <v>3225</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>434.4</v>
+        <v>436.9</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1015.7</v>
+        <v>1006.05</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7052</v>
+        <v>7035.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1398.7</v>
+        <v>1391.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>95.31</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>367.4</v>
+        <v>366.8</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1674.7</v>
+        <v>1637.4</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1675</v>
+        <v>1625</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>10344.5</v>
+        <v>9997.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>10300</v>
+        <v>10000</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>265.05</v>
+        <v>267.75</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37365</v>
+        <v>37565</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5470.5</v>
+        <v>5097.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5500</v>
+        <v>5100</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>269</v>
+        <v>269.95</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>413.05</v>
+        <v>416.6</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1454.6</v>
+        <v>1469.2</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2739.8</v>
+        <v>2738.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>104.09</v>
+        <v>105.8</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9531.5</v>
+        <v>9571.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>282.15</v>
+        <v>285.05</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>344.15</v>
+        <v>348.2</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>325.05</v>
+        <v>325.65</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1314.6</v>
+        <v>1313.2</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>205.85</v>
+        <v>203.87</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>605.5</v>
+        <v>596.55</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1801.7</v>
+        <v>1784.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>956.65</v>
+        <v>970.45</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24995</v>
+        <v>24775</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>911.7</v>
+        <v>912.95</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3729.7</v>
+        <v>3709.6</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3750</v>
+        <v>3700</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2745.3</v>
+        <v>2718.4</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1789.9</v>
+        <v>1788.5</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>517.9</v>
+        <v>515.25</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>440.85</v>
+        <v>438.1</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>738.1</v>
+        <v>719.75</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1906.2</v>
+        <v>1933.7</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1900</v>
+        <v>1925</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1154.7</v>
+        <v>1144</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>414.9</v>
+        <v>411.75</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>210.6</v>
+        <v>211.89</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2446.9</v>
+        <v>2241.7</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2450</v>
+        <v>2250</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1571.4</v>
+        <v>1472.3</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1575</v>
+        <v>1475</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4078.1</v>
+        <v>4088.8</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4317.9</v>
+        <v>4368.5</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4300</v>
+        <v>4350</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1423.9</v>
+        <v>1436.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4210.4</v>
+        <v>4257.6</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4200</v>
+        <v>4250</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3366.9</v>
+        <v>3316.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3375</v>
+        <v>3325</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1318.8</v>
+        <v>1340</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11165</v>
+        <v>11101</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11200</v>
+        <v>11100</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>162.68</v>
+        <v>166.7</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>641.65</v>
+        <v>646.05</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>333.55</v>
+        <v>328.2</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1240.4</v>
+        <v>1235</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>209.84</v>
+        <v>204.1</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1078.3</v>
+        <v>1076.6</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  03-Jun-2026 18:02</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  04-Jun-2026 16:22</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>463.8</v>
+        <v>460.1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7196</v>
+        <v>7156</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7200</v>
+        <v>7150</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26290</v>
+        <v>25820</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26200</v>
+        <v>25800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>348.75</v>
+        <v>353.65</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>60.54</v>
+        <v>61.03</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1350.9</v>
+        <v>1350.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2925.6</v>
+        <v>2972.8</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1803.8</v>
+        <v>1790.9</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5274</v>
+        <v>5276.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>426.95</v>
+        <v>426.35</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>334.75</v>
+        <v>337.7</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8290.5</v>
+        <v>8249</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>391.15</v>
+        <v>395.75</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>145.84</v>
+        <v>144.44</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2662.4</v>
+        <v>2661.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1536.9</v>
+        <v>1549.3</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>717.6</v>
+        <v>744.05</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1440.4</v>
+        <v>1463.6</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>970.6</v>
+        <v>962.05</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1255.2</v>
+        <v>1253.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10259</v>
+        <v>10362</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10300</v>
+        <v>10400</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1734.4</v>
+        <v>1709.8</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>876.8</v>
+        <v>874.4</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2200.4</v>
+        <v>2191.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>207.62</v>
+        <v>205.44</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>268.85</v>
+        <v>271.3</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>406.6</v>
+        <v>409.9</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>496.05</v>
+        <v>494.25</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1824.1</v>
+        <v>1818.9</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>406.3</v>
+        <v>389.2</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>412.45</v>
+        <v>416.05</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37760</v>
+        <v>37000</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37800</v>
+        <v>37000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>292.1</v>
+        <v>295.15</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5064</v>
+        <v>5090</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.85</v>
+        <v>133.12</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1470.6</v>
+        <v>1486</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1375.2</v>
+        <v>1398.7</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>472.3</v>
+        <v>481.65</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1420.9</v>
+        <v>1436.5</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2018.6</v>
+        <v>2004.4</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>451.9</v>
+        <v>454.35</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>272.65</v>
+        <v>269.3</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5692.5</v>
+        <v>5787.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>417.85</v>
+        <v>424.65</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1698.9</v>
+        <v>1676.7</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6576.5</v>
+        <v>6596.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11227</v>
+        <v>11488</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11200</v>
+        <v>11500</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>581.55</v>
+        <v>577.8</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1263.3</v>
+        <v>1267.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7130</v>
+        <v>7110</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2765</v>
+        <v>2751.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>398.95</v>
+        <v>403.4</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>301.05</v>
+        <v>300.1</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>163.86</v>
+        <v>167.55</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2174</v>
+        <v>2180.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>986.5</v>
+        <v>995.4</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>975</v>
+        <v>1000</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1704.8</v>
+        <v>1694.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>793.8</v>
+        <v>791.35</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3101.6</v>
+        <v>3103.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>397.75</v>
+        <v>402.8</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4264.1</v>
+        <v>4191</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4300</v>
+        <v>4200</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1156.4</v>
+        <v>1166.4</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1179</v>
+        <v>1168.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2510</v>
+        <v>2522.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>753.65</v>
+        <v>754.2</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>574.4</v>
+        <v>573.75</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4840.9</v>
+        <v>4882.3</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1138.9</v>
+        <v>1125.6</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>545.4</v>
+        <v>541.4</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>384.1</v>
+        <v>387</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2090.6</v>
+        <v>2079.4</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>71.78</v>
+        <v>72.16</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123.28</v>
+        <v>124.07</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>161.48</v>
+        <v>162.05</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>656.3</v>
+        <v>661.55</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1980</v>
+        <v>1994.2</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4512.1</v>
+        <v>4508.8</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>899.95</v>
+        <v>903.2</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>429.2</v>
+        <v>430.45</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1222.6</v>
+        <v>1201.3</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>137.38</v>
+        <v>138.95</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>510.8</v>
+        <v>527.5</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>277</v>
+        <v>280.3</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1211.3</v>
+        <v>1197.2</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>580.2</v>
+        <v>590.05</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1312.9</v>
+        <v>1301.1</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>432.3</v>
+        <v>430.3</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>381</v>
+        <v>381.5</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>774.25</v>
+        <v>773</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1569.6</v>
+        <v>1561.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1394.3</v>
+        <v>1427.2</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1395</v>
+        <v>1425</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>541.25</v>
+        <v>545.55</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3953.2</v>
+        <v>3942.1</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>267.85</v>
+        <v>266.7</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3299.2</v>
+        <v>3272.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2261.2</v>
+        <v>2249.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3011.1</v>
+        <v>3016.1</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>311.95</v>
+        <v>310.9</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>811.25</v>
+        <v>816.85</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13044</v>
+        <v>13064</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2833.6</v>
+        <v>2893.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2825</v>
+        <v>2900</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>536.15</v>
+        <v>544.15</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1559.6</v>
+        <v>1581.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1080.8</v>
+        <v>1074.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>145.61</v>
+        <v>144.31</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2288.5</v>
+        <v>2315.9</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>124790</v>
+        <v>124715</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>125000</v>
+        <v>124500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3218.3</v>
+        <v>3169.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3225</v>
+        <v>3175</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>436.9</v>
+        <v>414</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1006.05</v>
+        <v>1008.85</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7035.5</v>
+        <v>7090.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1391.5</v>
+        <v>1382.9</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>96.04000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>366.8</v>
+        <v>366.4</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1637.4</v>
+        <v>1631.9</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9997.5</v>
+        <v>10098</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>267.75</v>
+        <v>267.55</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37565</v>
+        <v>38835</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>37500</v>
+        <v>39000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5097.5</v>
+        <v>5121.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>269.95</v>
+        <v>269.05</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>416.6</v>
+        <v>424.45</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1469.2</v>
+        <v>1471.1</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2738.3</v>
+        <v>2707.5</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>105.8</v>
+        <v>105.67</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9571.5</v>
+        <v>9717.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>285.05</v>
+        <v>284.6</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>348.2</v>
+        <v>353.75</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>325.65</v>
+        <v>335.2</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1313.2</v>
+        <v>1303.7</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>203.87</v>
+        <v>197.31</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>596.55</v>
+        <v>589.5</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1784.2</v>
+        <v>1764.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>970.45</v>
+        <v>979.25</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24775</v>
+        <v>24485</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25000</v>
+        <v>24500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>912.95</v>
+        <v>915.8</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3709.6</v>
+        <v>3686.9</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2718.4</v>
+        <v>2726.6</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1788.5</v>
+        <v>1780.1</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>515.25</v>
+        <v>511.9</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>438.1</v>
+        <v>435.55</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>719.75</v>
+        <v>720.5</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1933.7</v>
+        <v>1985.9</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1925</v>
+        <v>1975</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1144</v>
+        <v>1149.3</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>411.75</v>
+        <v>410.8</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>211.89</v>
+        <v>210.57</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2241.7</v>
+        <v>2241</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1472.3</v>
+        <v>1487.3</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4088.8</v>
+        <v>4231</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4100</v>
+        <v>4250</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4368.5</v>
+        <v>4339.9</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1436.7</v>
+        <v>1440</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4257.6</v>
+        <v>2837.6</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4250</v>
+        <v>2850</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3316.9</v>
+        <v>3362.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3325</v>
+        <v>3350</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1340</v>
+        <v>1350.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11101</v>
+        <v>10997</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>166.7</v>
+        <v>166.54</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>646.05</v>
+        <v>639.15</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>328.2</v>
+        <v>327.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1235</v>
+        <v>1286.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1225</v>
+        <v>1275</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>204.1</v>
+        <v>204.32</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1076.6</v>
+        <v>1084.6</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  04-Jun-2026 16:22</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  05-Jun-2026 15:57</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>460.1</v>
+        <v>458.05</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7156</v>
+        <v>7167.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25820</v>
+        <v>26035</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25800</v>
+        <v>26000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>353.65</v>
+        <v>357.5</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61.03</v>
+        <v>60.09</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1350.8</v>
+        <v>1329.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2972.8</v>
+        <v>3048.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2950</v>
+        <v>3050</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1790.9</v>
+        <v>1824.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5276.5</v>
+        <v>5251.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>426.35</v>
+        <v>417.55</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>337.7</v>
+        <v>332.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8249</v>
+        <v>8304.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>395.75</v>
+        <v>396.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>144.44</v>
+        <v>145.29</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2661.6</v>
+        <v>2686.7</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2650</v>
+        <v>2700</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1549.3</v>
+        <v>1518.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>744.05</v>
+        <v>762.25</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1463.6</v>
+        <v>1462.3</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>962.05</v>
+        <v>969.4</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1253.3</v>
+        <v>1272.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10362</v>
+        <v>10342</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1709.8</v>
+        <v>1703.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>874.4</v>
+        <v>889.4</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2191.9</v>
+        <v>2142</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>205.44</v>
+        <v>205.87</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>271.3</v>
+        <v>263.7</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>409.9</v>
+        <v>408.2</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>494.25</v>
+        <v>490.25</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1818.9</v>
+        <v>1798.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>389.2</v>
+        <v>386.95</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>416.05</v>
+        <v>412.3</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37000</v>
+        <v>37240</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37000</v>
+        <v>37200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>295.15</v>
+        <v>295</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5090</v>
+        <v>5120.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>133.12</v>
+        <v>135.81</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1486</v>
+        <v>1503.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1475</v>
+        <v>1500</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1398.7</v>
+        <v>1401.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>481.65</v>
+        <v>472.3</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1436.5</v>
+        <v>1435.5</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2004.4</v>
+        <v>1999.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>454.35</v>
+        <v>450.95</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>269.3</v>
+        <v>266.6</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5787.5</v>
+        <v>5784</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>424.65</v>
+        <v>424.15</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1676.7</v>
+        <v>1680.1</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6596.5</v>
+        <v>6623</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11488</v>
+        <v>11432</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>577.8</v>
+        <v>577.7</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1267.5</v>
+        <v>1278.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7110</v>
+        <v>7070</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2751.1</v>
+        <v>2781.5</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>403.4</v>
+        <v>399.55</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>300.1</v>
+        <v>304.15</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>167.55</v>
+        <v>167.4</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2180.6</v>
+        <v>2166.2</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>995.4</v>
+        <v>998</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1694.3</v>
+        <v>1708.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>791.35</v>
+        <v>789.85</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3103.5</v>
+        <v>3087.7</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>402.8</v>
+        <v>400.5</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4191</v>
+        <v>4216.9</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1166.4</v>
+        <v>1150.5</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1168.3</v>
+        <v>1154.7</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2522.9</v>
+        <v>2495.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>754.2</v>
+        <v>747.05</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>573.75</v>
+        <v>575.3</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4882.3</v>
+        <v>4835</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1125.6</v>
+        <v>1092.6</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1130</v>
+        <v>1090</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>541.4</v>
+        <v>526.35</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>387</v>
+        <v>385.05</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2079.4</v>
+        <v>2121.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>72.16</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>124.07</v>
+        <v>122.38</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>162.05</v>
+        <v>164.32</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>661.55</v>
+        <v>657.6</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1994.2</v>
+        <v>2000.4</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4508.8</v>
+        <v>4481.3</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>903.2</v>
+        <v>904.8</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>430.45</v>
+        <v>429.65</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1201.3</v>
+        <v>1197.5</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>138.95</v>
+        <v>138.26</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>527.5</v>
+        <v>528.6</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>280.3</v>
+        <v>280.7</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1197.2</v>
+        <v>1181.3</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>590.05</v>
+        <v>584.2</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1301.1</v>
+        <v>1284</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>430.3</v>
+        <v>427.2</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>381.5</v>
+        <v>377.45</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>773</v>
+        <v>777.8</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1561.2</v>
+        <v>1536.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1427.2</v>
+        <v>1446.8</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1425</v>
+        <v>1445</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>545.55</v>
+        <v>549.75</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3942.1</v>
+        <v>3953.2</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>266.7</v>
+        <v>268.6</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3272.1</v>
+        <v>3212.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2249.8</v>
+        <v>2267.7</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3016.1</v>
+        <v>3040.5</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>310.9</v>
+        <v>308.2</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>816.85</v>
+        <v>810.65</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13064</v>
+        <v>13050</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13100</v>
+        <v>13000</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2893.5</v>
+        <v>2795</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>544.15</v>
+        <v>533.2</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1581.5</v>
+        <v>1604.2</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1074.4</v>
+        <v>1089.1</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>144.31</v>
+        <v>143.56</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2315.9</v>
+        <v>2330</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>124715</v>
+        <v>123505</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>124500</v>
+        <v>123500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3169.7</v>
+        <v>3153.1</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3175</v>
+        <v>3150</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>414</v>
+        <v>395.7</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1008.85</v>
+        <v>988.45</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7090.5</v>
+        <v>7032.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1382.9</v>
+        <v>1386.2</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>94.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>366.4</v>
+        <v>361.65</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1631.9</v>
+        <v>1633.4</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>10098</v>
+        <v>9936.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>10100</v>
+        <v>9900</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>267.55</v>
+        <v>264.75</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38835</v>
+        <v>38345</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>39000</v>
+        <v>38500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5121.5</v>
+        <v>5038.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>269.05</v>
+        <v>269.45</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>424.45</v>
+        <v>431.75</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1471.1</v>
+        <v>1476.6</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2707.5</v>
+        <v>2717.9</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>105.67</v>
+        <v>106.85</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9717.5</v>
+        <v>9699</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>284.6</v>
+        <v>285.65</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>353.75</v>
+        <v>351.35</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>335.2</v>
+        <v>343.9</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1303.7</v>
+        <v>1291</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>197.31</v>
+        <v>190.56</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>589.5</v>
+        <v>589.6</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1764.9</v>
+        <v>1782.8</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>979.25</v>
+        <v>977.7</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24485</v>
+        <v>24085</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24500</v>
+        <v>24000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>915.8</v>
+        <v>923.3</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3686.9</v>
+        <v>3700.8</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2726.6</v>
+        <v>2704.9</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1780.1</v>
+        <v>1782.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>511.9</v>
+        <v>516.55</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>435.55</v>
+        <v>434.25</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>720.5</v>
+        <v>719.3</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1985.9</v>
+        <v>1972.7</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1149.3</v>
+        <v>1130.9</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>410.8</v>
+        <v>409.2</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>210.57</v>
+        <v>206.77</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2241</v>
+        <v>2198.9</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1487.3</v>
+        <v>1483.5</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4231</v>
+        <v>4260.2</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4339.9</v>
+        <v>4420.9</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4350</v>
+        <v>4400</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1440</v>
+        <v>1460.1</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2837.6</v>
+        <v>2774.2</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2850</v>
+        <v>2750</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3362.5</v>
+        <v>3383.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3350</v>
+        <v>3375</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1350.7</v>
+        <v>1324</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>10997</v>
+        <v>10912</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>166.54</v>
+        <v>167</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>639.15</v>
+        <v>637.45</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>327.5</v>
+        <v>315.6</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1286.5</v>
+        <v>1298.3</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>204.32</v>
+        <v>198.37</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1084.6</v>
+        <v>1089</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  05-Jun-2026 15:57</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  08-Jun-2026 16:51</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>458.05</v>
+        <v>432.55</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7167.5</v>
+        <v>6958</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7150</v>
+        <v>6950</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26035</v>
+        <v>25780</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26000</v>
+        <v>25800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>357.5</v>
+        <v>344</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>60.09</v>
+        <v>59.29</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1329.8</v>
+        <v>1319.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3048.2</v>
+        <v>2970</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3050</v>
+        <v>2950</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1824.2</v>
+        <v>1805</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5251.5</v>
+        <v>5356.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>417.55</v>
+        <v>415.3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>332.6</v>
+        <v>325.7</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8304.5</v>
+        <v>8358.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>396.8</v>
+        <v>384.85</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>145.29</v>
+        <v>141.02</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2686.7</v>
+        <v>2659.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1518.8</v>
+        <v>1511.2</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>762.25</v>
+        <v>734.2</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1462.3</v>
+        <v>1451.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>969.4</v>
+        <v>958.9</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1272.3</v>
+        <v>1268.1</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10342</v>
+        <v>10231</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10300</v>
+        <v>10200</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1703.2</v>
+        <v>1674.6</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>889.4</v>
+        <v>871.1</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2142</v>
+        <v>2094.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>205.87</v>
+        <v>202.91</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>263.7</v>
+        <v>259.25</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>408.2</v>
+        <v>412.95</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>490.25</v>
+        <v>491.9</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1798.2</v>
+        <v>1813.3</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>386.95</v>
+        <v>386.3</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>412.3</v>
+        <v>409.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37240</v>
+        <v>36610</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37200</v>
+        <v>36600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>295</v>
+        <v>285.15</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5120.5</v>
+        <v>5078.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>135.81</v>
+        <v>131.91</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1503.2</v>
+        <v>1456</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1401.3</v>
+        <v>1387.9</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>472.3</v>
+        <v>464.9</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1435.5</v>
+        <v>1421.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1999.5</v>
+        <v>2005.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>450.95</v>
+        <v>445.35</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>266.6</v>
+        <v>256.9</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5784</v>
+        <v>5610.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5800</v>
+        <v>5600</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>424.15</v>
+        <v>419.75</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1680.1</v>
+        <v>1664.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6623</v>
+        <v>6521</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6600</v>
+        <v>6500</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11432</v>
+        <v>11392</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>577.7</v>
+        <v>561.3</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1278.2</v>
+        <v>1275.6</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7070</v>
+        <v>7050</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2781.5</v>
+        <v>2798.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>399.55</v>
+        <v>385.9</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>304.15</v>
+        <v>304.6</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>167.4</v>
+        <v>168.6</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2166.2</v>
+        <v>2176.5</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1708.3</v>
+        <v>1654.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>789.85</v>
+        <v>766.35</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>790</v>
+        <v>765</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3087.7</v>
+        <v>3050.1</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>400.5</v>
+        <v>400</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4216.9</v>
+        <v>4238</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1150.5</v>
+        <v>1140.3</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1154.7</v>
+        <v>1151.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2495.9</v>
+        <v>2453</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>747.05</v>
+        <v>738.65</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>575.3</v>
+        <v>564.55</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4835</v>
+        <v>4775.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4850</v>
+        <v>4800</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1092.6</v>
+        <v>1062.4</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1090</v>
+        <v>1060</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>526.35</v>
+        <v>506.15</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>385.05</v>
+        <v>372.75</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2121.5</v>
+        <v>2110.1</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>72.34999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>122.38</v>
+        <v>118.96</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>164.32</v>
+        <v>163.62</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>657.6</v>
+        <v>652.25</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2000.4</v>
+        <v>2008.4</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4481.3</v>
+        <v>4359.7</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4500</v>
+        <v>4350</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>904.8</v>
+        <v>895.05</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>429.65</v>
+        <v>426.15</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1197.5</v>
+        <v>1187.6</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>138.26</v>
+        <v>135.6</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>528.6</v>
+        <v>516.1</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>280.7</v>
+        <v>279.45</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1181.3</v>
+        <v>1156.3</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>584.2</v>
+        <v>570.95</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1284</v>
+        <v>1260.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>427.2</v>
+        <v>414.6</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>377.45</v>
+        <v>377.1</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>777.8</v>
+        <v>755.3</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1536.9</v>
+        <v>1545.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1446.8</v>
+        <v>1404.7</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1445</v>
+        <v>1405</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>549.75</v>
+        <v>541</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3953.2</v>
+        <v>3875.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3950</v>
+        <v>3900</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>268.6</v>
+        <v>261.7</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3212.7</v>
+        <v>3165.2</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2267.7</v>
+        <v>2254.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2275</v>
+        <v>2250</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3040.5</v>
+        <v>2966</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3050</v>
+        <v>2950</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>308.2</v>
+        <v>299.2</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>810.65</v>
+        <v>809</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13050</v>
+        <v>12912</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13000</v>
+        <v>12900</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2795</v>
+        <v>2823.8</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2800</v>
+        <v>2825</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>533.2</v>
+        <v>529.65</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1604.2</v>
+        <v>1577.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1089.1</v>
+        <v>1069.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>143.56</v>
+        <v>139.01</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2330</v>
+        <v>2334.1</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>123505</v>
+        <v>122820</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>123500</v>
+        <v>123000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3153.1</v>
+        <v>2964.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3150</v>
+        <v>2975</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>395.7</v>
+        <v>378.2</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>988.45</v>
+        <v>999.2</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7032.5</v>
+        <v>6863.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1386.2</v>
+        <v>1398.9</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>92.90000000000001</v>
+        <v>89.59</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3611,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>361.65</v>
+        <v>362.4</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1633.4</v>
+        <v>1600.4</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9936.5</v>
+        <v>9756</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>264.75</v>
+        <v>264.65</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38345</v>
+        <v>38550</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5038.5</v>
+        <v>5065</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>269.45</v>
+        <v>267.35</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>431.75</v>
+        <v>428.4</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1476.6</v>
+        <v>1459.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2717.9</v>
+        <v>2680.8</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>106.85</v>
+        <v>105.71</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9699</v>
+        <v>9495</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9700</v>
+        <v>9500</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>285.65</v>
+        <v>290.3</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>351.35</v>
+        <v>344.95</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>343.9</v>
+        <v>343.4</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1291</v>
+        <v>1263.3</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>190.56</v>
+        <v>183.78</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>589.6</v>
+        <v>574.55</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1782.8</v>
+        <v>1764.4</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>977.7</v>
+        <v>981.95</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24085</v>
+        <v>23535</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24000</v>
+        <v>23500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>923.3</v>
+        <v>896.65</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3700.8</v>
+        <v>3624</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2704.9</v>
+        <v>2674.4</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1782.2</v>
+        <v>1788.8</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>516.55</v>
+        <v>507.5</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>434.25</v>
+        <v>449.5</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>719.3</v>
+        <v>718</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1972.7</v>
+        <v>1905.8</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1975</v>
+        <v>1900</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1130.9</v>
+        <v>1107</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1130</v>
+        <v>1110</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>409.2</v>
+        <v>404.2</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>206.77</v>
+        <v>202.72</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2198.9</v>
+        <v>2151.4</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1483.5</v>
+        <v>1503.4</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1475</v>
+        <v>1500</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4260.2</v>
+        <v>4192.4</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4250</v>
+        <v>4200</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4420.9</v>
+        <v>4410.4</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1460.1</v>
+        <v>1454.4</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2774.2</v>
+        <v>2724.1</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3383.9</v>
+        <v>3317.6</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3375</v>
+        <v>3325</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1324</v>
+        <v>1314.3</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>10912</v>
+        <v>10795</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10900</v>
+        <v>10800</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>167</v>
+        <v>165.18</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>637.45</v>
+        <v>624.95</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>315.6</v>
+        <v>304.25</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1298.3</v>
+        <v>1276.2</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>198.37</v>
+        <v>181.76</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1089</v>
+        <v>1087.6</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  08-Jun-2026 16:51</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  09-Jun-2026 15:59</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>432.55</v>
+        <v>440.4</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6958</v>
+        <v>6931</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25780</v>
+        <v>26105</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25800</v>
+        <v>26200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>344</v>
+        <v>351.35</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>59.29</v>
+        <v>60.45</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1319.7</v>
+        <v>1324.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2970</v>
+        <v>2979.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1805</v>
+        <v>1826.4</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5356.5</v>
+        <v>5355.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>415.3</v>
+        <v>416</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>325.7</v>
+        <v>337.55</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8358.5</v>
+        <v>8524</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>384.85</v>
+        <v>391.35</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>141.02</v>
+        <v>143.8</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2659.2</v>
+        <v>2708.1</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2650</v>
+        <v>2700</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1511.2</v>
+        <v>1526</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>734.2</v>
+        <v>752.15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1451.8</v>
+        <v>1449</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>958.9</v>
+        <v>978.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1268.1</v>
+        <v>1292.4</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10231</v>
+        <v>10184</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1674.6</v>
+        <v>1693.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>871.1</v>
+        <v>886.9</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2094.6</v>
+        <v>2127.8</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>202.91</v>
+        <v>206.94</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>259.25</v>
+        <v>273.75</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>412.95</v>
+        <v>412.05</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>491.9</v>
+        <v>501.9</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1813.3</v>
+        <v>1799</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>386.3</v>
+        <v>396.55</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>409.25</v>
+        <v>416.35</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>36610</v>
+        <v>37820</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>36600</v>
+        <v>37800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>285.15</v>
+        <v>289.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5078.5</v>
+        <v>5107.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.91</v>
+        <v>137.51</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1456</v>
+        <v>1495.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1387.9</v>
+        <v>1376.5</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>464.9</v>
+        <v>466.9</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1421.1</v>
+        <v>1412</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2005.5</v>
+        <v>2023.4</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>445.35</v>
+        <v>452.95</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>256.9</v>
+        <v>260.45</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5610.5</v>
+        <v>5625.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5600</v>
+        <v>5650</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>419.75</v>
+        <v>426.15</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1664.8</v>
+        <v>1678.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6521</v>
+        <v>6753</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6500</v>
+        <v>6800</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11392</v>
+        <v>11611</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11400</v>
+        <v>11600</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>561.3</v>
+        <v>575.15</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1275.6</v>
+        <v>1268.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7050</v>
+        <v>7203</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2798.7</v>
+        <v>2789.9</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>385.9</v>
+        <v>392.95</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>304.6</v>
+        <v>315.1</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>168.6</v>
+        <v>167.59</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2176.5</v>
+        <v>2209.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2175</v>
+        <v>2200</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>997</v>
+        <v>1013.2</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1654.6</v>
+        <v>1684.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>766.35</v>
+        <v>765.05</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3050.1</v>
+        <v>3095.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>400</v>
+        <v>392.15</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4238</v>
+        <v>4263.8</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1140.3</v>
+        <v>1150.5</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1151.3</v>
+        <v>1146.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2453</v>
+        <v>2503.3</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>738.65</v>
+        <v>738.35</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>564.55</v>
+        <v>560.6</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4775.5</v>
+        <v>4855.4</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4800</v>
+        <v>4850</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1062.4</v>
+        <v>1076.7</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1060</v>
+        <v>1080</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>506.15</v>
+        <v>519.6</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>372.75</v>
+        <v>382</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2110.1</v>
+        <v>2132.8</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>71.43000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>118.96</v>
+        <v>120.06</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>163.62</v>
+        <v>162.5</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>652.25</v>
+        <v>666.7</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2008.4</v>
+        <v>2010.7</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4359.7</v>
+        <v>4537.6</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4350</v>
+        <v>4550</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>895.05</v>
+        <v>922.8</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>426.15</v>
+        <v>419.4</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1187.6</v>
+        <v>1180.3</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>135.6</v>
+        <v>138.13</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>516.1</v>
+        <v>517.85</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>279.45</v>
+        <v>280</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1156.3</v>
+        <v>1149.9</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>570.95</v>
+        <v>570.4</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1260.7</v>
+        <v>1261.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>414.6</v>
+        <v>422.8</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>377.1</v>
+        <v>381.7</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>755.3</v>
+        <v>756.15</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1545.9</v>
+        <v>1575.8</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1404.7</v>
+        <v>1424.4</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1405</v>
+        <v>1425</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>541</v>
+        <v>552.75</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3875.5</v>
+        <v>3900.6</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>261.7</v>
+        <v>265.55</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3165.2</v>
+        <v>3417.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2254.5</v>
+        <v>2264.2</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2966</v>
+        <v>2990.1</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>299.2</v>
+        <v>307.25</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>809</v>
+        <v>813.2</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>12912</v>
+        <v>13120</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>12900</v>
+        <v>13100</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2823.8</v>
+        <v>2824.8</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>529.65</v>
+        <v>535.55</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1577.5</v>
+        <v>1594.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1069.7</v>
+        <v>1059.1</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>139.01</v>
+        <v>144.06</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2334.1</v>
+        <v>2340.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>122820</v>
+        <v>122750</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2964.7</v>
+        <v>2991.1</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2975</v>
+        <v>3000</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>378.2</v>
+        <v>383.9</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>999.2</v>
+        <v>982.6</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6863.5</v>
+        <v>6828.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1398.9</v>
+        <v>1410.4</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>89.59</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>362.4</v>
+        <v>355.65</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1600.4</v>
+        <v>1632.5</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9756</v>
+        <v>9639.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9800</v>
+        <v>9600</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>264.65</v>
+        <v>259</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38550</v>
+        <v>38905</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>38500</v>
+        <v>39000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5065</v>
+        <v>5018</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>267.35</v>
+        <v>268.8</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>428.4</v>
+        <v>435.6</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1459.8</v>
+        <v>1481.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2680.8</v>
+        <v>2866.4</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2700</v>
+        <v>2850</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>105.71</v>
+        <v>109.65</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9495</v>
+        <v>9615.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>290.3</v>
+        <v>285.7</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>344.95</v>
+        <v>361</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>343.4</v>
+        <v>352.1</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1263.3</v>
+        <v>1269.2</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>183.78</v>
+        <v>185.99</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>574.55</v>
+        <v>584.95</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1764.4</v>
+        <v>1769.1</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>981.95</v>
+        <v>1002.7</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>23535</v>
+        <v>23415</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>896.65</v>
+        <v>911.7</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3624</v>
+        <v>3619.8</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2674.4</v>
+        <v>2689.6</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2650</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1788.8</v>
+        <v>1779</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>507.5</v>
+        <v>513.95</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>449.5</v>
+        <v>444.3</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>718</v>
+        <v>726.45</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1905.8</v>
+        <v>1975.8</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1900</v>
+        <v>1975</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1107</v>
+        <v>1106.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>404.2</v>
+        <v>398.65</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>202.72</v>
+        <v>203.18</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2151.4</v>
+        <v>2151</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1503.4</v>
+        <v>1483.8</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1500</v>
+        <v>1475</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4192.4</v>
+        <v>4104.9</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4410.4</v>
+        <v>4472.9</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4400</v>
+        <v>4450</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1454.4</v>
+        <v>1427.8</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2724.1</v>
+        <v>2771.3</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3317.6</v>
+        <v>3358</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3325</v>
+        <v>3350</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1314.3</v>
+        <v>1329</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>10795</v>
+        <v>10911</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10800</v>
+        <v>10900</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>165.18</v>
+        <v>170.44</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>624.95</v>
+        <v>628.4</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>304.25</v>
+        <v>306.25</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1276.2</v>
+        <v>1304.4</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>181.76</v>
+        <v>181.67</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1087.6</v>
+        <v>1105.6</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  09-Jun-2026 15:59</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  10-Jun-2026 16:37</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>440.4</v>
+        <v>433.65</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6931</v>
+        <v>6801</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6950</v>
+        <v>6800</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26105</v>
+        <v>26455</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26200</v>
+        <v>26400</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>351.35</v>
+        <v>342.7</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>60.45</v>
+        <v>58.76</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1324.7</v>
+        <v>1316.2</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2979.9</v>
+        <v>2931.1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1826.4</v>
+        <v>1821.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5355.5</v>
+        <v>5299.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>416</v>
+        <v>409.8</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>337.55</v>
+        <v>329.85</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8524</v>
+        <v>8488.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>391.35</v>
+        <v>385.85</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>143.8</v>
+        <v>141.54</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2708.1</v>
+        <v>2715.1</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1526</v>
+        <v>1501.5</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>752.15</v>
+        <v>728.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1449</v>
+        <v>1453.6</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>978.5</v>
+        <v>959.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1292.4</v>
+        <v>1314.5</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10184</v>
+        <v>10144</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1693.1</v>
+        <v>1664.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>886.9</v>
+        <v>884.1</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2127.8</v>
+        <v>2083.2</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>206.94</v>
+        <v>199.76</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>273.75</v>
+        <v>269.3</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>412.05</v>
+        <v>408.35</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>501.9</v>
+        <v>516.7</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1799</v>
+        <v>1775.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>396.55</v>
+        <v>377.3</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>416.35</v>
+        <v>414.6</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37820</v>
+        <v>37790</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>289.1</v>
+        <v>288</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5107.5</v>
+        <v>5171</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5100</v>
+        <v>5150</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>137.51</v>
+        <v>133.46</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1495.4</v>
+        <v>1472.6</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1500</v>
+        <v>1475</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1376.5</v>
+        <v>1377</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>466.9</v>
+        <v>451</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1412</v>
+        <v>1402.7</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2023.4</v>
+        <v>2056.3</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2025</v>
+        <v>2050</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>452.95</v>
+        <v>445.5</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>260.45</v>
+        <v>254.65</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5625.5</v>
+        <v>5609.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5650</v>
+        <v>5600</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>426.15</v>
+        <v>427.9</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1678.3</v>
+        <v>1664.7</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6753</v>
+        <v>6638.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11611</v>
+        <v>11487</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11600</v>
+        <v>11500</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>575.15</v>
+        <v>563.2</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1268.5</v>
+        <v>1271.7</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7203</v>
+        <v>7219.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2789.9</v>
+        <v>2740.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>392.95</v>
+        <v>386.35</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>315.1</v>
+        <v>311.1</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>167.59</v>
+        <v>168.01</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2209.6</v>
+        <v>2144.4</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1013.2</v>
+        <v>1027.6</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1684.3</v>
+        <v>1641.5</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>765.05</v>
+        <v>760.8</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3095.5</v>
+        <v>3071.2</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3100</v>
+        <v>3075</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>392.15</v>
+        <v>381.3</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4263.8</v>
+        <v>4219.2</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4300</v>
+        <v>4200</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1150.5</v>
+        <v>1155.5</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1146.3</v>
+        <v>1132.1</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2503.3</v>
+        <v>2447.8</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>738.35</v>
+        <v>746.85</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>560.6</v>
+        <v>549.55</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4855.4</v>
+        <v>4856.7</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1076.7</v>
+        <v>1039.3</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1080</v>
+        <v>1040</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>519.6</v>
+        <v>510.7</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>382</v>
+        <v>374.4</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2132.8</v>
+        <v>2169.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>73.69</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>120.06</v>
+        <v>118.75</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>162.5</v>
+        <v>162.17</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>666.7</v>
+        <v>665.85</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2010.7</v>
+        <v>2010</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4537.6</v>
+        <v>4524.9</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4550</v>
+        <v>4500</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>922.8</v>
+        <v>883.95</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>925</v>
+        <v>875</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>419.4</v>
+        <v>413.15</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1180.3</v>
+        <v>1145.3</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>138.13</v>
+        <v>136.88</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>517.85</v>
+        <v>512.35</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>280</v>
+        <v>283.65</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1149.9</v>
+        <v>1121.1</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>570.4</v>
+        <v>560.65</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1261.7</v>
+        <v>1269.8</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>422.8</v>
+        <v>425.05</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>381.7</v>
+        <v>388.1</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>756.15</v>
+        <v>732.95</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1575.8</v>
+        <v>1568.7</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1424.4</v>
+        <v>1385.7</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1425</v>
+        <v>1385</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>552.75</v>
+        <v>541</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3900.6</v>
+        <v>3917.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>265.55</v>
+        <v>260.35</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3417.7</v>
+        <v>3328</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2264.2</v>
+        <v>2247.2</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2275</v>
+        <v>2250</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2990.1</v>
+        <v>2952.5</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>307.25</v>
+        <v>288.25</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>813.2</v>
+        <v>819.9</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13120</v>
+        <v>13073</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2824.8</v>
+        <v>2743.8</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2825</v>
+        <v>2750</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>535.55</v>
+        <v>524.45</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1594.1</v>
+        <v>1598.3</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1059.1</v>
+        <v>1080.5</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>144.06</v>
+        <v>142.21</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2340.5</v>
+        <v>2297.8</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>122750</v>
+        <v>122595</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>123000</v>
+        <v>122500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2991.1</v>
+        <v>2898.8</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>383.9</v>
+        <v>376.15</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>982.6</v>
+        <v>971.25</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>6828.5</v>
+        <v>7046.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1410.4</v>
+        <v>1438.3</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>90.04000000000001</v>
+        <v>88.45</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>355.65</v>
+        <v>351.65</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1632.5</v>
+        <v>1591.6</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9639.5</v>
+        <v>9470</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>259</v>
+        <v>251.9</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38905</v>
+        <v>37955</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>39000</v>
+        <v>38000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5018</v>
+        <v>4928</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>268.8</v>
+        <v>268.3</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>435.6</v>
+        <v>431.3</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1481.8</v>
+        <v>1506.5</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2866.4</v>
+        <v>2807.7</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>109.65</v>
+        <v>107.17</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9615.5</v>
+        <v>9523.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>285.7</v>
+        <v>287.2</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>361</v>
+        <v>356.95</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>352.1</v>
+        <v>348.8</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1269.2</v>
+        <v>1258.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>185.99</v>
+        <v>181.72</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>584.95</v>
+        <v>580.7</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1769.1</v>
+        <v>1728.7</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1775</v>
+        <v>1725</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1002.7</v>
+        <v>1003.25</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>23415</v>
+        <v>23850</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>23500</v>
+        <v>24000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>911.7</v>
+        <v>897.35</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3619.8</v>
+        <v>3582.7</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2689.6</v>
+        <v>2734.1</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1779</v>
+        <v>1786.4</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>513.95</v>
+        <v>506.05</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>444.3</v>
+        <v>454.65</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>726.45</v>
+        <v>720.4</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1975.8</v>
+        <v>1978.6</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1106.5</v>
+        <v>1108</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>398.65</v>
+        <v>394.75</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>203.18</v>
+        <v>199.31</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2151</v>
+        <v>2153.9</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1483.8</v>
+        <v>1478.9</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4104.9</v>
+        <v>4042.1</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4472.9</v>
+        <v>4463.7</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1427.8</v>
+        <v>1399.1</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2771.3</v>
+        <v>2754.7</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3358</v>
+        <v>3334.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3350</v>
+        <v>3325</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1329</v>
+        <v>1327.3</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>10911</v>
+        <v>10866</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>170.44</v>
+        <v>166.45</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>628.4</v>
+        <v>611</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>306.25</v>
+        <v>299.3</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1304.4</v>
+        <v>1290</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>181.67</v>
+        <v>178.93</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1105.6</v>
+        <v>1098.3</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  10-Jun-2026 16:37</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  11-Jun-2026 16:58</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>433.65</v>
+        <v>427.85</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6801</v>
+        <v>6719</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26455</v>
+        <v>26065</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26400</v>
+        <v>26000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>342.7</v>
+        <v>336.6</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>58.76</v>
+        <v>58.24</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1316.2</v>
+        <v>1303.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2931.1</v>
+        <v>2908.8</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1821.2</v>
+        <v>1787.1</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1825</v>
+        <v>1775</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5299.5</v>
+        <v>5301.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>409.8</v>
+        <v>406.05</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>329.85</v>
+        <v>323.75</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -857,7 +857,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8488.5</v>
+        <v>8493</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>385.85</v>
+        <v>380.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>141.54</v>
+        <v>138.58</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2715.1</v>
+        <v>2690.9</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1501.5</v>
+        <v>1490.2</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>728.4</v>
+        <v>716.15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1453.6</v>
+        <v>1464.1</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>959.2</v>
+        <v>963.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1314.5</v>
+        <v>1317.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10144</v>
+        <v>10114</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1664.2</v>
+        <v>1645.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>884.1</v>
+        <v>870.55</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2083.2</v>
+        <v>1974</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2100</v>
+        <v>1950</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>199.76</v>
+        <v>193.9</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>269.3</v>
+        <v>267.6</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>408.35</v>
+        <v>402.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>516.7</v>
+        <v>513.95</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1775.2</v>
+        <v>1782.6</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>377.3</v>
+        <v>370.65</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>414.6</v>
+        <v>415.95</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37790</v>
+        <v>37565</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37800</v>
+        <v>37600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>288</v>
+        <v>286.35</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5171</v>
+        <v>5113</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5150</v>
+        <v>5100</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>133.46</v>
+        <v>131.52</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1472.6</v>
+        <v>1454.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1377</v>
+        <v>1383.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>451</v>
+        <v>446.2</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1402.7</v>
+        <v>1393.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2056.3</v>
+        <v>2028.6</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2050</v>
+        <v>2025</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>445.5</v>
+        <v>440.25</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>254.65</v>
+        <v>253</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5609.5</v>
+        <v>5557</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5600</v>
+        <v>5550</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>427.9</v>
+        <v>421.7</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1664.7</v>
+        <v>1612.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6638.5</v>
+        <v>6655.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11487</v>
+        <v>11371</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>563.2</v>
+        <v>563</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1271.7</v>
+        <v>1276</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7219.5</v>
+        <v>7179.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2740.6</v>
+        <v>2724.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>386.35</v>
+        <v>385.65</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>311.1</v>
+        <v>309.75</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>168.01</v>
+        <v>166.09</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2144.4</v>
+        <v>2144.5</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1027.6</v>
+        <v>1008.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1641.5</v>
+        <v>1618</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>760.8</v>
+        <v>763.15</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3071.2</v>
+        <v>3089.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3075</v>
+        <v>3100</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>381.3</v>
+        <v>376.8</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4219.2</v>
+        <v>4172.3</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1155.5</v>
+        <v>1129</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1132.1</v>
+        <v>1110.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2447.8</v>
+        <v>2389.8</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>746.85</v>
+        <v>744.6</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>549.55</v>
+        <v>545.25</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4856.7</v>
+        <v>4836.2</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1039.3</v>
+        <v>1024.3</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>510.7</v>
+        <v>499.25</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>374.4</v>
+        <v>365.7</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2169.5</v>
+        <v>2139.8</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>72.98999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>118.75</v>
+        <v>117.07</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>162.17</v>
+        <v>160.8</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>665.85</v>
+        <v>655.7</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2010</v>
+        <v>1968.2</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4524.9</v>
+        <v>4502.4</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>883.95</v>
+        <v>888.95</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>875</v>
+        <v>900</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>413.15</v>
+        <v>413</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1145.3</v>
+        <v>1114.6</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>136.88</v>
+        <v>134.24</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>512.35</v>
+        <v>521.05</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>283.65</v>
+        <v>282.4</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1121.1</v>
+        <v>1121.3</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>560.65</v>
+        <v>552.25</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1269.8</v>
+        <v>1282.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>425.05</v>
+        <v>413.6</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>388.1</v>
+        <v>393.35</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>732.95</v>
+        <v>736.9</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1568.7</v>
+        <v>1593.5</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1385.7</v>
+        <v>1390.8</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>541</v>
+        <v>535.9</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3917.5</v>
+        <v>3862</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3900</v>
+        <v>3850</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>260.35</v>
+        <v>256.9</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3328</v>
+        <v>3291.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2247.2</v>
+        <v>2273.3</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>2952.5</v>
+        <v>3000.9</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>288.25</v>
+        <v>292.05</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>819.9</v>
+        <v>810.8</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13073</v>
+        <v>13098</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2743.8</v>
+        <v>2778.8</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2750</v>
+        <v>2775</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>524.45</v>
+        <v>520.15</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1598.3</v>
+        <v>1562.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1080.5</v>
+        <v>1061</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>142.21</v>
+        <v>140.74</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2297.8</v>
+        <v>2277.8</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>122595</v>
+        <v>122935</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>122500</v>
+        <v>123000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2898.8</v>
+        <v>2890</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>376.15</v>
+        <v>370.6</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>971.25</v>
+        <v>963.8</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7046.5</v>
+        <v>7157</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1438.3</v>
+        <v>1422.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.45</v>
+        <v>88.47</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>351.65</v>
+        <v>351.85</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1591.6</v>
+        <v>1582.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9470</v>
+        <v>9265.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9500</v>
+        <v>9300</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>251.9</v>
+        <v>252.6</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37955</v>
+        <v>37740</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>38000</v>
+        <v>37500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4928</v>
+        <v>4874</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>268.3</v>
+        <v>263.05</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>431.3</v>
+        <v>413.55</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1506.5</v>
+        <v>1498.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2807.7</v>
+        <v>2801.2</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>107.17</v>
+        <v>106.17</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9523.5</v>
+        <v>9372</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9500</v>
+        <v>9400</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>287.2</v>
+        <v>286.65</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>356.95</v>
+        <v>359.1</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>348.8</v>
+        <v>336.85</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1258.8</v>
+        <v>1263</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>181.72</v>
+        <v>181.36</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>580.7</v>
+        <v>568.25</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1728.7</v>
+        <v>1719.1</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1003.25</v>
+        <v>1000.7</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>23850</v>
+        <v>23700</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24000</v>
+        <v>23500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>897.35</v>
+        <v>886.25</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3582.7</v>
+        <v>3522</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2734.1</v>
+        <v>2658.4</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2750</v>
+        <v>2650</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1786.4</v>
+        <v>1794.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>506.05</v>
+        <v>501.4</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>454.65</v>
+        <v>447.95</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>720.4</v>
+        <v>741.2</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1978.6</v>
+        <v>1966</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1108</v>
+        <v>1108.6</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>394.75</v>
+        <v>390.25</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>199.31</v>
+        <v>197.96</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2153.9</v>
+        <v>2135.6</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1478.9</v>
+        <v>1465.1</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4042.1</v>
+        <v>4025.2</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4463.7</v>
+        <v>4572.2</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4450</v>
+        <v>4550</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1399.1</v>
+        <v>1376.3</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2754.7</v>
+        <v>2710.9</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3334.9</v>
+        <v>3287.4</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3325</v>
+        <v>3275</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1327.3</v>
+        <v>1320.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>10866</v>
+        <v>10830</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10900</v>
+        <v>10800</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>166.45</v>
+        <v>164.54</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>611</v>
+        <v>593.75</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>299.3</v>
+        <v>304.9</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1290</v>
+        <v>1277.3</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>178.93</v>
+        <v>177.37</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1098.3</v>
+        <v>1105.9</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  11-Jun-2026 16:58</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  12-Jun-2026 16:22</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>427.85</v>
+        <v>440.6</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6719</v>
+        <v>6770.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6700</v>
+        <v>6750</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26065</v>
+        <v>26280</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26000</v>
+        <v>26200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>336.6</v>
+        <v>358.1</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>58.24</v>
+        <v>59.9</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1303.7</v>
+        <v>1336.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2908.8</v>
+        <v>2921.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1787.1</v>
+        <v>1812.9</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1775</v>
+        <v>1825</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5301.5</v>
+        <v>5298</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>406.05</v>
+        <v>423.1</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>323.75</v>
+        <v>339.5</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -857,7 +857,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8493</v>
+        <v>8498</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>380.3</v>
+        <v>396.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>138.58</v>
+        <v>152.45</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2690.9</v>
+        <v>2747.4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1490.2</v>
+        <v>1508.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>716.15</v>
+        <v>728.5</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1464.1</v>
+        <v>1472.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>963.3</v>
+        <v>1015.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>975</v>
+        <v>1025</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1317.3</v>
+        <v>1356.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10114</v>
+        <v>10063</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1645.1</v>
+        <v>1689.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>870.55</v>
+        <v>918.3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1974</v>
+        <v>2013.1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>193.9</v>
+        <v>204.6</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>267.6</v>
+        <v>274.75</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>402.3</v>
+        <v>406.5</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>513.95</v>
+        <v>515.15</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1782.6</v>
+        <v>1822.5</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1775</v>
+        <v>1825</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>370.65</v>
+        <v>378.75</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>415.95</v>
+        <v>419</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>37565</v>
+        <v>39060</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>37600</v>
+        <v>39000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>286.35</v>
+        <v>302.35</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5113</v>
+        <v>5165.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5100</v>
+        <v>5150</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.52</v>
+        <v>131.67</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1454.9</v>
+        <v>1568.1</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1450</v>
+        <v>1575</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1383.3</v>
+        <v>1389.4</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>446.2</v>
+        <v>443.5</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1393.8</v>
+        <v>1367.2</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2028.6</v>
+        <v>2079</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2025</v>
+        <v>2075</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>440.25</v>
+        <v>450.2</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>253</v>
+        <v>256.2</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5557</v>
+        <v>5621.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5550</v>
+        <v>5600</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>421.7</v>
+        <v>426.4</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1612.4</v>
+        <v>1669.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6655.5</v>
+        <v>6638</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11371</v>
+        <v>11546</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>563</v>
+        <v>587.05</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1276</v>
+        <v>1275.4</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7179.5</v>
+        <v>7312</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2724.7</v>
+        <v>2761.4</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>385.65</v>
+        <v>391.95</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>309.75</v>
+        <v>315.7</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>166.09</v>
+        <v>170.5</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2144.5</v>
+        <v>2173.8</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2150</v>
+        <v>2175</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1008.9</v>
+        <v>1033.3</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1618</v>
+        <v>1691.4</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>763.15</v>
+        <v>766.45</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3089.5</v>
+        <v>3105.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>376.8</v>
+        <v>388</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4172.3</v>
+        <v>4192.3</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1129</v>
+        <v>1154.1</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1110.2</v>
+        <v>1109.6</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2389.8</v>
+        <v>2455.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>744.6</v>
+        <v>772.45</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>545.25</v>
+        <v>555.35</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4836.2</v>
+        <v>4962.6</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4850</v>
+        <v>4950</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1024.3</v>
+        <v>1021.6</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>499.25</v>
+        <v>510</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>365.7</v>
+        <v>388.9</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2139.8</v>
+        <v>2168.8</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>72.95</v>
+        <v>76.5</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>117.07</v>
+        <v>120.84</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>160.8</v>
+        <v>163.52</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>655.7</v>
+        <v>679.45</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1968.2</v>
+        <v>2016.4</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4502.4</v>
+        <v>4709.7</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>888.95</v>
+        <v>917.35</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>413</v>
+        <v>421.2</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1114.6</v>
+        <v>1116.4</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>134.24</v>
+        <v>140.94</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>521.05</v>
+        <v>521.35</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>282.4</v>
+        <v>285.1</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1121.3</v>
+        <v>1148.5</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>552.25</v>
+        <v>559.35</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1282.3</v>
+        <v>1297.6</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>413.6</v>
+        <v>419.35</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>393.35</v>
+        <v>403.3</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>736.9</v>
+        <v>749</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1593.5</v>
+        <v>1601.5</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1390.8</v>
+        <v>1394.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>535.9</v>
+        <v>559.5</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3862</v>
+        <v>4049.3</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3850</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>256.9</v>
+        <v>275.95</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3291.1</v>
+        <v>3351.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2273.3</v>
+        <v>2293.3</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2275</v>
+        <v>2300</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3000.9</v>
+        <v>3042.9</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>292.05</v>
+        <v>305.2</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>810.8</v>
+        <v>819.05</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13098</v>
+        <v>13366</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13100</v>
+        <v>13400</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2778.8</v>
+        <v>2853</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2775</v>
+        <v>2850</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>520.15</v>
+        <v>530.7</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1562.1</v>
+        <v>1579</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1061</v>
+        <v>1094.9</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>140.74</v>
+        <v>143.4</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2277.8</v>
+        <v>2270.4</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>122935</v>
+        <v>125515</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>123000</v>
+        <v>125500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2890</v>
+        <v>3042.2</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2900</v>
+        <v>3050</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>370.6</v>
+        <v>376.85</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>963.8</v>
+        <v>972.2</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7157</v>
+        <v>7303</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1422.5</v>
+        <v>1375.7</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.47</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>351.85</v>
+        <v>353.9</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1582.7</v>
+        <v>1622.8</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1575</v>
+        <v>1625</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9265.5</v>
+        <v>9327.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>252.6</v>
+        <v>246.2</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37740</v>
+        <v>38625</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>37500</v>
+        <v>38500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4874</v>
+        <v>4811</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>263.05</v>
+        <v>274.75</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>413.55</v>
+        <v>421.05</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1498.8</v>
+        <v>1535.5</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2801.2</v>
+        <v>2841.7</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>106.17</v>
+        <v>106.88</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9372</v>
+        <v>9554</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>286.65</v>
+        <v>284.8</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>359.1</v>
+        <v>365.85</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>336.85</v>
+        <v>348.05</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1263</v>
+        <v>1293</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>181.36</v>
+        <v>184.09</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>568.25</v>
+        <v>589.45</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1719.1</v>
+        <v>1706</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1000.7</v>
+        <v>1017.15</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1000</v>
+        <v>1020</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>23700</v>
+        <v>24175</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>23500</v>
+        <v>24000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>886.25</v>
+        <v>954.95</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3522</v>
+        <v>3569.6</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3500</v>
+        <v>3550</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2658.4</v>
+        <v>2743</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2650</v>
+        <v>2750</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1794.2</v>
+        <v>1807.7</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>501.4</v>
+        <v>514.7</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>447.95</v>
+        <v>458.55</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>741.2</v>
+        <v>745.95</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1966</v>
+        <v>1966.6</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1108.6</v>
+        <v>1100.7</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>390.25</v>
+        <v>393.55</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>197.96</v>
+        <v>197.86</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2135.6</v>
+        <v>2161.4</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1465.1</v>
+        <v>1429.2</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1475</v>
+        <v>1425</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4025.2</v>
+        <v>4184</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4050</v>
+        <v>4200</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4572.2</v>
+        <v>4571.2</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1376.3</v>
+        <v>1392</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2710.9</v>
+        <v>2755.3</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3287.4</v>
+        <v>3312.8</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3275</v>
+        <v>3325</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1320.7</v>
+        <v>1353.3</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>10830</v>
+        <v>11117</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>10800</v>
+        <v>11100</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>164.54</v>
+        <v>170.05</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>593.75</v>
+        <v>610.1</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>304.9</v>
+        <v>309.65</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1277.3</v>
+        <v>1285.4</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>177.37</v>
+        <v>180.14</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1105.9</v>
+        <v>1104.7</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  12-Jun-2026 16:22</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  15-Jun-2026 17:59</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>440.6</v>
+        <v>498.15</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6770.5</v>
+        <v>6922.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6750</v>
+        <v>6900</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26280</v>
+        <v>26255</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>358.1</v>
+        <v>368.2</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>59.9</v>
+        <v>61.04</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1336.6</v>
+        <v>1356.4</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2921.6</v>
+        <v>2942.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1812.9</v>
+        <v>1804.8</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5298</v>
+        <v>5334</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>423.1</v>
+        <v>428.85</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>339.5</v>
+        <v>352.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8498</v>
+        <v>8468.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>396.3</v>
+        <v>414.35</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>152.45</v>
+        <v>157.7</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2747.4</v>
+        <v>2739.3</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1508.6</v>
+        <v>1544.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>728.5</v>
+        <v>720.05</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1472.8</v>
+        <v>1408.3</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1475</v>
+        <v>1400</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1015.5</v>
+        <v>1033.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1356.3</v>
+        <v>1368.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10063</v>
+        <v>9943</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10100</v>
+        <v>9900</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1689.1</v>
+        <v>1750.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>918.3</v>
+        <v>942.3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2013.1</v>
+        <v>2192.5</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>204.6</v>
+        <v>210.88</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>274.75</v>
+        <v>276.05</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>406.5</v>
+        <v>409.55</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>515.15</v>
+        <v>519.4</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1822.5</v>
+        <v>1841.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>378.75</v>
+        <v>382.85</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>419</v>
+        <v>416.05</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>39060</v>
+        <v>39070</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>302.35</v>
+        <v>310.6</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5165.5</v>
+        <v>5199.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5150</v>
+        <v>5200</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.67</v>
+        <v>132.2</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1568.1</v>
+        <v>1653.6</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1575</v>
+        <v>1650</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1389.4</v>
+        <v>1381.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>443.5</v>
+        <v>444.05</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1367.2</v>
+        <v>1402.5</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2079</v>
+        <v>2057.7</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>450.2</v>
+        <v>459.35</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>256.2</v>
+        <v>266.05</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5621.5</v>
+        <v>5754</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5600</v>
+        <v>5750</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>426.4</v>
+        <v>429.15</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1669.9</v>
+        <v>1666.7</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6638</v>
+        <v>6608.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11546</v>
+        <v>11957</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>11500</v>
+        <v>12000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>587.05</v>
+        <v>614.45</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1275.4</v>
+        <v>1279.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7312</v>
+        <v>7624.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7300</v>
+        <v>7600</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2761.4</v>
+        <v>2801.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>391.95</v>
+        <v>394.85</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>315.7</v>
+        <v>317.1</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>170.5</v>
+        <v>175.41</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2173.8</v>
+        <v>2156.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2175</v>
+        <v>2150</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1033.3</v>
+        <v>1036.8</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1691.4</v>
+        <v>1766.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>766.45</v>
+        <v>748.5</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3105.5</v>
+        <v>3164.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3100</v>
+        <v>3175</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>388</v>
+        <v>399.7</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4192.3</v>
+        <v>4284.7</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1154.1</v>
+        <v>1171.1</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1109.6</v>
+        <v>1119.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2455.9</v>
+        <v>2622.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>772.45</v>
+        <v>777.35</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>555.35</v>
+        <v>581.2</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>4962.6</v>
+        <v>5024</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1021.6</v>
+        <v>1013.9</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>510</v>
+        <v>516.1</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>388.9</v>
+        <v>401.65</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2168.8</v>
+        <v>2156.1</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>76.5</v>
+        <v>78.33</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>120.84</v>
+        <v>122.95</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>163.52</v>
+        <v>169.62</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>679.45</v>
+        <v>689.85</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2016.4</v>
+        <v>2048.7</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4709.7</v>
+        <v>4880.4</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4700</v>
+        <v>4900</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>917.35</v>
+        <v>933.2</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>421.2</v>
+        <v>413.25</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1116.4</v>
+        <v>1134.9</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>140.94</v>
+        <v>144.49</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>521.35</v>
+        <v>517.95</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>285.1</v>
+        <v>287.9</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1148.5</v>
+        <v>1149.5</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>559.35</v>
+        <v>566.25</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1297.6</v>
+        <v>1296.5</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>419.35</v>
+        <v>422.65</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>403.3</v>
+        <v>405.75</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1601.5</v>
+        <v>1616</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1394.3</v>
+        <v>1389.1</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>559.5</v>
+        <v>553.85</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4049.3</v>
+        <v>4169.8</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4150</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>275.95</v>
+        <v>293.25</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3351.1</v>
+        <v>3395.3</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2293.3</v>
+        <v>2273.1</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2300</v>
+        <v>2275</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3042.9</v>
+        <v>3134.3</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3050</v>
+        <v>3150</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>305.2</v>
+        <v>317.65</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>819.05</v>
+        <v>809.65</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13366</v>
+        <v>13805</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13400</v>
+        <v>13800</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2853</v>
+        <v>2895.6</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2850</v>
+        <v>2900</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>530.7</v>
+        <v>525.9</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1579</v>
+        <v>1632.6</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1575</v>
+        <v>1625</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1094.9</v>
+        <v>1139</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>143.4</v>
+        <v>148.12</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2270.4</v>
+        <v>2309.7</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>125515</v>
+        <v>128540</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>125500</v>
+        <v>128500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3042.2</v>
+        <v>3160.1</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3050</v>
+        <v>3150</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>376.85</v>
+        <v>382.35</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>972.2</v>
+        <v>982.45</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7303</v>
+        <v>7287</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1375.7</v>
+        <v>1374.7</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>90.93000000000001</v>
+        <v>88.47</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>353.9</v>
+        <v>348.1</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1622.8</v>
+        <v>1669.4</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1625</v>
+        <v>1675</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9327.5</v>
+        <v>9373</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>246.2</v>
+        <v>243.65</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38625</v>
+        <v>39195</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>38500</v>
+        <v>39000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4811</v>
+        <v>4890.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>274.75</v>
+        <v>285.9</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>421.05</v>
+        <v>424.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1535.5</v>
+        <v>1571</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2841.7</v>
+        <v>2834.5</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>106.88</v>
+        <v>107.96</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9554</v>
+        <v>9556</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>284.8</v>
+        <v>285.7</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>365.85</v>
+        <v>372.65</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>348.05</v>
+        <v>351.85</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1293</v>
+        <v>1307</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>184.09</v>
+        <v>182.51</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>589.45</v>
+        <v>600.9</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1706</v>
+        <v>1759.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1017.15</v>
+        <v>1020.85</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24175</v>
+        <v>24825</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>954.95</v>
+        <v>1000.65</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3569.6</v>
+        <v>3601.8</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3550</v>
+        <v>3600</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2743</v>
+        <v>2720.5</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1807.7</v>
+        <v>1806</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>514.7</v>
+        <v>517.75</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>458.55</v>
+        <v>453.5</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>745.95</v>
+        <v>735.1</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1966.6</v>
+        <v>1933.9</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1975</v>
+        <v>1925</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1100.7</v>
+        <v>1100.4</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>393.55</v>
+        <v>404.1</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>197.86</v>
+        <v>197.28</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2161.4</v>
+        <v>2162</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1429.2</v>
+        <v>1425.6</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4184</v>
+        <v>4283.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4571.2</v>
+        <v>4504</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4550</v>
+        <v>4500</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1392</v>
+        <v>1389.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2755.3</v>
+        <v>2901.1</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2750</v>
+        <v>2900</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3312.8</v>
+        <v>3459.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3325</v>
+        <v>3450</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1353.3</v>
+        <v>1349.4</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11117</v>
+        <v>11466</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11100</v>
+        <v>11500</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>170.05</v>
+        <v>171.3</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>610.1</v>
+        <v>616.6</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>309.65</v>
+        <v>302.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1285.4</v>
+        <v>1326.4</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1275</v>
+        <v>1325</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>180.14</v>
+        <v>181.38</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1104.7</v>
+        <v>1088.1</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  15-Jun-2026 17:59</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  16-Jun-2026 18:07</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>498.15</v>
+        <v>496.7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6922.5</v>
+        <v>7021</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26255</v>
+        <v>26100</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26200</v>
+        <v>26000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>368.2</v>
+        <v>373.8</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61.04</v>
+        <v>60.97</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1356.4</v>
+        <v>1349</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2942.5</v>
+        <v>2943.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1804.8</v>
+        <v>1822</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5334</v>
+        <v>5348</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>428.85</v>
+        <v>426.05</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>352.3</v>
+        <v>348.25</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8468.5</v>
+        <v>8390.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8500</v>
+        <v>8400</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>414.35</v>
+        <v>416.45</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>157.7</v>
+        <v>158.5</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2739.3</v>
+        <v>2748.1</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1544.8</v>
+        <v>1564</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>720.05</v>
+        <v>713.7</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1408.3</v>
+        <v>1396.7</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1033.6</v>
+        <v>1023.1</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1368.3</v>
+        <v>1365.7</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9943</v>
+        <v>9939</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1750.2</v>
+        <v>1787.3</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>942.3</v>
+        <v>959.65</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2192.5</v>
+        <v>2230.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>210.88</v>
+        <v>216.74</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>276.05</v>
+        <v>275.35</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>409.55</v>
+        <v>407.55</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>519.4</v>
+        <v>510.5</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1841.2</v>
+        <v>1853</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>382.85</v>
+        <v>384.2</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>416.05</v>
+        <v>416.45</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>39070</v>
+        <v>39045</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>310.6</v>
+        <v>312.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5199.5</v>
+        <v>5217.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>132.2</v>
+        <v>132.83</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1653.6</v>
+        <v>1680.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1650</v>
+        <v>1675</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1381.3</v>
+        <v>1373.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>444.05</v>
+        <v>450.95</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1402.5</v>
+        <v>1464.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2057.7</v>
+        <v>2096.9</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2050</v>
+        <v>2100</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>459.35</v>
+        <v>463.35</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>266.05</v>
+        <v>264.7</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5754</v>
+        <v>5723.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5750</v>
+        <v>5700</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>429.15</v>
+        <v>435.45</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1666.7</v>
+        <v>1641.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6608.5</v>
+        <v>6712.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11957</v>
+        <v>12235</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>614.45</v>
+        <v>629.3</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1279.5</v>
+        <v>1276.9</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7624.5</v>
+        <v>7560.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2801.1</v>
+        <v>2830</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>394.85</v>
+        <v>388.55</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>317.1</v>
+        <v>320.6</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175.41</v>
+        <v>176.09</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2156.6</v>
+        <v>2156.7</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1036.8</v>
+        <v>1034.5</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1766.2</v>
+        <v>1794.5</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>748.5</v>
+        <v>748.35</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3164.5</v>
+        <v>3140.3</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3175</v>
+        <v>3150</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>399.7</v>
+        <v>394.2</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4284.7</v>
+        <v>4255.8</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1171.1</v>
+        <v>1180.2</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1119.3</v>
+        <v>1159</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2622.9</v>
+        <v>2658.6</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>777.35</v>
+        <v>784.9</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>581.2</v>
+        <v>574.4</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5024</v>
+        <v>5031</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5000</v>
+        <v>5050</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1013.9</v>
+        <v>982.4</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1010</v>
+        <v>980</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>516.1</v>
+        <v>511.75</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>401.65</v>
+        <v>401.8</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2156.1</v>
+        <v>2199.9</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>78.33</v>
+        <v>77.5</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>122.95</v>
+        <v>123.57</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>169.62</v>
+        <v>168.76</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>689.85</v>
+        <v>694.4</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2048.7</v>
+        <v>2084.1</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4880.4</v>
+        <v>4840</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>933.2</v>
+        <v>926</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>413.25</v>
+        <v>411.75</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1134.9</v>
+        <v>1143.6</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>144.49</v>
+        <v>145.11</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>517.95</v>
+        <v>522.9</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>287.9</v>
+        <v>291.65</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1149.5</v>
+        <v>1139.8</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>566.25</v>
+        <v>562.05</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1296.5</v>
+        <v>1274.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>422.65</v>
+        <v>423.35</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>405.75</v>
+        <v>407.85</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>757</v>
+        <v>756.55</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1616</v>
+        <v>1642</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1389.1</v>
+        <v>1376.4</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1390</v>
+        <v>1375</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>553.85</v>
+        <v>552.8</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4169.8</v>
+        <v>4186.4</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4150</v>
+        <v>4200</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>293.25</v>
+        <v>294.25</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3395.3</v>
+        <v>3462.9</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2273.1</v>
+        <v>2277.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3134.3</v>
+        <v>3137.9</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>317.65</v>
+        <v>317.45</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>809.65</v>
+        <v>808.45</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13805</v>
+        <v>13691</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13800</v>
+        <v>13700</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2895.6</v>
+        <v>2885.4</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2900</v>
+        <v>2875</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>525.9</v>
+        <v>534.15</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1632.6</v>
+        <v>1612.3</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1139</v>
+        <v>1185.6</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>148.12</v>
+        <v>147.6</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2309.7</v>
+        <v>2327.2</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>128540</v>
+        <v>128470</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3160.1</v>
+        <v>3166.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3150</v>
+        <v>3175</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>382.35</v>
+        <v>366.65</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>982.45</v>
+        <v>997.65</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7287</v>
+        <v>7315.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1374.7</v>
+        <v>1391.7</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.47</v>
+        <v>88.09</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>348.1</v>
+        <v>355.55</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1669.4</v>
+        <v>1704.8</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9373</v>
+        <v>9500.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9400</v>
+        <v>9500</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>243.65</v>
+        <v>248.2</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>39195</v>
+        <v>39065</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4890.5</v>
+        <v>5016.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>285.9</v>
+        <v>290.55</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>424.5</v>
+        <v>427.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1571</v>
+        <v>1571.2</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2834.5</v>
+        <v>2878</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2850</v>
+        <v>2900</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>107.96</v>
+        <v>107.97</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9556</v>
+        <v>9591.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>285.7</v>
+        <v>285.15</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>372.65</v>
+        <v>369.7</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>351.85</v>
+        <v>356.55</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1307</v>
+        <v>1328.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>182.51</v>
+        <v>180.99</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>600.9</v>
+        <v>621.65</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1759.5</v>
+        <v>1767.6</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1020.85</v>
+        <v>1015.3</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24825</v>
+        <v>24870</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1000.65</v>
+        <v>1005.75</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3601.8</v>
+        <v>3636.9</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3600</v>
+        <v>3650</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2720.5</v>
+        <v>2744</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1806</v>
+        <v>1800.7</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>517.75</v>
+        <v>519.85</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>453.5</v>
+        <v>453.1</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>735.1</v>
+        <v>729.45</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1933.9</v>
+        <v>1913.6</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1100.4</v>
+        <v>1130.9</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1100</v>
+        <v>1130</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>404.1</v>
+        <v>402.25</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>197.28</v>
+        <v>196</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2162</v>
+        <v>2199</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1425.6</v>
+        <v>1446.8</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4283.5</v>
+        <v>4338</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4300</v>
+        <v>4350</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4504</v>
+        <v>4466.7</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4500</v>
+        <v>4450</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1389.7</v>
+        <v>1408.4</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2901.1</v>
+        <v>2897.8</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3459.5</v>
+        <v>3435.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3450</v>
+        <v>3425</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1349.4</v>
+        <v>1335.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11466</v>
+        <v>11391</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>171.3</v>
+        <v>170.56</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>616.6</v>
+        <v>615.35</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>302.5</v>
+        <v>299.95</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1326.4</v>
+        <v>1327.6</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>181.38</v>
+        <v>182.67</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1088.1</v>
+        <v>1078.7</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  16-Jun-2026 18:07</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  17-Jun-2026 16:41</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>496.7</v>
+        <v>479.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7021</v>
+        <v>7164</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7000</v>
+        <v>7150</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26100</v>
+        <v>25955</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>373.8</v>
+        <v>372.45</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>60.97</v>
+        <v>61.72</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2943.6</v>
+        <v>2951.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1822</v>
+        <v>1828.6</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5348</v>
+        <v>5347.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>426.05</v>
+        <v>426.45</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>348.25</v>
+        <v>348.7</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8390.5</v>
+        <v>8427.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>416.45</v>
+        <v>429.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>158.5</v>
+        <v>159.57</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2748.1</v>
+        <v>2738</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1564</v>
+        <v>1565.2</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>713.7</v>
+        <v>702.65</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>725</v>
+        <v>700</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1396.7</v>
+        <v>1422.4</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1400</v>
+        <v>1425</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1023.1</v>
+        <v>1020.85</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1365.7</v>
+        <v>1350.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9939</v>
+        <v>10042</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1787.3</v>
+        <v>1764.6</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>959.65</v>
+        <v>958.4</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2230.6</v>
+        <v>2256</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>216.74</v>
+        <v>213.76</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>275.35</v>
+        <v>281.85</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>407.55</v>
+        <v>419.85</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>510.5</v>
+        <v>511.7</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1853</v>
+        <v>1875.7</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>384.2</v>
+        <v>392.25</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>416.45</v>
+        <v>411.85</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>39045</v>
+        <v>39230</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>39000</v>
+        <v>39200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>312.1</v>
+        <v>317.95</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5217.5</v>
+        <v>5232</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>132.83</v>
+        <v>135.24</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1680.4</v>
+        <v>1679.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1373.2</v>
+        <v>1350.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>450.95</v>
+        <v>455.75</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1464.8</v>
+        <v>1465.7</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2096.9</v>
+        <v>2034.2</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2100</v>
+        <v>2025</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>463.35</v>
+        <v>467</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>264.7</v>
+        <v>275.9</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5723.5</v>
+        <v>5833</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5700</v>
+        <v>5850</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>435.45</v>
+        <v>429</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1641.3</v>
+        <v>1615.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6712.5</v>
+        <v>6663.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>12235</v>
+        <v>12833</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>12200</v>
+        <v>12800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>629.3</v>
+        <v>623.55</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1276.9</v>
+        <v>1269</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7560.5</v>
+        <v>7509</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>388.55</v>
+        <v>388.4</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>320.6</v>
+        <v>322.7</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>176.09</v>
+        <v>175.03</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2156.7</v>
+        <v>2136.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2150</v>
+        <v>2125</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1034.5</v>
+        <v>1020</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1794.5</v>
+        <v>1788.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>748.35</v>
+        <v>741.4</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3140.3</v>
+        <v>3150.4</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>394.2</v>
+        <v>397.3</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4255.8</v>
+        <v>4460.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4300</v>
+        <v>4500</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1180.2</v>
+        <v>1196.8</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1159</v>
+        <v>1166.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2658.6</v>
+        <v>2711.1</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>784.9</v>
+        <v>787.1</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>574.4</v>
+        <v>581.8</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5031</v>
+        <v>5016.4</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5050</v>
+        <v>5000</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>982.4</v>
+        <v>1007.9</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>980</v>
+        <v>1010</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>511.75</v>
+        <v>515.2</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>401.8</v>
+        <v>402.65</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2199.9</v>
+        <v>2197.6</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>77.5</v>
+        <v>77.38</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123.57</v>
+        <v>124.18</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>168.76</v>
+        <v>170.78</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>694.4</v>
+        <v>699.1</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2084.1</v>
+        <v>2090</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4840</v>
+        <v>4878.4</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>926</v>
+        <v>936.2</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>411.75</v>
+        <v>413.85</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1143.6</v>
+        <v>1157.7</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>145.11</v>
+        <v>145.42</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>522.9</v>
+        <v>519.95</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>291.65</v>
+        <v>290.75</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1139.8</v>
+        <v>1135.8</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>562.05</v>
+        <v>572</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1274.3</v>
+        <v>1287.2</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>423.35</v>
+        <v>423.15</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>407.85</v>
+        <v>404.5</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>756.55</v>
+        <v>752</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1642</v>
+        <v>1651.8</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1376.4</v>
+        <v>1369.8</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>552.8</v>
+        <v>551.05</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4186.4</v>
+        <v>4207.7</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>294.25</v>
+        <v>294.15</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3462.9</v>
+        <v>3453.8</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2277.8</v>
+        <v>2272</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3137.9</v>
+        <v>3132.9</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>317.45</v>
+        <v>319.05</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>808.45</v>
+        <v>805</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13691</v>
+        <v>13630</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13700</v>
+        <v>13600</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2885.4</v>
+        <v>2857.3</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2875</v>
+        <v>2850</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>534.15</v>
+        <v>545.6</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1612.3</v>
+        <v>1631.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1185.6</v>
+        <v>1208.9</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>147.6</v>
+        <v>145.1</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2327.2</v>
+        <v>2340.2</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>128470</v>
+        <v>129245</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>128500</v>
+        <v>129000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3166.9</v>
+        <v>3190.6</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3175</v>
+        <v>3200</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>366.65</v>
+        <v>370</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>997.65</v>
+        <v>1017.05</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7315.5</v>
+        <v>7344</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1391.7</v>
+        <v>1407.3</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.09</v>
+        <v>88</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1704.8</v>
+        <v>1694.8</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9500.5</v>
+        <v>9444.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9500</v>
+        <v>9400</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>248.2</v>
+        <v>245</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>39065</v>
+        <v>39300</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>39000</v>
+        <v>39500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5016.5</v>
+        <v>5045</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>290.55</v>
+        <v>292</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>427.5</v>
+        <v>431.75</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1571.2</v>
+        <v>1578.2</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2878</v>
+        <v>2835.2</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2900</v>
+        <v>2850</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>107.97</v>
+        <v>108.87</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9591.5</v>
+        <v>9926.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9600</v>
+        <v>9900</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>285.15</v>
+        <v>286.35</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>369.7</v>
+        <v>369.2</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>356.55</v>
+        <v>358.75</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1328.8</v>
+        <v>1332.7</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>180.99</v>
+        <v>179.58</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>621.65</v>
+        <v>625.7</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1767.6</v>
+        <v>1793.6</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1015.3</v>
+        <v>1026.5</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24870</v>
+        <v>24970</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1005.75</v>
+        <v>1007.5</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3636.9</v>
+        <v>3725.4</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3650</v>
+        <v>3750</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2744</v>
+        <v>2705.5</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1800.7</v>
+        <v>1820.4</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>519.85</v>
+        <v>519.35</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>453.1</v>
+        <v>448.3</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>729.45</v>
+        <v>729</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1913.6</v>
+        <v>1899.8</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1925</v>
+        <v>1900</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1130.9</v>
+        <v>1124.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>402.25</v>
+        <v>401.5</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>196</v>
+        <v>199.01</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2199</v>
+        <v>2223</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1446.8</v>
+        <v>1462.4</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4338</v>
+        <v>4380.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4350</v>
+        <v>4400</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4466.7</v>
+        <v>4442.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1408.4</v>
+        <v>1407.3</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2897.8</v>
+        <v>3102.8</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3435.5</v>
+        <v>3448.7</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3425</v>
+        <v>3450</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1335.7</v>
+        <v>1335</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11391</v>
+        <v>11373</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>170.56</v>
+        <v>173.75</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>615.35</v>
+        <v>614.4</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>299.95</v>
+        <v>306.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1327.6</v>
+        <v>1352.9</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>182.67</v>
+        <v>184.47</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1078.7</v>
+        <v>1061.4</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  17-Jun-2026 16:41</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  18-Jun-2026 16:37</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>479.2</v>
+        <v>486.45</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7164</v>
+        <v>7229</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7150</v>
+        <v>7250</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25955</v>
+        <v>26145</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26000</v>
+        <v>26200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>372.45</v>
+        <v>370.6</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61.72</v>
+        <v>61.54</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1350</v>
+        <v>1358.9</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2951.9</v>
+        <v>3013.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1828.6</v>
+        <v>1842.1</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5347.5</v>
+        <v>5372</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>426.45</v>
+        <v>430</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>348.7</v>
+        <v>352.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8427.5</v>
+        <v>8411.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>429.6</v>
+        <v>428</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>159.57</v>
+        <v>158.45</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2738</v>
+        <v>2755</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1565.2</v>
+        <v>1565.7</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>702.65</v>
+        <v>724.35</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1422.4</v>
+        <v>1443.7</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1020.85</v>
+        <v>1025.35</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1350.9</v>
+        <v>1360.1</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10042</v>
+        <v>10077</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1764.6</v>
+        <v>1771.7</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>958.4</v>
+        <v>958.85</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2256</v>
+        <v>2234.2</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>213.76</v>
+        <v>214.28</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>281.85</v>
+        <v>283</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>419.85</v>
+        <v>428.6</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>511.7</v>
+        <v>505.05</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1875.7</v>
+        <v>1874.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>392.25</v>
+        <v>405.9</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>411.85</v>
+        <v>413.85</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>39230</v>
+        <v>40035</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>39200</v>
+        <v>40000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>317.95</v>
+        <v>316.3</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5232</v>
+        <v>5245</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>135.24</v>
+        <v>134.97</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1679.2</v>
+        <v>1688.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1350.8</v>
+        <v>1355.5</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>455.75</v>
+        <v>452</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1465.7</v>
+        <v>1483</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2034.2</v>
+        <v>2027.3</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>467</v>
+        <v>467.15</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>275.9</v>
+        <v>277.1</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5833</v>
+        <v>5858</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>429</v>
+        <v>428.7</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1615.3</v>
+        <v>1658.2</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6663.5</v>
+        <v>6767</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>12833</v>
+        <v>12666</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>12800</v>
+        <v>12700</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>623.55</v>
+        <v>640.7</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1269</v>
+        <v>1267.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7509</v>
+        <v>7601</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2831</v>
+        <v>2809.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>388.4</v>
+        <v>384.85</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>322.7</v>
+        <v>320.45</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175.03</v>
+        <v>176.44</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2136.6</v>
+        <v>2154</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2125</v>
+        <v>2150</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1020</v>
+        <v>1009.2</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1788.3</v>
+        <v>1810.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>741.4</v>
+        <v>782.1</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3150.4</v>
+        <v>3145.1</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>397.3</v>
+        <v>399.7</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4460.5</v>
+        <v>4411.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1196.8</v>
+        <v>1194.4</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1166.8</v>
+        <v>1161.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2711.1</v>
+        <v>2728.2</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>787.1</v>
+        <v>799</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>581.8</v>
+        <v>591.3</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5016.4</v>
+        <v>5021.6</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1007.9</v>
+        <v>1008.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>515.2</v>
+        <v>509.7</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>402.65</v>
+        <v>401.6</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2197.6</v>
+        <v>2218.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>77.38</v>
+        <v>78.09</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>124.18</v>
+        <v>123.56</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>170.78</v>
+        <v>169.99</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>699.1</v>
+        <v>710.45</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2090</v>
+        <v>2137.7</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4878.4</v>
+        <v>5011.8</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>936.2</v>
+        <v>938.75</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>413.85</v>
+        <v>414.3</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1157.7</v>
+        <v>1127.5</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>145.42</v>
+        <v>146.11</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>519.95</v>
+        <v>524</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>290.75</v>
+        <v>291.15</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1135.8</v>
+        <v>1131.9</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>572</v>
+        <v>575.55</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1287.2</v>
+        <v>1293.9</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>423.15</v>
+        <v>422.95</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>404.5</v>
+        <v>402.95</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>752</v>
+        <v>745.95</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1651.8</v>
+        <v>1662.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1369.8</v>
+        <v>1368.8</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>551.05</v>
+        <v>550.15</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4207.7</v>
+        <v>4190</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>294.15</v>
+        <v>286.9</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3453.8</v>
+        <v>3407.8</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2272</v>
+        <v>2327.1</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2275</v>
+        <v>2325</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3132.9</v>
+        <v>3136.5</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>319.05</v>
+        <v>321.35</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>805</v>
+        <v>820.75</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13630</v>
+        <v>13484</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13600</v>
+        <v>13500</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2857.3</v>
+        <v>2817.2</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2850</v>
+        <v>2825</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>545.6</v>
+        <v>542.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1631.8</v>
+        <v>1688.2</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1625</v>
+        <v>1700</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1208.9</v>
+        <v>1210.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>145.1</v>
+        <v>144.68</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2340.2</v>
+        <v>2336.6</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>129245</v>
+        <v>130085</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>129000</v>
+        <v>130000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3190.6</v>
+        <v>3182.4</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3200</v>
+        <v>3175</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>370</v>
+        <v>367.75</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1017.05</v>
+        <v>1006.8</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7344</v>
+        <v>7303.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1407.3</v>
+        <v>1400.4</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88</v>
+        <v>88.53</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>355.55</v>
+        <v>361.95</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1694.8</v>
+        <v>1694.2</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9444.5</v>
+        <v>9399.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>245</v>
+        <v>245.3</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>39300</v>
+        <v>40180</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>39500</v>
+        <v>40000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5045</v>
+        <v>4940.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>292</v>
+        <v>288.25</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>431.75</v>
+        <v>429.3</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1578.2</v>
+        <v>1581.1</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2835.2</v>
+        <v>2846</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>108.87</v>
+        <v>109.58</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9926.5</v>
+        <v>9952.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>286.35</v>
+        <v>288.7</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>369.2</v>
+        <v>369.25</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>358.75</v>
+        <v>358.7</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1332.7</v>
+        <v>1328.1</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>179.58</v>
+        <v>182.16</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>625.7</v>
+        <v>624.95</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1793.6</v>
+        <v>1807.6</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1026.5</v>
+        <v>1042.7</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24970</v>
+        <v>25410</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25000</v>
+        <v>25500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1007.5</v>
+        <v>1002.7</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3725.4</v>
+        <v>3746.2</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2705.5</v>
+        <v>2703</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1820.4</v>
+        <v>1824.8</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>519.35</v>
+        <v>521.9</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>448.3</v>
+        <v>440.3</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>729</v>
+        <v>732.65</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1899.8</v>
+        <v>1942</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1124.5</v>
+        <v>1111.4</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>401.5</v>
+        <v>402.9</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>199.01</v>
+        <v>200.52</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2223</v>
+        <v>2203.3</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1462.4</v>
+        <v>1447.7</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4380.5</v>
+        <v>4387.9</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4442.8</v>
+        <v>4445.5</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1407.3</v>
+        <v>1448.6</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3102.8</v>
+        <v>3179.7</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3448.7</v>
+        <v>3457.6</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1335</v>
+        <v>1341.3</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11373</v>
+        <v>11430</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>173.75</v>
+        <v>176.12</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>614.4</v>
+        <v>610.8</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>306.5</v>
+        <v>306</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1352.9</v>
+        <v>1357.6</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>184.47</v>
+        <v>182.84</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1061.4</v>
+        <v>1074.4</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  18-Jun-2026 16:37</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  19-Jun-2026 16:08</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>486.45</v>
+        <v>484.5</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7229</v>
+        <v>7248</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26145</v>
+        <v>26215</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>370.6</v>
+        <v>375.9</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61.54</v>
+        <v>60.64</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1358.9</v>
+        <v>1343.3</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3013.4</v>
+        <v>3038.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1842.1</v>
+        <v>1835.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5372</v>
+        <v>5373.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>430</v>
+        <v>423.95</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>352.8</v>
+        <v>353.7</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8411.5</v>
+        <v>8489.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>428</v>
+        <v>425.5</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>158.45</v>
+        <v>156.66</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2755</v>
+        <v>2732.9</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1565.7</v>
+        <v>1542.1</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>724.35</v>
+        <v>727.3</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1443.7</v>
+        <v>1497.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1025.35</v>
+        <v>1033.05</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1360.1</v>
+        <v>1357.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10077</v>
+        <v>10066</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1771.7</v>
+        <v>1769.4</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>958.85</v>
+        <v>961.8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2234.2</v>
+        <v>2243.7</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>214.28</v>
+        <v>208.09</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>283</v>
+        <v>281.05</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>428.6</v>
+        <v>426.9</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>505.05</v>
+        <v>550.7</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1874.8</v>
+        <v>1910.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>405.9</v>
+        <v>414.35</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>413.85</v>
+        <v>415.5</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>40035</v>
+        <v>40195</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>40000</v>
+        <v>40200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>316.3</v>
+        <v>306.6</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5245</v>
+        <v>5195</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5250</v>
+        <v>5200</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>134.97</v>
+        <v>133.74</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1688.9</v>
+        <v>1693.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1355.5</v>
+        <v>1351.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>452</v>
+        <v>451.3</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1483</v>
+        <v>1463.3</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2027.3</v>
+        <v>1997.8</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>467.15</v>
+        <v>471.75</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>277.1</v>
+        <v>275.25</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5858</v>
+        <v>5865</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>428.7</v>
+        <v>423.5</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1658.2</v>
+        <v>1644.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>6767</v>
+        <v>6743</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>12666</v>
+        <v>12517</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>12700</v>
+        <v>12500</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>640.7</v>
+        <v>624.5</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1267.5</v>
+        <v>1272.1</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7601</v>
+        <v>7611</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2809.7</v>
+        <v>2821.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>384.85</v>
+        <v>380.75</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>320.45</v>
+        <v>323.95</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>176.44</v>
+        <v>173.9</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2154</v>
+        <v>2213.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2150</v>
+        <v>2225</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1009.2</v>
+        <v>1000.6</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1810.2</v>
+        <v>1795.9</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>782.1</v>
+        <v>786.9</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3145.1</v>
+        <v>3149.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>399.7</v>
+        <v>388.45</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4411.5</v>
+        <v>4408.1</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1194.4</v>
+        <v>1176.3</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1161.8</v>
+        <v>1131.7</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2728.2</v>
+        <v>2719</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>799</v>
+        <v>779.8</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>591.3</v>
+        <v>591.85</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5021.6</v>
+        <v>4974.9</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1008.5</v>
+        <v>1010</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>509.7</v>
+        <v>511.15</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>401.6</v>
+        <v>392.1</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2218.5</v>
+        <v>2194.6</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>78.09</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123.56</v>
+        <v>122.78</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>169.99</v>
+        <v>167.6</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>710.45</v>
+        <v>724.75</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>2137.7</v>
+        <v>2089.4</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5011.8</v>
+        <v>5021.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>938.75</v>
+        <v>947.45</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>414.3</v>
+        <v>411.2</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1127.5</v>
+        <v>1051.4</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1125</v>
+        <v>1050</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>146.11</v>
+        <v>143.43</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>524</v>
+        <v>519.6</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>291.15</v>
+        <v>292.5</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1131.9</v>
+        <v>1137.7</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>575.55</v>
+        <v>570.1</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1293.9</v>
+        <v>1287.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>422.95</v>
+        <v>419</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>402.95</v>
+        <v>399.25</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>745.95</v>
+        <v>760.05</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1662.9</v>
+        <v>1635.8</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1368.8</v>
+        <v>1412.9</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1370</v>
+        <v>1415</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>550.15</v>
+        <v>549.9</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4190</v>
+        <v>4209.4</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>286.9</v>
+        <v>286.5</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3407.8</v>
+        <v>3331.2</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2327.1</v>
+        <v>2351.6</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3136.5</v>
+        <v>3074.8</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3150</v>
+        <v>3050</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>321.35</v>
+        <v>318.65</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>820.75</v>
+        <v>817.05</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13484</v>
+        <v>13395</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2817.2</v>
+        <v>2803.8</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2825</v>
+        <v>2800</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>542.5</v>
+        <v>552.75</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1688.2</v>
+        <v>1669.3</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1210.7</v>
+        <v>1209</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>144.68</v>
+        <v>145.54</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2336.6</v>
+        <v>2267.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2350</v>
+        <v>2250</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>130085</v>
+        <v>128645</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>130000</v>
+        <v>128500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3182.4</v>
+        <v>3126.1</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3175</v>
+        <v>3125</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>367.75</v>
+        <v>376</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1006.8</v>
+        <v>984.25</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7303.5</v>
+        <v>7493.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7300</v>
+        <v>7500</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1400.4</v>
+        <v>1414.8</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>88.53</v>
+        <v>88.42</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>361.95</v>
+        <v>365.8</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1694.2</v>
+        <v>1683.5</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>9399.5</v>
+        <v>9638.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>245.3</v>
+        <v>246.25</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>40180</v>
+        <v>39975</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>4940.5</v>
+        <v>4829</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>288.25</v>
+        <v>288.7</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>429.3</v>
+        <v>431</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1581.1</v>
+        <v>1579.9</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2846</v>
+        <v>2803.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>109.58</v>
+        <v>108.77</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9952.5</v>
+        <v>10083</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>10000</v>
+        <v>10100</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>288.7</v>
+        <v>292.25</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>369.25</v>
+        <v>378.85</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>358.7</v>
+        <v>355.35</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1328.1</v>
+        <v>1309.5</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>182.16</v>
+        <v>180.05</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>624.95</v>
+        <v>616.9</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1807.6</v>
+        <v>1800.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1042.7</v>
+        <v>1035.1</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25410</v>
+        <v>25075</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25500</v>
+        <v>25000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1002.7</v>
+        <v>1001.9</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3746.2</v>
+        <v>3759.6</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2703</v>
+        <v>2709.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1824.8</v>
+        <v>1838.3</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>521.9</v>
+        <v>520.85</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>440.3</v>
+        <v>440.75</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>732.65</v>
+        <v>729.15</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1942</v>
+        <v>1988.8</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1111.4</v>
+        <v>1111.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>402.9</v>
+        <v>402.35</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>200.52</v>
+        <v>198.96</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2203.3</v>
+        <v>2125</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1447.7</v>
+        <v>1409.6</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4387.9</v>
+        <v>4419.9</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4445.5</v>
+        <v>4429.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1448.6</v>
+        <v>1438.4</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3179.7</v>
+        <v>3205.8</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3457.6</v>
+        <v>3442.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1341.3</v>
+        <v>1341.9</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11430</v>
+        <v>11367</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>176.12</v>
+        <v>175.76</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>610.8</v>
+        <v>608.65</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>306</v>
+        <v>300.8</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1357.6</v>
+        <v>1343.4</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>182.84</v>
+        <v>180.8</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1074.4</v>
+        <v>1070.8</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  19-Jun-2026 16:08</t>
+          <t>NSE Stock Options  |  CM:25-Jun-2026  NM:30-Jul-2026  |  22-Jun-2026 17:42</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>484.5</v>
+        <v>486.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7248</v>
+        <v>7258</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26215</v>
+        <v>26065</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26200</v>
+        <v>26000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>375.9</v>
+        <v>391.95</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>60.64</v>
+        <v>60.72</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1343.3</v>
+        <v>1349.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3038.4</v>
+        <v>3059.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1835.3</v>
+        <v>1827.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5373.5</v>
+        <v>5367</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>423.95</v>
+        <v>428</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>353.7</v>
+        <v>354.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8489.5</v>
+        <v>8469</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>425.5</v>
+        <v>428.15</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>156.66</v>
+        <v>157.19</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2732.9</v>
+        <v>2674</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2750</v>
+        <v>2650</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1542.1</v>
+        <v>1557.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>727.3</v>
+        <v>733.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1497.8</v>
+        <v>1491.9</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1033.05</v>
+        <v>1045.05</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
 